--- a/inputs/es/demo_region3_input.xlsx
+++ b/inputs/es/demo_region3_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{965E11F9-2183-4A25-A5BC-03AC173FD7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DD57AC4-52F5-43EB-9B7E-A6F8F2E563EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5681,7 +5681,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7z4e2h2EaMpgOfkE7wePfpAzmqET3CqPuNnEA6uSpBpX9/v4I1q/r7FT7CfwTJpIiFPCHtlmRayZ13qT/AXinw==" saltValue="9BDV2ezX41lp7EoUDonPhg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BTeOL4PuKmSLPjjCSOs80FItv7MNSLC4tKf32uxMpBD/Yypocvcwh1Hy4eoGBKAkU9vbKVi22bABdIJXMLkrZg==" saltValue="aHKCf9lb9r6Lx8Ozr1n4JQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -6605,7 +6605,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JehJ+e27fROk1WcDW4ucVg6/TMJKtklh6Dz0gk9XGXWRaiU7og2CBtXdsaoPUZnbCH8+PeT32G6h4f/+PyK9zQ==" saltValue="rP2HYonjV6b/Wh9Z+J325w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vhBZbloXbd9z7Nu+qubRg1Jy0idiQKuj1K/sQQqy4S9pBqy+Y5mhRIjAQPjx853I0kPrFahHnutzNCiHPFXOyA==" saltValue="4QjKFaOjeUySIA/Z7mxOzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -6764,7 +6764,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="A3qEKwQ1AbVFI54hYK+34mhiaUaieTo+sKGy8dbrVMTh8XTYuQtyijOzyW6szheQ0o9HuxYJyZaob5CbLJT+aQ==" saltValue="uFTVGdjBbXKecOKtJpnBZg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jiWB00uK7Buh7QPwIgfwe6Ho/x0HcT5hcXg8b8kh9XS4lQJzK22f9eudbviuKUnYrUVrw+J5liux0jDvsLBVvw==" saltValue="/lehf6I6FAWveTRqQvwdKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -6859,7 +6859,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ivaR+2EdHerkPmyFZxAnP+ss3M7xpszGoZ3CuqGAMjkvU3CskRowg8lfc5A9t8ZOk1HP2YfU6zcZ2A+0gQOj0w==" saltValue="t2KcHuXsyO5tfE3uPv9E8w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ph11QfXaZwUwbp6PSi5tTIBwlVY+qQSdyxmajd132Hb9GqpsmH2O7pOUQkO3qDSU8a9n0NFRVrtKGPggHVszQw==" saltValue="xVg08oGhAwgtkpBnA35eFw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6969,7 +6969,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6bqswvVrDtgH/Qi+Th3bjawSACQOkHb4DpkAUhQ667MgWUnzNM+ZVJOAMY+Z796JK2Q/4v3pwDAOBJzmAr6vKA==" saltValue="QS82jg/o5eMrh55J4qgSmQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6xH+Dpn6un7VgESq2QYltSkucy+OJohTteitO2QsBo78MJFaKzkQDaJKxCl0fOoGa0GBL2MOk0vQtV+ikSfURw==" saltValue="lJXdIcAhpHKmQQ4oB+EoUA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -8725,7 +8725,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7PNVmXyWyrsHl9fjht5pEsy9INdkr2jsaEe2S2kWvyzY9Pt5JSsxYYP4j0hoqUJa+Yp+dn3k3qzUUDjesxTlpA==" saltValue="dm0iE9ax3FRZ6/OjDNBtpA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ODQVTVPe9ia9KmL3614urMB61n7QTu/6BiGrmtrMnp73ol8QK0HXS3nxCWdJ+w+SWcfYp72tKlx6Zg4W6Cd2yA==" saltValue="TKDFvL1YekVc4Av22QkZ3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -8760,7 +8760,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vNbsnwRC0Xx20yK1SaguzHT8W8imD2hxQnNc7ddTmcb/Nb98PjRmFJMEVseheescpLKE55oKo9W1Sp99wbTIJQ==" saltValue="VuFyPp1BZ1iGt6oiWqzjRw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CnKNMk0+sHNsSE3w7qKDdCiomc3E+G0YdaKhL+15H7Lhrhr3NOubTlKJWPA8dysC8jtammFO6B5NI//mcUIM3A==" saltValue="nKfgK54MNECcV7U7frUhSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8960,7 +8960,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a5y84epqmvy5GZkvxRMNzUGjUKbgX+5GL13zjffXsmGXRdAKaykSiD0nOTpjcZ9ky/tqMbuDJ9IbJBjMQP5r9A==" saltValue="ceRpXHDOvZk1pnprjD5zDA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SaMQGX7D/HQLzReIsuxqBpLFHnIS/0fid32ddoCVYrsJj326RrszSnYDi8vX199CneYctOnMsfdszDzw5KllJA==" saltValue="puqRpilpJ5cKmZfUhrQeew==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10769,7 +10769,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="naId2hytSFIeo1HsCy5GRIYJs2F1YbkYHE13EO6fUOTMaLRyS2na3Wk4UkW1RQPmHGaX54rUthVEYSCb9VpT3A==" saltValue="cK8BJ+VHUxdv1jEVdRRNkg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+sOyrC2SmtgEpNbdCZJCp2B7G1V1caAS/8CTeGvOEg9K8/wrGvfZkUQerDm4jQr3YXGog6j6AT3p7AgMUrIYpQ==" saltValue="qQrI++mlSwcxfvJ9sJpMQQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11531,7 +11531,7 @@
       <c r="K39" s="101"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vu0mGfQFFrSvbu1H0hQyf4Ro/PVJqSm7IG0keW8qVtLuAOBP2te0axgJ9vU7FHvU8bNLEk6qgCMmRpwPQ0yQpA==" saltValue="+rTLGMaDL6bewEVTYksHQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dYeUc+bkN8hRwef88lEyephmy7yKvBG8vvnO3q7HikgvCSKQxvbOCKOf6ExBu/bRtRAehdmzk7u2Wtw49h4Q5g==" saltValue="bIC8SEmfbPQFcJ1jCr5p4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11900,7 +11900,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/cieVNL1mGHXTbFY6gH4XAfwwEDacBL33CznOgmCatXFxrafuQFnzeKA2zc8COab98C6PwpzDCILDCi8FBleQg==" saltValue="wSKsJcsQ3HM8pgU1xAb4Bg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="k1yJv1brA/8tFEWIirVpGcBG/oTQVGu6QrlDKZEkJ3zlJIWefgyuheiDBe1cIO2Pwn2QyZAtyxkOBpJvgKXSyw==" saltValue="qv82NSkN9Kt2kDavBJf23A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12984,7 +12984,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z5xqYdWnjCZ3fm6HVtsuGtxICtcBQ6uFXua4YV227HLQU1cJK5R5i4OZX5N4KrYjwTU3czE3b9OGdKmhxwnukQ==" saltValue="gml7gWeH5GJrVM5FKPZ98w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Vnnv3UKzpJIcm9o1XHJGe26Ovc8KEhMj4elDooxYtPc8VQzEgBaa1Ml8O1BdwnLQOv4TEFYPm0bGOHBt/a4UIQ==" saltValue="DtBAGxQgPg1LRU3U1mOX/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -13113,9 +13113,7 @@
         <v>150</v>
       </c>
       <c r="D5" s="102">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="102">
         <v>1</v>
@@ -13136,9 +13134,7 @@
         <v>149</v>
       </c>
       <c r="D6" s="102">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.56)</f>
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="102">
         <v>1</v>
@@ -13185,9 +13181,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="102">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>2.8134491663553263</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="102">
         <v>1</v>
@@ -13208,9 +13202,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="102">
-        <f>IFERROR((MIN(1,1.56*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.56*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.56)</f>
-        <v>2.8134491663553263</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="102">
         <v>1</v>
@@ -14241,9 +14233,7 @@
         <v>150</v>
       </c>
       <c r="D58" s="102">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="102">
         <f t="shared" si="1"/>
@@ -14268,9 +14258,7 @@
         <v>149</v>
       </c>
       <c r="D59" s="102">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.37)</f>
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="102">
         <f t="shared" si="1"/>
@@ -14327,9 +14315,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="102">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.9415046815127641</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="102">
         <f t="shared" si="2"/>
@@ -14354,9 +14340,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="102">
-        <f>IFERROR((MIN(1,1.37*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.37*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.37)</f>
-        <v>1.9415046815127641</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="102">
         <f t="shared" si="2"/>
@@ -15586,9 +15570,7 @@
         <v>150</v>
       </c>
       <c r="D111" s="102">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="102">
         <f t="shared" si="8"/>
@@ -15613,9 +15595,7 @@
         <v>149</v>
       </c>
       <c r="D112" s="102">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$C$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$C$2))) /
-('Distribución de lactancia'!$C$2/(1-'Distribución de lactancia'!$C$2)), 1.77)</f>
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="102">
         <f t="shared" si="8"/>
@@ -15672,9 +15652,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="102">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>4.5688105335991329</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="102">
         <f t="shared" si="9"/>
@@ -15699,9 +15677,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="102">
-        <f>IFERROR((MIN(1,1.77*'Distribución de lactancia'!$D$2)/(1-MIN(1,1.77*'Distribución de lactancia'!$D$2))) /
-('Distribución de lactancia'!$D$2/(1-'Distribución de lactancia'!$D$2)), 1.77)</f>
-        <v>4.5688105335991329</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="102">
         <f t="shared" si="9"/>
@@ -16803,14 +16779,38 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zJt94Qkkjevgdh5GBPa2+GvwvHVCgI92EOVUj7/6wCkFhy43+ghYMGyPhXBc1zy8x3Ty0eHnezbOiMmtBAManA==" saltValue="tFmsTOsrO/eQQh3VqtZHsA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NtBIRwIFOjO2Igv6B3NzMNGtLK1fjLsPFK/UmebI2EkheY1PiJS+X/I9l6NA4GqZwtBzeD5D9BYqLBSLzhfkHg==" saltValue="6PCQ0GyGhs1xyNg4yulDcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -16820,41 +16820,14 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D158:H158" unlockedFormula="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -18067,7 +18040,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sT4NoGELbCRXD+CtpCshoWwMjgj0HNcunxVDlvJQCnmWNNdEh4TwIrmypJvR7fF07fZhh+k0JhqsjoPyV5HJOA==" saltValue="usuR7daawGyKNbdVWA5xBA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D+SVSSiuH8NeX8GvkUbRALVeKtNKu11HFZ+OTmLI0CVLM36TNFG5pY0HgxIZMaiDVHvWeSI1CxTdAWghUYVzJQ==" saltValue="5IjgGYpw4c2jrIEZT1dMCw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -19781,7 +19754,7 @@
         <v>124</v>
       </c>
       <c r="D66" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E66" s="103">
         <v>1</v>
@@ -19896,7 +19869,7 @@
         <v>124</v>
       </c>
       <c r="D70" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E70" s="103">
         <v>1</v>
@@ -20011,7 +19984,7 @@
         <v>124</v>
       </c>
       <c r="D74" s="103">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="E74" s="103">
         <v>1</v>
@@ -21013,24 +20986,24 @@
         <v>7</v>
       </c>
       <c r="D113" s="105">
-        <f>D3*0.8</f>
-        <v>0.8</v>
+        <f>IF(D3=1,1,D3*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E113" s="105">
-        <f t="shared" ref="E113:H113" si="0">E3*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="E113:H113" si="0">IF(E3=1,1,E3*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H113" s="105">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -21038,24 +21011,24 @@
         <v>273</v>
       </c>
       <c r="D114" s="105">
-        <f t="shared" ref="D114:H114" si="1">D4*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="D114:H129" si="1">IF(D4=1,1,D4*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="F114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="G114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="H114" s="105">
         <f t="shared" si="1"/>
-        <v>1.3360000000000001</v>
+        <v>1.5029999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -21063,24 +21036,24 @@
         <v>274</v>
       </c>
       <c r="D115" s="105">
-        <f t="shared" ref="D115:H115" si="2">D5*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="F115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="G115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
       <c r="H115" s="105">
-        <f t="shared" si="2"/>
-        <v>1.9039999999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.1419999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -21088,24 +21061,24 @@
         <v>272</v>
       </c>
       <c r="D116" s="105">
-        <f t="shared" ref="D116:H116" si="3">D6*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="F116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="G116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="3"/>
-        <v>5.0640000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.6970000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -21116,24 +21089,24 @@
         <v>7</v>
       </c>
       <c r="D117" s="105">
-        <f t="shared" ref="D117:H117" si="4">D7*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H117" s="105">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -21141,24 +21114,24 @@
         <v>273</v>
       </c>
       <c r="D118" s="105">
-        <f t="shared" ref="D118:H118" si="5">D8*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="F118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="G118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
       <c r="H118" s="105">
-        <f t="shared" si="5"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.395</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -21166,24 +21139,24 @@
         <v>274</v>
       </c>
       <c r="D119" s="105">
-        <f t="shared" ref="D119:H119" si="6">D9*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="F119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="G119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
       <c r="H119" s="105">
-        <f t="shared" si="6"/>
-        <v>1.7440000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.9620000000000002</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -21191,24 +21164,24 @@
         <v>272</v>
       </c>
       <c r="D120" s="105">
-        <f t="shared" ref="D120:H120" si="7">D10*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="F120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="G120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
       <c r="H120" s="105">
-        <f t="shared" si="7"/>
-        <v>5.1120000000000001</v>
+        <f t="shared" si="1"/>
+        <v>5.7509999999999994</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -21219,24 +21192,24 @@
         <v>7</v>
       </c>
       <c r="D121" s="105">
-        <f t="shared" ref="D121:H121" si="8">D11*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H121" s="105">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -21244,24 +21217,24 @@
         <v>273</v>
       </c>
       <c r="D122" s="105">
-        <f t="shared" ref="D122:H122" si="9">D12*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H122" s="105">
-        <f t="shared" si="9"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -21269,24 +21242,24 @@
         <v>274</v>
       </c>
       <c r="D123" s="105">
-        <f t="shared" ref="D123:H123" si="10">D13*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="F123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="G123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
       <c r="H123" s="105">
-        <f t="shared" si="10"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.5110000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -21294,24 +21267,24 @@
         <v>272</v>
       </c>
       <c r="D124" s="105">
-        <f t="shared" ref="D124:H124" si="11">D14*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="F124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="G124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
       <c r="H124" s="105">
-        <f t="shared" si="11"/>
-        <v>4.8079999999999998</v>
+        <f t="shared" si="1"/>
+        <v>5.4089999999999998</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -21322,24 +21295,24 @@
         <v>7</v>
       </c>
       <c r="D125" s="105">
-        <f t="shared" ref="D125:H125" si="12">D15*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H125" s="105">
-        <f t="shared" si="12"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -21347,24 +21320,24 @@
         <v>273</v>
       </c>
       <c r="D126" s="105">
-        <f t="shared" ref="D126:H126" si="13">D16*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H126" s="105">
-        <f t="shared" si="13"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -21372,24 +21345,24 @@
         <v>274</v>
       </c>
       <c r="D127" s="105">
-        <f t="shared" ref="D127:H127" si="14">D17*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H127" s="105">
-        <f t="shared" si="14"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -21397,24 +21370,24 @@
         <v>272</v>
       </c>
       <c r="D128" s="105">
-        <f t="shared" ref="D128:H128" si="15">D18*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H128" s="105">
-        <f t="shared" si="15"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -21425,24 +21398,24 @@
         <v>7</v>
       </c>
       <c r="D129" s="105">
-        <f t="shared" ref="D129:H129" si="16">D19*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H129" s="105">
-        <f t="shared" si="16"/>
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -21450,24 +21423,24 @@
         <v>273</v>
       </c>
       <c r="D130" s="105">
-        <f t="shared" ref="D130:H130" si="17">D20*0.8</f>
-        <v>0.8</v>
+        <f t="shared" ref="D130:H136" si="2">IF(D20=1,1,D20*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H130" s="105">
-        <f t="shared" si="17"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -21475,24 +21448,24 @@
         <v>274</v>
       </c>
       <c r="D131" s="105">
-        <f t="shared" ref="D131:H131" si="18">D21*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="F131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="G131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="H131" s="105">
-        <f t="shared" si="18"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -21500,24 +21473,24 @@
         <v>272</v>
       </c>
       <c r="D132" s="105">
-        <f t="shared" ref="D132:H132" si="19">D22*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="F132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="G132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="H132" s="105">
-        <f t="shared" si="19"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -21528,24 +21501,24 @@
         <v>7</v>
       </c>
       <c r="D133" s="105">
-        <f t="shared" ref="D133:H133" si="20">D23*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H133" s="105">
-        <f t="shared" si="20"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -21553,24 +21526,24 @@
         <v>273</v>
       </c>
       <c r="D134" s="105">
-        <f t="shared" ref="D134:H134" si="21">D24*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="G134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="H134" s="105">
-        <f t="shared" si="21"/>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -21578,24 +21551,24 @@
         <v>274</v>
       </c>
       <c r="D135" s="105">
-        <f t="shared" ref="D135:H135" si="22">D25*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="F135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="G135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
       <c r="H135" s="105">
-        <f t="shared" si="22"/>
-        <v>1.4880000000000002</v>
+        <f t="shared" si="2"/>
+        <v>1.6740000000000002</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -21603,24 +21576,24 @@
         <v>272</v>
       </c>
       <c r="D136" s="105">
-        <f t="shared" ref="D136:H136" si="23">D26*0.8</f>
-        <v>0.8</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="E136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="F136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="G136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
       <c r="H136" s="105">
-        <f t="shared" si="23"/>
-        <v>2.4079999999999999</v>
+        <f t="shared" si="2"/>
+        <v>2.7090000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="13" x14ac:dyDescent="0.3">
@@ -21670,24 +21643,24 @@
         <v>7</v>
       </c>
       <c r="D140" s="105">
-        <f>D30*0.7</f>
-        <v>0.7</v>
+        <f>IF(D30=1,1,D30*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E140" s="105">
-        <f t="shared" ref="E140:H140" si="24">E30*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E140:H140" si="3">IF(E30=1,1,E30*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="G140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
       <c r="H140" s="105">
-        <f t="shared" si="24"/>
-        <v>0.7</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -21695,24 +21668,24 @@
         <v>273</v>
       </c>
       <c r="D141" s="105">
-        <f t="shared" ref="D141:H141" si="25">D31*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D141:H156" si="4">IF(D31=1,1,D31*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="F141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="G141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
       <c r="H141" s="105">
-        <f t="shared" si="25"/>
-        <v>1.1199999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.4400000000000002</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -21720,24 +21693,24 @@
         <v>3</v>
       </c>
       <c r="D142" s="105">
-        <f t="shared" ref="D142:H142" si="26">D32*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="F142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="G142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="H142" s="105">
-        <f t="shared" si="26"/>
-        <v>2.387</v>
+        <f t="shared" si="4"/>
+        <v>3.0690000000000004</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -21745,24 +21718,24 @@
         <v>207</v>
       </c>
       <c r="D143" s="105">
-        <f t="shared" ref="D143:H143" si="27">D33*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="F143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="G143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
       <c r="H143" s="105">
-        <f t="shared" si="27"/>
-        <v>8.6310000000000002</v>
+        <f t="shared" si="4"/>
+        <v>11.097</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -21773,24 +21746,24 @@
         <v>7</v>
       </c>
       <c r="D144" s="105">
-        <f t="shared" ref="D144:H144" si="28">D34*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H144" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.25">
@@ -21798,24 +21771,24 @@
         <v>273</v>
       </c>
       <c r="D145" s="105">
-        <f t="shared" ref="D145:H145" si="29">D35*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="F145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="G145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
       <c r="H145" s="105">
-        <f t="shared" si="29"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="4"/>
+        <v>1.728</v>
       </c>
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.25">
@@ -21823,24 +21796,24 @@
         <v>3</v>
       </c>
       <c r="D146" s="105">
-        <f t="shared" ref="D146:H146" si="30">D36*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="F146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="G146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
       <c r="H146" s="105">
-        <f t="shared" si="30"/>
-        <v>3.262</v>
+        <f t="shared" si="4"/>
+        <v>4.194</v>
       </c>
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.25">
@@ -21848,24 +21821,24 @@
         <v>207</v>
       </c>
       <c r="D147" s="105">
-        <f t="shared" ref="D147:H147" si="31">D37*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="F147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="G147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
       <c r="H147" s="105">
-        <f t="shared" si="31"/>
-        <v>6.7759999999999998</v>
+        <f t="shared" si="4"/>
+        <v>8.7119999999999997</v>
       </c>
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.25">
@@ -21876,24 +21849,24 @@
         <v>7</v>
       </c>
       <c r="D148" s="105">
-        <f t="shared" ref="D148:H148" si="32">D38*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H148" s="105">
-        <f t="shared" si="32"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="2:8" x14ac:dyDescent="0.25">
@@ -21901,24 +21874,24 @@
         <v>273</v>
       </c>
       <c r="D149" s="105">
-        <f t="shared" ref="D149:H149" si="33">D39*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H149" s="105">
-        <f t="shared" si="33"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.25">
@@ -21926,24 +21899,24 @@
         <v>3</v>
       </c>
       <c r="D150" s="105">
-        <f t="shared" ref="D150:H150" si="34">D40*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="F150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="G150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="H150" s="105">
-        <f t="shared" si="34"/>
-        <v>1.8059999999999998</v>
+        <f t="shared" si="4"/>
+        <v>2.3220000000000001</v>
       </c>
     </row>
     <row r="151" spans="2:8" x14ac:dyDescent="0.25">
@@ -21951,24 +21924,24 @@
         <v>207</v>
       </c>
       <c r="D151" s="105">
-        <f t="shared" ref="D151:H151" si="35">D41*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="F151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="G151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
       <c r="H151" s="105">
-        <f t="shared" si="35"/>
-        <v>6.7410000000000005</v>
+        <f t="shared" si="4"/>
+        <v>8.6670000000000016</v>
       </c>
     </row>
     <row r="152" spans="2:8" x14ac:dyDescent="0.25">
@@ -21979,24 +21952,24 @@
         <v>7</v>
       </c>
       <c r="D152" s="105">
-        <f t="shared" ref="D152:H152" si="36">D42*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H152" s="105">
-        <f t="shared" si="36"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="2:8" x14ac:dyDescent="0.25">
@@ -22004,24 +21977,24 @@
         <v>273</v>
       </c>
       <c r="D153" s="105">
-        <f t="shared" ref="D153:H153" si="37">D43*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H153" s="105">
-        <f t="shared" si="37"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="2:8" x14ac:dyDescent="0.25">
@@ -22029,24 +22002,24 @@
         <v>3</v>
       </c>
       <c r="D154" s="105">
-        <f t="shared" ref="D154:H154" si="38">D44*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H154" s="105">
-        <f t="shared" si="38"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="2:8" x14ac:dyDescent="0.25">
@@ -22054,24 +22027,24 @@
         <v>207</v>
       </c>
       <c r="D155" s="105">
-        <f t="shared" ref="D155:H155" si="39">D45*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H155" s="105">
-        <f t="shared" si="39"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="2:8" x14ac:dyDescent="0.25">
@@ -22082,24 +22055,24 @@
         <v>7</v>
       </c>
       <c r="D156" s="105">
-        <f t="shared" ref="D156:H156" si="40">D46*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="E156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="F156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="G156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="H156" s="105">
-        <f t="shared" si="40"/>
-        <v>0.7</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="2:8" x14ac:dyDescent="0.25">
@@ -22107,24 +22080,24 @@
         <v>273</v>
       </c>
       <c r="D157" s="105">
-        <f t="shared" ref="D157:H157" si="41">D47*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D157:H163" si="5">IF(D47=1,1,D47*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="F157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="G157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="H157" s="105">
-        <f t="shared" si="41"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
     </row>
     <row r="158" spans="2:8" x14ac:dyDescent="0.25">
@@ -22132,24 +22105,24 @@
         <v>3</v>
       </c>
       <c r="D158" s="105">
-        <f t="shared" ref="D158:H158" si="42">D48*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="F158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="G158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="H158" s="105">
-        <f t="shared" si="42"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
     </row>
     <row r="159" spans="2:8" x14ac:dyDescent="0.25">
@@ -22157,24 +22130,24 @@
         <v>207</v>
       </c>
       <c r="D159" s="105">
-        <f t="shared" ref="D159:H159" si="43">D49*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="F159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="G159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="H159" s="105">
-        <f t="shared" si="43"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
     </row>
     <row r="160" spans="2:8" x14ac:dyDescent="0.25">
@@ -22185,24 +22158,24 @@
         <v>7</v>
       </c>
       <c r="D160" s="105">
-        <f t="shared" ref="D160:H160" si="44">D50*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="F160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="G160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="H160" s="105">
-        <f t="shared" si="44"/>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -22210,24 +22183,24 @@
         <v>273</v>
       </c>
       <c r="D161" s="105">
-        <f t="shared" ref="D161:H161" si="45">D51*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="F161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="G161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
       <c r="H161" s="105">
-        <f t="shared" si="45"/>
-        <v>1.1549999999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.4849999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -22235,24 +22208,24 @@
         <v>3</v>
       </c>
       <c r="D162" s="105">
-        <f t="shared" ref="D162:H162" si="46">D52*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="F162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="G162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
       <c r="H162" s="105">
-        <f t="shared" si="46"/>
-        <v>1.9109999999999998</v>
+        <f t="shared" si="5"/>
+        <v>2.4569999999999999</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -22260,24 +22233,24 @@
         <v>207</v>
       </c>
       <c r="D163" s="105">
-        <f t="shared" ref="D163:H163" si="47">D53*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="F163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="G163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
       <c r="H163" s="105">
-        <f t="shared" si="47"/>
-        <v>7.8470000000000004</v>
+        <f t="shared" si="5"/>
+        <v>10.089</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -22329,20 +22302,20 @@
         <v>275</v>
       </c>
       <c r="D167" s="105">
-        <f>D57*0.7</f>
-        <v>0.7</v>
+        <f>IF(D57=1,1,D57*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E167" s="105">
-        <f t="shared" ref="E167:G167" si="48">E57*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E167:G167" si="6">IF(E57=1,1,E57*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F167" s="105">
-        <f t="shared" si="48"/>
-        <v>0.7</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="G167" s="105">
-        <f t="shared" si="48"/>
-        <v>0.7</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="H167" s="92"/>
     </row>
@@ -22351,20 +22324,20 @@
         <v>268</v>
       </c>
       <c r="D168" s="105">
-        <f t="shared" ref="D168:G168" si="49">D58*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" ref="D168:G172" si="7">IF(D58=1,1,D58*0.9)</f>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G168" s="105">
-        <f t="shared" si="49"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H168" s="92"/>
     </row>
@@ -22376,20 +22349,20 @@
         <v>275</v>
       </c>
       <c r="D169" s="105">
-        <f t="shared" ref="D169:G169" si="50">D59*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="F169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="G169" s="105">
-        <f t="shared" si="50"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H169" s="92"/>
     </row>
@@ -22398,20 +22371,20 @@
         <v>268</v>
       </c>
       <c r="D170" s="105">
-        <f t="shared" ref="D170:G170" si="51">D60*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G170" s="105">
-        <f t="shared" si="51"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H170" s="92"/>
     </row>
@@ -22423,20 +22396,20 @@
         <v>275</v>
       </c>
       <c r="D171" s="105">
-        <f t="shared" ref="D171:G171" si="52">D61*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="E171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="F171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="G171" s="105">
-        <f t="shared" si="52"/>
-        <v>0.7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H171" s="92"/>
     </row>
@@ -22445,20 +22418,20 @@
         <v>268</v>
       </c>
       <c r="D172" s="105">
-        <f t="shared" ref="D172:G172" si="53">D62*0.7</f>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="E172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="F172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="G172" s="105">
-        <f t="shared" si="53"/>
-        <v>7.4725000000000001</v>
+        <f t="shared" si="7"/>
+        <v>9.6075000000000017</v>
       </c>
       <c r="H172" s="92"/>
     </row>
@@ -22513,20 +22486,20 @@
         <v>124</v>
       </c>
       <c r="D176" s="105">
-        <f>D66*0.7</f>
-        <v>0.7</v>
+        <f>IF(D66=1,1,D66*0.9)</f>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E176" s="105">
-        <f t="shared" ref="E176:G176" si="54">E66*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E176:G176" si="8">IF(E66=1,1,E66*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F176" s="105">
-        <f t="shared" si="54"/>
-        <v>0.7</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="G176" s="105">
-        <f t="shared" si="54"/>
-        <v>0.7</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="H176" s="92">
         <v>0.9</v>
@@ -22537,20 +22510,20 @@
         <v>127</v>
       </c>
       <c r="D177" s="105">
-        <f t="shared" ref="D177:G177" si="55">D67*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" ref="D177:G192" si="9">IF(D67=1,1,D67*0.9)</f>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G177" s="105">
-        <f t="shared" si="55"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H177" s="92">
         <v>0.9</v>
@@ -22561,20 +22534,20 @@
         <v>126</v>
       </c>
       <c r="D178" s="105">
-        <f t="shared" ref="D178:G178" si="56">D68*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G178" s="105">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H178" s="92">
         <v>0.9</v>
@@ -22585,20 +22558,20 @@
         <v>125</v>
       </c>
       <c r="D179" s="105">
-        <f t="shared" ref="D179:G179" si="57">D69*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G179" s="105">
-        <f t="shared" si="57"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H179" s="92">
         <v>0.9</v>
@@ -22612,20 +22585,20 @@
         <v>124</v>
       </c>
       <c r="D180" s="105">
-        <f t="shared" ref="D180:G180" si="58">D70*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G180" s="105">
-        <f t="shared" si="58"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H180" s="92">
         <v>0.9</v>
@@ -22636,20 +22609,20 @@
         <v>127</v>
       </c>
       <c r="D181" s="105">
-        <f t="shared" ref="D181:G181" si="59">D71*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G181" s="105">
-        <f t="shared" si="59"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H181" s="92">
         <v>0.9</v>
@@ -22660,20 +22633,20 @@
         <v>126</v>
       </c>
       <c r="D182" s="105">
-        <f t="shared" ref="D182:G182" si="60">D72*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G182" s="105">
-        <f t="shared" si="60"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H182" s="92">
         <v>0.9</v>
@@ -22684,20 +22657,20 @@
         <v>125</v>
       </c>
       <c r="D183" s="105">
-        <f t="shared" ref="D183:G183" si="61">D73*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G183" s="105">
-        <f t="shared" si="61"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H183" s="92">
         <v>0.9</v>
@@ -22711,20 +22684,20 @@
         <v>124</v>
       </c>
       <c r="D184" s="105">
-        <f t="shared" ref="D184:G184" si="62">D74*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G184" s="105">
-        <f t="shared" si="62"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H184" s="92">
         <v>0.9</v>
@@ -22735,20 +22708,20 @@
         <v>127</v>
       </c>
       <c r="D185" s="105">
-        <f t="shared" ref="D185:G185" si="63">D75*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G185" s="105">
-        <f t="shared" si="63"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H185" s="92">
         <v>0.9</v>
@@ -22759,20 +22732,20 @@
         <v>126</v>
       </c>
       <c r="D186" s="105">
-        <f t="shared" ref="D186:G186" si="64">D76*0.7</f>
-        <v>0.94499999999999995</v>
+        <f t="shared" si="9"/>
+        <v>1.2150000000000001</v>
       </c>
       <c r="E186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G186" s="105">
-        <f t="shared" si="64"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H186" s="92">
         <v>0.9</v>
@@ -22783,20 +22756,20 @@
         <v>125</v>
       </c>
       <c r="D187" s="105">
-        <f t="shared" ref="D187:G187" si="65">D77*0.7</f>
-        <v>3.78</v>
+        <f t="shared" si="9"/>
+        <v>4.8600000000000003</v>
       </c>
       <c r="E187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G187" s="105">
-        <f t="shared" si="65"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H187" s="92">
         <v>0.9</v>
@@ -22810,20 +22783,20 @@
         <v>124</v>
       </c>
       <c r="D188" s="105">
-        <f t="shared" ref="D188:G188" si="66">D78*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G188" s="105">
-        <f t="shared" si="66"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H188" s="92">
         <v>0.9</v>
@@ -22834,20 +22807,20 @@
         <v>127</v>
       </c>
       <c r="D189" s="105">
-        <f t="shared" ref="D189:G189" si="67">D79*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G189" s="105">
-        <f t="shared" si="67"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H189" s="92">
         <v>0.9</v>
@@ -22858,20 +22831,20 @@
         <v>126</v>
       </c>
       <c r="D190" s="105">
-        <f t="shared" ref="D190:G190" si="68">D80*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G190" s="105">
-        <f t="shared" si="68"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H190" s="92">
         <v>0.9</v>
@@ -22882,20 +22855,20 @@
         <v>125</v>
       </c>
       <c r="D191" s="105">
-        <f t="shared" ref="D191:G191" si="69">D81*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G191" s="105">
-        <f t="shared" si="69"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H191" s="92">
         <v>0.9</v>
@@ -22909,20 +22882,20 @@
         <v>124</v>
       </c>
       <c r="D192" s="105">
-        <f t="shared" ref="D192:G192" si="70">D82*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="E192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="G192" s="105">
-        <f t="shared" si="70"/>
-        <v>0.7</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="H192" s="92">
         <v>0.9</v>
@@ -22933,20 +22906,20 @@
         <v>127</v>
       </c>
       <c r="D193" s="105">
-        <f t="shared" ref="D193:G193" si="71">D83*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D193:G208" si="10">IF(D83=1,1,D83*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E193" s="105">
-        <f t="shared" si="71"/>
-        <v>1.5959999999999999</v>
+        <f t="shared" si="10"/>
+        <v>2.052</v>
       </c>
       <c r="F193" s="105">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G193" s="105">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H193" s="92">
         <v>0.9</v>
@@ -22957,20 +22930,20 @@
         <v>126</v>
       </c>
       <c r="D194" s="105">
-        <f t="shared" ref="D194:G194" si="72">D84*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E194" s="105">
-        <f t="shared" si="72"/>
-        <v>3.234</v>
+        <f t="shared" si="10"/>
+        <v>4.1580000000000004</v>
       </c>
       <c r="F194" s="105">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G194" s="105">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H194" s="92">
         <v>0.9</v>
@@ -22981,20 +22954,20 @@
         <v>125</v>
       </c>
       <c r="D195" s="105">
-        <f t="shared" ref="D195:G195" si="73">D85*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E195" s="105">
-        <f t="shared" si="73"/>
-        <v>7.3709999999999987</v>
+        <f t="shared" si="10"/>
+        <v>9.4770000000000003</v>
       </c>
       <c r="F195" s="105">
-        <f t="shared" si="73"/>
-        <v>1.0289999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.323</v>
       </c>
       <c r="G195" s="105">
-        <f t="shared" si="73"/>
-        <v>1.7989999999999997</v>
+        <f t="shared" si="10"/>
+        <v>2.3129999999999997</v>
       </c>
       <c r="H195" s="92">
         <v>0.9</v>
@@ -23008,20 +22981,20 @@
         <v>124</v>
       </c>
       <c r="D196" s="105">
-        <f t="shared" ref="D196:G196" si="74">D86*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G196" s="105">
-        <f t="shared" si="74"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H196" s="92">
         <v>0.9</v>
@@ -23032,20 +23005,20 @@
         <v>127</v>
       </c>
       <c r="D197" s="105">
-        <f t="shared" ref="D197:G197" si="75">D87*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E197" s="105">
-        <f t="shared" si="75"/>
-        <v>1.1619999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.494</v>
       </c>
       <c r="F197" s="105">
-        <f t="shared" si="75"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G197" s="105">
-        <f t="shared" si="75"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H197" s="92">
         <v>0.9</v>
@@ -23056,20 +23029,20 @@
         <v>126</v>
       </c>
       <c r="D198" s="105">
-        <f t="shared" ref="D198:G198" si="76">D88*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E198" s="105">
-        <f t="shared" si="76"/>
-        <v>1.75</v>
+        <f t="shared" si="10"/>
+        <v>2.25</v>
       </c>
       <c r="F198" s="105">
-        <f t="shared" si="76"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G198" s="105">
-        <f t="shared" si="76"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H198" s="92">
         <v>0.9</v>
@@ -23080,20 +23053,20 @@
         <v>125</v>
       </c>
       <c r="D199" s="105">
-        <f t="shared" ref="D199:G199" si="77">D89*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E199" s="105">
-        <f t="shared" si="77"/>
-        <v>10.478999999999999</v>
+        <f t="shared" si="10"/>
+        <v>13.473000000000001</v>
       </c>
       <c r="F199" s="105">
-        <f t="shared" si="77"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.728</v>
       </c>
       <c r="G199" s="105">
-        <f t="shared" si="77"/>
-        <v>1.3439999999999999</v>
+        <f t="shared" si="10"/>
+        <v>1.728</v>
       </c>
       <c r="H199" s="92">
         <v>0.9</v>
@@ -23107,20 +23080,20 @@
         <v>124</v>
       </c>
       <c r="D200" s="105">
-        <f t="shared" ref="D200:G200" si="78">D90*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G200" s="105">
-        <f t="shared" si="78"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H200" s="92">
         <v>0.9</v>
@@ -23131,20 +23104,20 @@
         <v>127</v>
       </c>
       <c r="D201" s="105">
-        <f t="shared" ref="D201:G201" si="79">D91*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E201" s="105">
-        <f t="shared" si="79"/>
-        <v>1.036</v>
+        <f t="shared" si="10"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F201" s="105">
-        <f t="shared" si="79"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G201" s="105">
-        <f t="shared" si="79"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H201" s="92">
         <v>0.9</v>
@@ -23155,20 +23128,20 @@
         <v>126</v>
       </c>
       <c r="D202" s="105">
-        <f t="shared" ref="D202:G202" si="80">D92*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E202" s="105">
-        <f t="shared" si="80"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="10"/>
+        <v>2.556</v>
       </c>
       <c r="F202" s="105">
-        <f t="shared" si="80"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G202" s="105">
-        <f t="shared" si="80"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H202" s="92">
         <v>0.9</v>
@@ -23179,20 +23152,20 @@
         <v>125</v>
       </c>
       <c r="D203" s="105">
-        <f t="shared" ref="D203:G203" si="81">D93*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E203" s="105">
-        <f t="shared" si="81"/>
-        <v>10.08</v>
+        <f t="shared" si="10"/>
+        <v>12.96</v>
       </c>
       <c r="F203" s="105">
-        <f t="shared" si="81"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G203" s="105">
-        <f t="shared" si="81"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H203" s="92">
         <v>0.9</v>
@@ -23206,20 +23179,20 @@
         <v>124</v>
       </c>
       <c r="D204" s="105">
-        <f t="shared" ref="D204:G204" si="82">D94*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G204" s="105">
-        <f t="shared" si="82"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H204" s="92">
         <v>0.9</v>
@@ -23230,20 +23203,20 @@
         <v>127</v>
       </c>
       <c r="D205" s="105">
-        <f t="shared" ref="D205:G205" si="83">D95*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E205" s="105">
-        <f t="shared" si="83"/>
-        <v>1.036</v>
+        <f t="shared" si="10"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F205" s="105">
-        <f t="shared" si="83"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G205" s="105">
-        <f t="shared" si="83"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H205" s="92">
         <v>0.9</v>
@@ -23254,20 +23227,20 @@
         <v>126</v>
       </c>
       <c r="D206" s="105">
-        <f t="shared" ref="D206:G206" si="84">D96*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E206" s="105">
-        <f t="shared" si="84"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="10"/>
+        <v>2.556</v>
       </c>
       <c r="F206" s="105">
-        <f t="shared" si="84"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G206" s="105">
-        <f t="shared" si="84"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H206" s="92">
         <v>0.9</v>
@@ -23278,20 +23251,20 @@
         <v>125</v>
       </c>
       <c r="D207" s="105">
-        <f t="shared" ref="D207:G207" si="85">D97*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E207" s="105">
-        <f t="shared" si="85"/>
-        <v>10.08</v>
+        <f t="shared" si="10"/>
+        <v>12.96</v>
       </c>
       <c r="F207" s="105">
-        <f t="shared" si="85"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G207" s="105">
-        <f t="shared" si="85"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="10"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H207" s="92">
         <v>0.9</v>
@@ -23305,20 +23278,20 @@
         <v>124</v>
       </c>
       <c r="D208" s="105">
-        <f t="shared" ref="D208:G208" si="86">D98*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="E208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="F208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="G208" s="105">
-        <f t="shared" si="86"/>
-        <v>0.7</v>
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
       <c r="H208" s="92">
         <v>0.9</v>
@@ -23329,20 +23302,20 @@
         <v>127</v>
       </c>
       <c r="D209" s="105">
-        <f t="shared" ref="D209:G209" si="87">D99*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="D209:G211" si="11">IF(D99=1,1,D99*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E209" s="105">
-        <f t="shared" si="87"/>
-        <v>1.036</v>
+        <f t="shared" si="11"/>
+        <v>1.3320000000000001</v>
       </c>
       <c r="F209" s="105">
-        <f t="shared" si="87"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="G209" s="105">
-        <f t="shared" si="87"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="H209" s="92">
         <v>0.9</v>
@@ -23353,20 +23326,20 @@
         <v>126</v>
       </c>
       <c r="D210" s="105">
-        <f t="shared" ref="D210:G210" si="88">D100*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="E210" s="105">
-        <f t="shared" si="88"/>
-        <v>1.9879999999999998</v>
+        <f t="shared" si="11"/>
+        <v>2.556</v>
       </c>
       <c r="F210" s="105">
-        <f t="shared" si="88"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="G210" s="105">
-        <f t="shared" si="88"/>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="H210" s="92">
         <v>0.9</v>
@@ -23377,20 +23350,20 @@
         <v>125</v>
       </c>
       <c r="D211" s="105">
-        <f t="shared" ref="D211:G211" si="89">D101*0.7</f>
-        <v>0.7</v>
+        <f t="shared" si="11"/>
+        <v>1</v>
       </c>
       <c r="E211" s="105">
-        <f t="shared" si="89"/>
-        <v>10.08</v>
+        <f t="shared" si="11"/>
+        <v>12.96</v>
       </c>
       <c r="F211" s="105">
-        <f t="shared" si="89"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="11"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="G211" s="105">
-        <f t="shared" si="89"/>
-        <v>2.5829999999999997</v>
+        <f t="shared" si="11"/>
+        <v>3.3210000000000002</v>
       </c>
       <c r="H211" s="92">
         <v>0.9</v>
@@ -23440,20 +23413,20 @@
         <v>124</v>
       </c>
       <c r="D215" s="105">
-        <f>D105*0.7</f>
-        <v>0.7</v>
+        <f>IF(D105=1,1,D105*0.9)</f>
+        <v>1</v>
       </c>
       <c r="E215" s="105">
-        <f t="shared" ref="E215:G215" si="90">E105*0.7</f>
-        <v>0.7</v>
+        <f t="shared" ref="E215:G215" si="12">IF(E105=1,1,E105*0.9)</f>
+        <v>1</v>
       </c>
       <c r="F215" s="105">
-        <f t="shared" si="90"/>
-        <v>0.7</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="G215" s="105">
-        <f t="shared" si="90"/>
-        <v>0.7</v>
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="H215" s="92">
         <v>0.9</v>
@@ -23464,20 +23437,20 @@
         <v>127</v>
       </c>
       <c r="D216" s="105">
-        <f t="shared" ref="D216:G216" si="91">D106*0.7</f>
-        <v>0.8819999999999999</v>
+        <f t="shared" ref="D216:G218" si="13">IF(D106=1,1,D106*0.9)</f>
+        <v>1.1340000000000001</v>
       </c>
       <c r="E216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.8819999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.1340000000000001</v>
       </c>
       <c r="F216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="G216" s="105">
-        <f t="shared" si="91"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="H216" s="92">
         <v>0.9</v>
@@ -23488,20 +23461,20 @@
         <v>126</v>
       </c>
       <c r="D217" s="105">
-        <f t="shared" ref="D217:G217" si="92">D107*0.7</f>
-        <v>1.1759999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.512</v>
       </c>
       <c r="E217" s="105">
-        <f t="shared" si="92"/>
-        <v>1.1759999999999999</v>
+        <f t="shared" si="13"/>
+        <v>1.512</v>
       </c>
       <c r="F217" s="105">
-        <f t="shared" si="92"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="G217" s="105">
-        <f t="shared" si="92"/>
-        <v>0.7</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="H217" s="92">
         <v>0.9</v>
@@ -23512,20 +23485,20 @@
         <v>125</v>
       </c>
       <c r="D218" s="105">
-        <f t="shared" ref="D218:G218" si="93">D108*0.7</f>
-        <v>1.8549999999999998</v>
+        <f t="shared" si="13"/>
+        <v>2.3849999999999998</v>
       </c>
       <c r="E218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.8549999999999998</v>
+        <f t="shared" si="13"/>
+        <v>2.3849999999999998</v>
       </c>
       <c r="F218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.4489999999999998</v>
+        <f t="shared" si="13"/>
+        <v>1.863</v>
       </c>
       <c r="G218" s="105">
-        <f t="shared" si="93"/>
-        <v>1.4489999999999998</v>
+        <f t="shared" si="13"/>
+        <v>1.863</v>
       </c>
       <c r="H218" s="92">
         <v>0.9</v>
@@ -23586,24 +23559,24 @@
         <v>7</v>
       </c>
       <c r="D223" s="105">
-        <f>D3*1.2</f>
-        <v>1.2</v>
+        <f>IF(D3=1,1,D3*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E223" s="105">
-        <f t="shared" ref="E223:H223" si="94">E3*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E223:H223" si="14">IF(E3=1,1,E3*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="G223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="H223" s="105">
-        <f t="shared" si="94"/>
-        <v>1.2</v>
+        <f t="shared" si="14"/>
+        <v>1</v>
       </c>
       <c r="I223" s="92"/>
     </row>
@@ -23612,24 +23585,24 @@
         <v>273</v>
       </c>
       <c r="D224" s="105">
-        <f t="shared" ref="D224:H224" si="95">D4*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D224:H239" si="15">IF(D4=1,1,D4*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="F224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="G224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="H224" s="105">
-        <f t="shared" si="95"/>
-        <v>2.004</v>
+        <f t="shared" si="15"/>
+        <v>1.837</v>
       </c>
       <c r="I224" s="92"/>
     </row>
@@ -23638,24 +23611,24 @@
         <v>274</v>
       </c>
       <c r="D225" s="105">
-        <f t="shared" ref="D225:H225" si="96">D5*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="F225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="G225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="H225" s="105">
-        <f t="shared" si="96"/>
-        <v>2.8559999999999999</v>
+        <f t="shared" si="15"/>
+        <v>2.6179999999999999</v>
       </c>
       <c r="I225" s="92"/>
     </row>
@@ -23664,24 +23637,24 @@
         <v>272</v>
       </c>
       <c r="D226" s="105">
-        <f t="shared" ref="D226:H226" si="97">D6*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="F226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="G226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="H226" s="105">
-        <f t="shared" si="97"/>
-        <v>7.5960000000000001</v>
+        <f t="shared" si="15"/>
+        <v>6.963000000000001</v>
       </c>
       <c r="I226" s="92"/>
     </row>
@@ -23693,24 +23666,24 @@
         <v>7</v>
       </c>
       <c r="D227" s="105">
-        <f t="shared" ref="D227:H227" si="98">D7*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H227" s="105">
-        <f t="shared" si="98"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I227" s="92"/>
     </row>
@@ -23719,24 +23692,24 @@
         <v>273</v>
       </c>
       <c r="D228" s="105">
-        <f t="shared" ref="D228:H228" si="99">D8*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="F228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="G228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="H228" s="105">
-        <f t="shared" si="99"/>
-        <v>1.8599999999999999</v>
+        <f t="shared" si="15"/>
+        <v>1.7050000000000003</v>
       </c>
       <c r="I228" s="92"/>
     </row>
@@ -23745,24 +23718,24 @@
         <v>274</v>
       </c>
       <c r="D229" s="105">
-        <f t="shared" ref="D229:H229" si="100">D9*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="F229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="G229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="H229" s="105">
-        <f t="shared" si="100"/>
-        <v>2.6160000000000001</v>
+        <f t="shared" si="15"/>
+        <v>2.3980000000000006</v>
       </c>
       <c r="I229" s="92"/>
     </row>
@@ -23771,24 +23744,24 @@
         <v>272</v>
       </c>
       <c r="D230" s="105">
-        <f t="shared" ref="D230:H230" si="101">D10*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="F230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="G230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="H230" s="105">
-        <f t="shared" si="101"/>
-        <v>7.6679999999999993</v>
+        <f t="shared" si="15"/>
+        <v>7.0289999999999999</v>
       </c>
       <c r="I230" s="92"/>
     </row>
@@ -23800,24 +23773,24 @@
         <v>7</v>
       </c>
       <c r="D231" s="105">
-        <f t="shared" ref="D231:H231" si="102">D11*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H231" s="105">
-        <f t="shared" si="102"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I231" s="92"/>
     </row>
@@ -23826,24 +23799,24 @@
         <v>273</v>
       </c>
       <c r="D232" s="105">
-        <f t="shared" ref="D232:H232" si="103">D12*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H232" s="105">
-        <f t="shared" si="103"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I232" s="92"/>
     </row>
@@ -23852,24 +23825,24 @@
         <v>274</v>
       </c>
       <c r="D233" s="105">
-        <f t="shared" ref="D233:H233" si="104">D13*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="F233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="G233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="H233" s="105">
-        <f t="shared" si="104"/>
-        <v>3.3479999999999999</v>
+        <f t="shared" si="15"/>
+        <v>3.0690000000000004</v>
       </c>
       <c r="I233" s="92"/>
     </row>
@@ -23878,24 +23851,24 @@
         <v>272</v>
       </c>
       <c r="D234" s="105">
-        <f t="shared" ref="D234:H234" si="105">D14*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="F234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="G234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="H234" s="105">
-        <f t="shared" si="105"/>
-        <v>7.2119999999999997</v>
+        <f t="shared" si="15"/>
+        <v>6.6110000000000007</v>
       </c>
       <c r="I234" s="92"/>
     </row>
@@ -23907,24 +23880,24 @@
         <v>7</v>
       </c>
       <c r="D235" s="105">
-        <f t="shared" ref="D235:H235" si="106">D15*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H235" s="105">
-        <f t="shared" si="106"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I235" s="92"/>
     </row>
@@ -23933,24 +23906,24 @@
         <v>273</v>
       </c>
       <c r="D236" s="105">
-        <f t="shared" ref="D236:H236" si="107">D16*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H236" s="105">
-        <f t="shared" si="107"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I236" s="92"/>
     </row>
@@ -23959,24 +23932,24 @@
         <v>274</v>
       </c>
       <c r="D237" s="105">
-        <f t="shared" ref="D237:H237" si="108">D17*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H237" s="105">
-        <f t="shared" si="108"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I237" s="92"/>
     </row>
@@ -23985,24 +23958,24 @@
         <v>272</v>
       </c>
       <c r="D238" s="105">
-        <f t="shared" ref="D238:H238" si="109">D18*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H238" s="105">
-        <f t="shared" si="109"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I238" s="92"/>
     </row>
@@ -24014,24 +23987,24 @@
         <v>7</v>
       </c>
       <c r="D239" s="105">
-        <f t="shared" ref="D239:H239" si="110">D19*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="E239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="F239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="G239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="H239" s="105">
-        <f t="shared" si="110"/>
-        <v>1.2</v>
+        <f t="shared" si="15"/>
+        <v>1</v>
       </c>
       <c r="I239" s="92"/>
     </row>
@@ -24040,24 +24013,24 @@
         <v>273</v>
       </c>
       <c r="D240" s="105">
-        <f t="shared" ref="D240:H240" si="111">D20*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D240:H246" si="16">IF(D20=1,1,D20*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H240" s="105">
-        <f t="shared" si="111"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I240" s="92"/>
     </row>
@@ -24066,24 +24039,24 @@
         <v>274</v>
       </c>
       <c r="D241" s="105">
-        <f t="shared" ref="D241:H241" si="112">D21*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="F241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="G241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="H241" s="105">
-        <f t="shared" si="112"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="I241" s="92"/>
     </row>
@@ -24092,24 +24065,24 @@
         <v>272</v>
       </c>
       <c r="D242" s="105">
-        <f t="shared" ref="D242:H242" si="113">D22*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="F242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="G242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="H242" s="105">
-        <f t="shared" si="113"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="I242" s="92"/>
     </row>
@@ -24121,24 +24094,24 @@
         <v>7</v>
       </c>
       <c r="D243" s="105">
-        <f t="shared" ref="D243:H243" si="114">D23*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H243" s="105">
-        <f t="shared" si="114"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I243" s="92"/>
     </row>
@@ -24147,24 +24120,24 @@
         <v>273</v>
       </c>
       <c r="D244" s="105">
-        <f t="shared" ref="D244:H244" si="115">D24*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="F244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="G244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="H244" s="105">
-        <f t="shared" si="115"/>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="I244" s="92"/>
     </row>
@@ -24173,24 +24146,24 @@
         <v>274</v>
       </c>
       <c r="D245" s="105">
-        <f t="shared" ref="D245:H245" si="116">D25*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="F245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="G245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="H245" s="105">
-        <f t="shared" si="116"/>
-        <v>2.2320000000000002</v>
+        <f t="shared" si="16"/>
+        <v>2.0460000000000003</v>
       </c>
       <c r="I245" s="92"/>
     </row>
@@ -24199,24 +24172,24 @@
         <v>272</v>
       </c>
       <c r="D246" s="105">
-        <f t="shared" ref="D246:H246" si="117">D26*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
       <c r="E246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="F246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="G246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="H246" s="105">
-        <f t="shared" si="117"/>
-        <v>3.6119999999999997</v>
+        <f t="shared" si="16"/>
+        <v>3.3109999999999999</v>
       </c>
       <c r="I246" s="92"/>
     </row>
@@ -24269,24 +24242,24 @@
         <v>7</v>
       </c>
       <c r="D250" s="105">
-        <f>D30*1.2</f>
-        <v>1.2</v>
+        <f>IF(D30=1,1,D30*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E250" s="105">
-        <f t="shared" ref="E250:H250" si="118">E30*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E250:H250" si="17">IF(E30=1,1,E30*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="G250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="H250" s="105">
-        <f t="shared" si="118"/>
-        <v>1.2</v>
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="I250" s="94"/>
     </row>
@@ -24295,24 +24268,24 @@
         <v>273</v>
       </c>
       <c r="D251" s="105">
-        <f t="shared" ref="D251:H251" si="119">D31*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D251:H266" si="18">IF(D31=1,1,D31*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="F251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="G251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="H251" s="105">
-        <f t="shared" si="119"/>
-        <v>1.92</v>
+        <f t="shared" si="18"/>
+        <v>1.7600000000000002</v>
       </c>
       <c r="I251" s="92"/>
     </row>
@@ -24321,24 +24294,24 @@
         <v>3</v>
       </c>
       <c r="D252" s="105">
-        <f t="shared" ref="D252:H252" si="120">D32*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="F252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="G252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="H252" s="105">
-        <f t="shared" si="120"/>
-        <v>4.0919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>3.7510000000000003</v>
       </c>
       <c r="I252" s="92"/>
     </row>
@@ -24347,24 +24320,24 @@
         <v>207</v>
       </c>
       <c r="D253" s="105">
-        <f t="shared" ref="D253:H253" si="121">D33*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="F253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="G253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="H253" s="105">
-        <f t="shared" si="121"/>
-        <v>14.795999999999999</v>
+        <f t="shared" si="18"/>
+        <v>13.563000000000001</v>
       </c>
       <c r="I253" s="92"/>
     </row>
@@ -24376,24 +24349,24 @@
         <v>7</v>
       </c>
       <c r="D254" s="105">
-        <f t="shared" ref="D254:H254" si="122">D34*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H254" s="105">
-        <f t="shared" si="122"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I254" s="92"/>
     </row>
@@ -24402,24 +24375,24 @@
         <v>273</v>
       </c>
       <c r="D255" s="105">
-        <f t="shared" ref="D255:H255" si="123">D35*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="F255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="G255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="H255" s="105">
-        <f t="shared" si="123"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="18"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="I255" s="92"/>
     </row>
@@ -24428,24 +24401,24 @@
         <v>3</v>
       </c>
       <c r="D256" s="105">
-        <f t="shared" ref="D256:H256" si="124">D36*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="F256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="G256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="H256" s="105">
-        <f t="shared" si="124"/>
-        <v>5.5919999999999996</v>
+        <f t="shared" si="18"/>
+        <v>5.1260000000000003</v>
       </c>
       <c r="I256" s="92"/>
     </row>
@@ -24454,24 +24427,24 @@
         <v>207</v>
       </c>
       <c r="D257" s="105">
-        <f t="shared" ref="D257:H257" si="125">D37*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="F257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="G257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="H257" s="105">
-        <f t="shared" si="125"/>
-        <v>11.616</v>
+        <f t="shared" si="18"/>
+        <v>10.648</v>
       </c>
       <c r="I257" s="92"/>
     </row>
@@ -24483,24 +24456,24 @@
         <v>7</v>
       </c>
       <c r="D258" s="105">
-        <f t="shared" ref="D258:H258" si="126">D38*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H258" s="105">
-        <f t="shared" si="126"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I258" s="92"/>
     </row>
@@ -24509,24 +24482,24 @@
         <v>273</v>
       </c>
       <c r="D259" s="105">
-        <f t="shared" ref="D259:H259" si="127">D39*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H259" s="105">
-        <f t="shared" si="127"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I259" s="92"/>
     </row>
@@ -24535,24 +24508,24 @@
         <v>3</v>
       </c>
       <c r="D260" s="105">
-        <f t="shared" ref="D260:H260" si="128">D40*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="F260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="G260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="H260" s="105">
-        <f t="shared" si="128"/>
-        <v>3.0960000000000001</v>
+        <f t="shared" si="18"/>
+        <v>2.8380000000000005</v>
       </c>
       <c r="I260" s="92"/>
     </row>
@@ -24561,24 +24534,24 @@
         <v>207</v>
       </c>
       <c r="D261" s="105">
-        <f t="shared" ref="D261:H261" si="129">D41*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="F261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="G261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="H261" s="105">
-        <f t="shared" si="129"/>
-        <v>11.556000000000001</v>
+        <f t="shared" si="18"/>
+        <v>10.593000000000002</v>
       </c>
       <c r="I261" s="92"/>
     </row>
@@ -24590,24 +24563,24 @@
         <v>7</v>
       </c>
       <c r="D262" s="105">
-        <f t="shared" ref="D262:H262" si="130">D42*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H262" s="105">
-        <f t="shared" si="130"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I262" s="92"/>
     </row>
@@ -24616,24 +24589,24 @@
         <v>273</v>
       </c>
       <c r="D263" s="105">
-        <f t="shared" ref="D263:H263" si="131">D43*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H263" s="105">
-        <f t="shared" si="131"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I263" s="92"/>
     </row>
@@ -24642,24 +24615,24 @@
         <v>3</v>
       </c>
       <c r="D264" s="105">
-        <f t="shared" ref="D264:H264" si="132">D44*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H264" s="105">
-        <f t="shared" si="132"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I264" s="92"/>
     </row>
@@ -24668,24 +24641,24 @@
         <v>207</v>
       </c>
       <c r="D265" s="105">
-        <f t="shared" ref="D265:H265" si="133">D45*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H265" s="105">
-        <f t="shared" si="133"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I265" s="92"/>
     </row>
@@ -24697,24 +24670,24 @@
         <v>7</v>
       </c>
       <c r="D266" s="105">
-        <f t="shared" ref="D266:H266" si="134">D46*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="E266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="F266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="G266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="H266" s="105">
-        <f t="shared" si="134"/>
-        <v>1.2</v>
+        <f t="shared" si="18"/>
+        <v>1</v>
       </c>
       <c r="I266" s="92"/>
     </row>
@@ -24723,24 +24696,24 @@
         <v>273</v>
       </c>
       <c r="D267" s="105">
-        <f t="shared" ref="D267:H267" si="135">D47*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D267:H273" si="19">IF(D47=1,1,D47*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="F267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="G267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="H267" s="105">
-        <f t="shared" si="135"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="I267" s="92"/>
     </row>
@@ -24749,24 +24722,24 @@
         <v>3</v>
       </c>
       <c r="D268" s="105">
-        <f t="shared" ref="D268:H268" si="136">D48*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="F268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="G268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="H268" s="105">
-        <f t="shared" si="136"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="I268" s="92"/>
     </row>
@@ -24775,24 +24748,24 @@
         <v>207</v>
       </c>
       <c r="D269" s="105">
-        <f t="shared" ref="D269:H269" si="137">D49*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="F269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="G269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="H269" s="105">
-        <f t="shared" si="137"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="I269" s="92"/>
     </row>
@@ -24804,24 +24777,24 @@
         <v>7</v>
       </c>
       <c r="D270" s="105">
-        <f t="shared" ref="D270:H270" si="138">D50*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="F270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="G270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="H270" s="105">
-        <f t="shared" si="138"/>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="I270" s="92"/>
     </row>
@@ -24830,24 +24803,24 @@
         <v>273</v>
       </c>
       <c r="D271" s="105">
-        <f t="shared" ref="D271:H271" si="139">D51*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="F271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="G271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="H271" s="105">
-        <f t="shared" si="139"/>
-        <v>1.9799999999999998</v>
+        <f t="shared" si="19"/>
+        <v>1.8149999999999999</v>
       </c>
       <c r="I271" s="92"/>
     </row>
@@ -24856,24 +24829,24 @@
         <v>3</v>
       </c>
       <c r="D272" s="105">
-        <f t="shared" ref="D272:H272" si="140">D52*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="F272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="G272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="H272" s="105">
-        <f t="shared" si="140"/>
-        <v>3.2759999999999998</v>
+        <f t="shared" si="19"/>
+        <v>3.0030000000000001</v>
       </c>
       <c r="I272" s="92"/>
     </row>
@@ -24882,24 +24855,24 @@
         <v>207</v>
       </c>
       <c r="D273" s="105">
-        <f t="shared" ref="D273:H273" si="141">D53*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="19"/>
+        <v>1</v>
       </c>
       <c r="E273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="F273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="G273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="H273" s="105">
-        <f t="shared" si="141"/>
-        <v>13.452</v>
+        <f t="shared" si="19"/>
+        <v>12.331000000000001</v>
       </c>
       <c r="I273" s="92"/>
     </row>
@@ -24953,20 +24926,20 @@
         <v>275</v>
       </c>
       <c r="D277" s="105">
-        <f>D57*1.2</f>
-        <v>1.2</v>
+        <f>IF(D57=1,1,D57*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E277" s="105">
-        <f t="shared" ref="E277:G277" si="142">E57*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E277:G277" si="20">IF(E57=1,1,E57*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F277" s="105">
-        <f t="shared" si="142"/>
-        <v>1.2</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="G277" s="105">
-        <f t="shared" si="142"/>
-        <v>1.2</v>
+        <f t="shared" si="20"/>
+        <v>1</v>
       </c>
       <c r="H277" s="92"/>
     </row>
@@ -24975,20 +24948,20 @@
         <v>268</v>
       </c>
       <c r="D278" s="105">
-        <f t="shared" ref="D278:G278" si="143">D58*1.2</f>
-        <v>12.81</v>
+        <f t="shared" ref="D278:G282" si="21">IF(D58=1,1,D58*1.1)</f>
+        <v>11.742500000000001</v>
       </c>
       <c r="E278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G278" s="105">
-        <f t="shared" si="143"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H278" s="92"/>
     </row>
@@ -25000,20 +24973,20 @@
         <v>275</v>
       </c>
       <c r="D279" s="105">
-        <f t="shared" ref="D279:G279" si="144">D59*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="E279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="F279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="G279" s="105">
-        <f t="shared" si="144"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="H279" s="92"/>
     </row>
@@ -25022,20 +24995,20 @@
         <v>268</v>
       </c>
       <c r="D280" s="105">
-        <f t="shared" ref="D280:G280" si="145">D60*1.2</f>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="E280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G280" s="105">
-        <f t="shared" si="145"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H280" s="92"/>
     </row>
@@ -25047,20 +25020,20 @@
         <v>275</v>
       </c>
       <c r="D281" s="105">
-        <f t="shared" ref="D281:G281" si="146">D61*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="E281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="F281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="G281" s="105">
-        <f t="shared" si="146"/>
-        <v>1.2</v>
+        <f t="shared" si="21"/>
+        <v>1</v>
       </c>
       <c r="H281" s="92"/>
     </row>
@@ -25069,20 +25042,20 @@
         <v>268</v>
       </c>
       <c r="D282" s="105">
-        <f t="shared" ref="D282:G282" si="147">D62*1.2</f>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="E282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="F282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="G282" s="105">
-        <f t="shared" si="147"/>
-        <v>12.81</v>
+        <f t="shared" si="21"/>
+        <v>11.742500000000001</v>
       </c>
       <c r="H282" s="92"/>
     </row>
@@ -25139,20 +25112,20 @@
         <v>124</v>
       </c>
       <c r="D286" s="105">
-        <f>D66*1.2</f>
-        <v>1.2</v>
+        <f>IF(D66=1,1,D66*1.1)</f>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E286" s="105">
-        <f t="shared" ref="E286:G286" si="148">E66*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E286:G286" si="22">IF(E66=1,1,E66*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F286" s="105">
-        <f t="shared" si="148"/>
-        <v>1.2</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="G286" s="105">
-        <f t="shared" si="148"/>
-        <v>1.2</v>
+        <f t="shared" si="22"/>
+        <v>1</v>
       </c>
       <c r="H286" s="92">
         <v>1.05</v>
@@ -25164,20 +25137,20 @@
         <v>127</v>
       </c>
       <c r="D287" s="105">
-        <f t="shared" ref="D287:G287" si="149">D67*1.2</f>
-        <v>1.62</v>
+        <f t="shared" ref="D287:G302" si="23">IF(D67=1,1,D67*1.1)</f>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G287" s="105">
-        <f t="shared" si="149"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H287" s="92">
         <v>1.05</v>
@@ -25189,20 +25162,20 @@
         <v>126</v>
       </c>
       <c r="D288" s="105">
-        <f t="shared" ref="D288:G288" si="150">D68*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G288" s="105">
-        <f t="shared" si="150"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H288" s="92">
         <v>1.05</v>
@@ -25214,20 +25187,20 @@
         <v>125</v>
       </c>
       <c r="D289" s="105">
-        <f t="shared" ref="D289:G289" si="151">D69*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G289" s="105">
-        <f t="shared" si="151"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H289" s="92">
         <v>1.05</v>
@@ -25242,20 +25215,20 @@
         <v>124</v>
       </c>
       <c r="D290" s="105">
-        <f t="shared" ref="D290:G290" si="152">D70*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G290" s="105">
-        <f t="shared" si="152"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H290" s="92">
         <v>1.05</v>
@@ -25267,20 +25240,20 @@
         <v>127</v>
       </c>
       <c r="D291" s="105">
-        <f t="shared" ref="D291:G291" si="153">D71*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G291" s="105">
-        <f t="shared" si="153"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H291" s="92">
         <v>1.05</v>
@@ -25292,20 +25265,20 @@
         <v>126</v>
       </c>
       <c r="D292" s="105">
-        <f t="shared" ref="D292:G292" si="154">D72*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G292" s="105">
-        <f t="shared" si="154"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H292" s="92">
         <v>1.05</v>
@@ -25317,20 +25290,20 @@
         <v>125</v>
       </c>
       <c r="D293" s="105">
-        <f t="shared" ref="D293:G293" si="155">D73*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G293" s="105">
-        <f t="shared" si="155"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H293" s="92">
         <v>1.05</v>
@@ -25345,20 +25318,20 @@
         <v>124</v>
       </c>
       <c r="D294" s="105">
-        <f t="shared" ref="D294:G294" si="156">D74*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G294" s="105">
-        <f t="shared" si="156"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H294" s="92">
         <v>1.05</v>
@@ -25370,20 +25343,20 @@
         <v>127</v>
       </c>
       <c r="D295" s="105">
-        <f t="shared" ref="D295:G295" si="157">D75*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G295" s="105">
-        <f t="shared" si="157"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H295" s="92">
         <v>1.05</v>
@@ -25395,20 +25368,20 @@
         <v>126</v>
       </c>
       <c r="D296" s="105">
-        <f t="shared" ref="D296:G296" si="158">D76*1.2</f>
-        <v>1.62</v>
+        <f t="shared" si="23"/>
+        <v>1.4850000000000003</v>
       </c>
       <c r="E296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G296" s="105">
-        <f t="shared" si="158"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H296" s="92">
         <v>1.05</v>
@@ -25420,20 +25393,20 @@
         <v>125</v>
       </c>
       <c r="D297" s="105">
-        <f t="shared" ref="D297:G297" si="159">D77*1.2</f>
-        <v>6.48</v>
+        <f t="shared" si="23"/>
+        <v>5.9400000000000013</v>
       </c>
       <c r="E297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G297" s="105">
-        <f t="shared" si="159"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H297" s="92">
         <v>1.05</v>
@@ -25448,20 +25421,20 @@
         <v>124</v>
       </c>
       <c r="D298" s="105">
-        <f t="shared" ref="D298:G298" si="160">D78*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G298" s="105">
-        <f t="shared" si="160"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H298" s="92">
         <v>1.05</v>
@@ -25473,20 +25446,20 @@
         <v>127</v>
       </c>
       <c r="D299" s="105">
-        <f t="shared" ref="D299:G299" si="161">D79*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G299" s="105">
-        <f t="shared" si="161"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H299" s="92">
         <v>1.05</v>
@@ -25498,20 +25471,20 @@
         <v>126</v>
       </c>
       <c r="D300" s="105">
-        <f t="shared" ref="D300:G300" si="162">D80*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G300" s="105">
-        <f t="shared" si="162"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H300" s="92">
         <v>1.05</v>
@@ -25523,20 +25496,20 @@
         <v>125</v>
       </c>
       <c r="D301" s="105">
-        <f t="shared" ref="D301:G301" si="163">D81*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G301" s="105">
-        <f t="shared" si="163"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H301" s="92">
         <v>1.05</v>
@@ -25551,20 +25524,20 @@
         <v>124</v>
       </c>
       <c r="D302" s="105">
-        <f t="shared" ref="D302:G302" si="164">D82*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="E302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="F302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="G302" s="105">
-        <f t="shared" si="164"/>
-        <v>1.2</v>
+        <f t="shared" si="23"/>
+        <v>1</v>
       </c>
       <c r="H302" s="92">
         <v>1.05</v>
@@ -25576,20 +25549,20 @@
         <v>127</v>
       </c>
       <c r="D303" s="105">
-        <f t="shared" ref="D303:G303" si="165">D83*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D303:G318" si="24">IF(D83=1,1,D83*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E303" s="105">
-        <f t="shared" si="165"/>
-        <v>2.7359999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.508</v>
       </c>
       <c r="F303" s="105">
-        <f t="shared" si="165"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G303" s="105">
-        <f t="shared" si="165"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H303" s="92">
         <v>1.05</v>
@@ -25601,20 +25574,20 @@
         <v>126</v>
       </c>
       <c r="D304" s="105">
-        <f t="shared" ref="D304:G304" si="166">D84*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E304" s="105">
-        <f t="shared" si="166"/>
-        <v>5.5439999999999996</v>
+        <f t="shared" si="24"/>
+        <v>5.0820000000000007</v>
       </c>
       <c r="F304" s="105">
-        <f t="shared" si="166"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G304" s="105">
-        <f t="shared" si="166"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H304" s="92">
         <v>1.05</v>
@@ -25626,20 +25599,20 @@
         <v>125</v>
       </c>
       <c r="D305" s="105">
-        <f t="shared" ref="D305:G305" si="167">D85*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E305" s="105">
-        <f t="shared" si="167"/>
-        <v>12.635999999999999</v>
+        <f t="shared" si="24"/>
+        <v>11.583</v>
       </c>
       <c r="F305" s="105">
-        <f t="shared" si="167"/>
-        <v>1.764</v>
+        <f t="shared" si="24"/>
+        <v>1.617</v>
       </c>
       <c r="G305" s="105">
-        <f t="shared" si="167"/>
-        <v>3.0839999999999996</v>
+        <f t="shared" si="24"/>
+        <v>2.827</v>
       </c>
       <c r="H305" s="92">
         <v>1.05</v>
@@ -25654,20 +25627,20 @@
         <v>124</v>
       </c>
       <c r="D306" s="105">
-        <f t="shared" ref="D306:G306" si="168">D86*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G306" s="105">
-        <f t="shared" si="168"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H306" s="92">
         <v>1.05</v>
@@ -25679,20 +25652,20 @@
         <v>127</v>
       </c>
       <c r="D307" s="105">
-        <f t="shared" ref="D307:G307" si="169">D87*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.9919999999999998</v>
+        <f t="shared" si="24"/>
+        <v>1.8260000000000001</v>
       </c>
       <c r="F307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G307" s="105">
-        <f t="shared" si="169"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H307" s="92">
         <v>1.05</v>
@@ -25704,20 +25677,20 @@
         <v>126</v>
       </c>
       <c r="D308" s="105">
-        <f t="shared" ref="D308:G308" si="170">D88*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E308" s="105">
-        <f t="shared" si="170"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>2.75</v>
       </c>
       <c r="F308" s="105">
-        <f t="shared" si="170"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G308" s="105">
-        <f t="shared" si="170"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H308" s="92">
         <v>1.05</v>
@@ -25729,20 +25702,20 @@
         <v>125</v>
       </c>
       <c r="D309" s="105">
-        <f t="shared" ref="D309:G309" si="171">D89*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E309" s="105">
-        <f t="shared" si="171"/>
-        <v>17.963999999999999</v>
+        <f t="shared" si="24"/>
+        <v>16.467000000000002</v>
       </c>
       <c r="F309" s="105">
-        <f t="shared" si="171"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="G309" s="105">
-        <f t="shared" si="171"/>
-        <v>2.3039999999999998</v>
+        <f t="shared" si="24"/>
+        <v>2.1120000000000001</v>
       </c>
       <c r="H309" s="92">
         <v>1.05</v>
@@ -25757,20 +25730,20 @@
         <v>124</v>
       </c>
       <c r="D310" s="105">
-        <f t="shared" ref="D310:G310" si="172">D90*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G310" s="105">
-        <f t="shared" si="172"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H310" s="92">
         <v>1.05</v>
@@ -25782,20 +25755,20 @@
         <v>127</v>
       </c>
       <c r="D311" s="105">
-        <f t="shared" ref="D311:G311" si="173">D91*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.776</v>
+        <f t="shared" si="24"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G311" s="105">
-        <f t="shared" si="173"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H311" s="92">
         <v>1.05</v>
@@ -25807,20 +25780,20 @@
         <v>126</v>
       </c>
       <c r="D312" s="105">
-        <f t="shared" ref="D312:G312" si="174">D92*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E312" s="105">
-        <f t="shared" si="174"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="24"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F312" s="105">
-        <f t="shared" si="174"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G312" s="105">
-        <f t="shared" si="174"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H312" s="92">
         <v>1.05</v>
@@ -25832,20 +25805,20 @@
         <v>125</v>
       </c>
       <c r="D313" s="105">
-        <f t="shared" ref="D313:G313" si="175">D93*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E313" s="105">
-        <f t="shared" si="175"/>
-        <v>17.28</v>
+        <f t="shared" si="24"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F313" s="105">
-        <f t="shared" si="175"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G313" s="105">
-        <f t="shared" si="175"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H313" s="92">
         <v>1.05</v>
@@ -25860,20 +25833,20 @@
         <v>124</v>
       </c>
       <c r="D314" s="105">
-        <f t="shared" ref="D314:G314" si="176">D94*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G314" s="105">
-        <f t="shared" si="176"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H314" s="92">
         <v>1.05</v>
@@ -25885,20 +25858,20 @@
         <v>127</v>
       </c>
       <c r="D315" s="105">
-        <f t="shared" ref="D315:G315" si="177">D95*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.776</v>
+        <f t="shared" si="24"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G315" s="105">
-        <f t="shared" si="177"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H315" s="92">
         <v>1.05</v>
@@ -25910,20 +25883,20 @@
         <v>126</v>
       </c>
       <c r="D316" s="105">
-        <f t="shared" ref="D316:G316" si="178">D96*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E316" s="105">
-        <f t="shared" si="178"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="24"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F316" s="105">
-        <f t="shared" si="178"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G316" s="105">
-        <f t="shared" si="178"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H316" s="92">
         <v>1.05</v>
@@ -25935,20 +25908,20 @@
         <v>125</v>
       </c>
       <c r="D317" s="105">
-        <f t="shared" ref="D317:G317" si="179">D97*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E317" s="105">
-        <f t="shared" si="179"/>
-        <v>17.28</v>
+        <f t="shared" si="24"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F317" s="105">
-        <f t="shared" si="179"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G317" s="105">
-        <f t="shared" si="179"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="24"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H317" s="92">
         <v>1.05</v>
@@ -25963,20 +25936,20 @@
         <v>124</v>
       </c>
       <c r="D318" s="105">
-        <f t="shared" ref="D318:G318" si="180">D98*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="E318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="G318" s="105">
-        <f t="shared" si="180"/>
-        <v>1.2</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="H318" s="92">
         <v>1.05</v>
@@ -25988,20 +25961,20 @@
         <v>127</v>
       </c>
       <c r="D319" s="105">
-        <f t="shared" ref="D319:G319" si="181">D99*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="D319:G321" si="25">IF(D99=1,1,D99*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.776</v>
+        <f t="shared" si="25"/>
+        <v>1.6280000000000001</v>
       </c>
       <c r="F319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="G319" s="105">
-        <f t="shared" si="181"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="H319" s="92">
         <v>1.05</v>
@@ -26013,20 +25986,20 @@
         <v>126</v>
       </c>
       <c r="D320" s="105">
-        <f t="shared" ref="D320:G320" si="182">D100*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="E320" s="105">
-        <f t="shared" si="182"/>
-        <v>3.4079999999999999</v>
+        <f t="shared" si="25"/>
+        <v>3.1240000000000001</v>
       </c>
       <c r="F320" s="105">
-        <f t="shared" si="182"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="G320" s="105">
-        <f t="shared" si="182"/>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="H320" s="92">
         <v>1.05</v>
@@ -26038,20 +26011,20 @@
         <v>125</v>
       </c>
       <c r="D321" s="105">
-        <f t="shared" ref="D321:G321" si="183">D101*1.2</f>
-        <v>1.2</v>
+        <f t="shared" si="25"/>
+        <v>1</v>
       </c>
       <c r="E321" s="105">
-        <f t="shared" si="183"/>
-        <v>17.28</v>
+        <f t="shared" si="25"/>
+        <v>15.840000000000002</v>
       </c>
       <c r="F321" s="105">
-        <f t="shared" si="183"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="25"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="G321" s="105">
-        <f t="shared" si="183"/>
-        <v>4.4279999999999999</v>
+        <f t="shared" si="25"/>
+        <v>4.0590000000000002</v>
       </c>
       <c r="H321" s="92">
         <v>1.05</v>
@@ -26104,20 +26077,20 @@
         <v>124</v>
       </c>
       <c r="D325" s="105">
-        <f>D105*1.2</f>
-        <v>1.2</v>
+        <f>IF(D105=1,1,D105*1.1)</f>
+        <v>1</v>
       </c>
       <c r="E325" s="105">
-        <f t="shared" ref="E325:G325" si="184">E105*1.2</f>
-        <v>1.2</v>
+        <f t="shared" ref="E325:G325" si="26">IF(E105=1,1,E105*1.1)</f>
+        <v>1</v>
       </c>
       <c r="F325" s="105">
-        <f t="shared" si="184"/>
-        <v>1.2</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="G325" s="105">
-        <f t="shared" si="184"/>
-        <v>1.2</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
       </c>
       <c r="H325" s="92">
         <v>1.05</v>
@@ -26129,20 +26102,20 @@
         <v>127</v>
       </c>
       <c r="D326" s="105">
-        <f t="shared" ref="D326:G326" si="185">D106*1.2</f>
-        <v>1.512</v>
+        <f t="shared" ref="D326:G328" si="27">IF(D106=1,1,D106*1.1)</f>
+        <v>1.3860000000000001</v>
       </c>
       <c r="E326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.512</v>
+        <f t="shared" si="27"/>
+        <v>1.3860000000000001</v>
       </c>
       <c r="F326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="G326" s="105">
-        <f t="shared" si="185"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H326" s="92">
         <v>1.05</v>
@@ -26154,20 +26127,20 @@
         <v>126</v>
       </c>
       <c r="D327" s="105">
-        <f t="shared" ref="D327:G327" si="186">D107*1.2</f>
-        <v>2.016</v>
+        <f t="shared" si="27"/>
+        <v>1.8480000000000001</v>
       </c>
       <c r="E327" s="105">
-        <f t="shared" si="186"/>
-        <v>2.016</v>
+        <f t="shared" si="27"/>
+        <v>1.8480000000000001</v>
       </c>
       <c r="F327" s="105">
-        <f t="shared" si="186"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="G327" s="105">
-        <f t="shared" si="186"/>
-        <v>1.2</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H327" s="92">
         <v>1.05</v>
@@ -26179,20 +26152,20 @@
         <v>125</v>
       </c>
       <c r="D328" s="105">
-        <f t="shared" ref="D328:G328" si="187">D108*1.2</f>
-        <v>3.1799999999999997</v>
+        <f t="shared" si="27"/>
+        <v>2.915</v>
       </c>
       <c r="E328" s="105">
-        <f t="shared" si="187"/>
-        <v>3.1799999999999997</v>
+        <f t="shared" si="27"/>
+        <v>2.915</v>
       </c>
       <c r="F328" s="105">
-        <f t="shared" si="187"/>
-        <v>2.4839999999999995</v>
+        <f t="shared" si="27"/>
+        <v>2.2770000000000001</v>
       </c>
       <c r="G328" s="105">
-        <f t="shared" si="187"/>
-        <v>2.4839999999999995</v>
+        <f t="shared" si="27"/>
+        <v>2.2770000000000001</v>
       </c>
       <c r="H328" s="92">
         <v>1.05</v>
@@ -26200,12 +26173,9 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KZz8g2OlfLTzqwPv8ev0gm+RfJs6zGMY35veya1aUPJFCyJgxdGdQyb6Cg9nvOSFU2u9I52IMlddaWJNKXsk8Q==" saltValue="rSafH1HsFJdNqLr6vFu5DQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/VZzj8y0LwE/VxoCQ+H6qCKtATYCqb68ZT9Ig715zr9m5+wG4vmTAVMu/Ybmg+wnryJ5ifHQxsZAozMqYTN0LQ==" saltValue="VA2cpEiv/Ws1ggCx1KfxcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <ignoredErrors>
-    <ignoredError sqref="D113:H135 D140:H163 D167:G172 D176:G211 D215:G218 D223:H246 D250:H273 D277:G282 D286:G321 D325:G328" unlockedFormula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -26310,13 +26280,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.64, (0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.64*SUM('Distribución estado nutricional'!$E$4:$E$5)))
-/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.58066667124954463</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.64, (0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.64*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.51238891655164942</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="104">
         <v>1</v>
@@ -26333,12 +26300,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.85101406604290009</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.81254490106633903</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="104">
         <v>1</v>
@@ -26355,12 +26320,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$E$4),0.88, (0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-0.88*SUM('Distribución estado nutricional'!$E$4:$E$5)))/ (SUM('Distribución estado nutricional'!$E$4:$E$5)/(1-SUM('Distribución estado nutricional'!$E$4:$E$5))))</f>
-        <v>0.85101406604290009</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!$F$4),0.88, (0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-0.88*SUM('Distribución estado nutricional'!$F$4:$F$5)))/ (SUM('Distribución estado nutricional'!$F$4:$F$5)/(1-SUM('Distribución estado nutricional'!$F$4:$F$5))))</f>
-        <v>0.81254490106633903</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="104">
         <v>1</v>
@@ -26638,12 +26601,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.44, (0.44*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.44*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.37965437977673294</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.44, (0.44*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.44*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.31713700135771467</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="104">
         <f t="shared" si="2"/>
@@ -26663,12 +26626,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.81528861437883526</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.77008703591766947</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="104">
         <f t="shared" si="3"/>
@@ -26688,12 +26649,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.85, (0.85*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.85*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.81528861437883526</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.85, (0.85*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.85*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.77008703591766947</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="104">
         <f t="shared" si="3"/>
@@ -26750,12 +26709,10 @@
         <v>303</v>
       </c>
       <c r="C35" s="104">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="104">
-        <f t="shared" ref="D35" si="4">D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="104">
         <v>1</v>
@@ -26794,19 +26751,19 @@
         <v>0.92249999999999999</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" ref="D38:G38" si="5">IF(D15=1,1,D15*0.9)</f>
+        <f t="shared" ref="D38:G38" si="4">IF(D15=1,1,D15*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="E38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
@@ -26816,23 +26773,23 @@
         <v>292</v>
       </c>
       <c r="C39" s="104">
-        <f t="shared" ref="C39:G40" si="6">IF(C16=1,1,C16*0.9)</f>
+        <f t="shared" ref="C39:G40" si="5">IF(C16=1,1,C16*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="D39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="E39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G39" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
@@ -26844,23 +26801,23 @@
         <v>298</v>
       </c>
       <c r="C40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G40" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -26955,19 +26912,19 @@
         <v>8</v>
       </c>
       <c r="D49" s="104">
-        <f t="shared" ref="D49:G50" si="7">D3*1.05</f>
+        <f t="shared" ref="D49:G50" si="6">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
     </row>
@@ -26981,19 +26938,19 @@
         <v>1.0762499999999999</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1.0762499999999999</v>
       </c>
     </row>
@@ -27011,19 +26968,19 @@
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" ref="D52:G52" si="8">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="7">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.92, (0.92*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.92*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.89957340821150999</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.92, (0.92*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.92*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.87175307455800355</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -27032,23 +26989,21 @@
         <v>306</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" ref="C53:G55" si="9">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G55" si="8">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.88733277546126343</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.85666183196284651</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27057,23 +27012,21 @@
         <v>320</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$4),0.91, (0.91*SUM('Distribución estado nutricional'!E$4:E$5)/(1-0.91*SUM('Distribución estado nutricional'!E$4:E$5)))/ (SUM('Distribución estado nutricional'!E$4:E$5)/(1-SUM('Distribución estado nutricional'!E$4:E$5))))</f>
-        <v>0.88733277546126343</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$4),0.91, (0.91*SUM('Distribución estado nutricional'!F$4:F$5)/(1-0.91*SUM('Distribución estado nutricional'!F$4:F$5)))/ (SUM('Distribución estado nutricional'!F$4:F$5)/(1-SUM('Distribución estado nutricional'!F$4:F$5))))</f>
-        <v>0.85666183196284651</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27082,23 +27035,23 @@
         <v>318</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -27127,12 +27080,10 @@
         <v>304</v>
       </c>
       <c r="C58" s="104">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="104">
-        <f t="shared" ref="D58" si="10">D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="104">
         <v>1</v>
@@ -27171,19 +27122,19 @@
         <v>1.1274999999999999</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" ref="D61:G61" si="11">IF(D15=1,1,D15*1.1)</f>
+        <f t="shared" ref="D61:G61" si="9">IF(D15=1,1,D15*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="E61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
@@ -27193,23 +27144,23 @@
         <v>293</v>
       </c>
       <c r="C62" s="104">
-        <f t="shared" ref="C62:G63" si="12">IF(C16=1,1,C16*1.1)</f>
+        <f t="shared" ref="C62:G63" si="10">IF(C16=1,1,C16*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="D62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="E62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G62" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
@@ -27221,23 +27172,23 @@
         <v>299</v>
       </c>
       <c r="C63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G63" s="104">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -27288,7 +27239,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5W6kYPdvTZhnXMKluL16yLoX5ApU0HAP4o6ABRB0H4GQdd3oZmPOSfC7X2YezgMsSEcNyg8oaPkOtUHdidM42g==" saltValue="7k9n9eCdw+MMg0aHrIDr9w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EwxCuQXTLhqtNsMIsSZCjMSPBF/lZ2dzOl1G/52wtAk91b+t2nOjWBAUfl7JIV3WzbqlS2ndixow8bV9atLBMg==" saltValue="EN0D6eb/ZWFY/LHaUVXUIA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -28109,7 +28060,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="05N7LFaTiDS+xIOOSCWSe3nIGxmFC1p/+IVl3yo5tdvYJs2aJ68K4RjlG32+rKQbjBaqfWv6KrxtXf2lO+RpVQ==" saltValue="GN8MLlk6l2igy8PvLhQOUA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bDgA55LHnnOYlYED/NtVwQaVlI1QGvlpKfjqcRPDLfnmrLUSjQdCtDh599aneDXTvmxRCwY4UcI6Mi2puv7sJQ==" saltValue="V0AkeUJLm6m2GhyGcK1RzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -28182,7 +28133,7 @@
         <v>169</v>
       </c>
       <c r="C3" s="104">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="104">
         <v>0.53</v>
@@ -28517,16 +28468,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="104">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -28693,15 +28644,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="104">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="104">
+        <f t="shared" ref="M14:O14" si="0">M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="104">
+        <f t="shared" si="0"/>
         <v>0.51</v>
       </c>
       <c r="O14" s="104">
+        <f t="shared" si="0"/>
         <v>0.51</v>
       </c>
     </row>
@@ -28810,59 +28765,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.72,(0.72*'Distribución estado nutricional'!E$14/(1-0.72*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.36026320599524769</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.72,(0.72*'Distribución estado nutricional'!F$14/(1-0.72*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.41022832589097646</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.72,(0.72*'Distribución estado nutricional'!G$14/(1-0.72*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.57039401006505464</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.72,(0.72*'Distribución estado nutricional'!H$14/(1-0.72*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.57539730680577461</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.72,(0.72*'Distribución estado nutricional'!I$14/(1-0.72*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.5871180842279109</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.72,(0.72*'Distribución estado nutricional'!J$14/(1-0.72*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.5931651749389748</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.72,(0.72*'Distribución estado nutricional'!K$14/(1-0.72*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.58929828678713914</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.72,(0.72*'Distribución estado nutricional'!L$14/(1-0.72*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.57539730680577461</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.72,(0.72*'Distribución estado nutricional'!M$14/(1-0.72*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.5871180842279109</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.72,(0.72*'Distribución estado nutricional'!N$14/(1-0.72*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.5931651749389748</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.72,(0.72*'Distribución estado nutricional'!O$14/(1-0.72*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.58929828678713914</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -28876,37 +28809,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="104">
-        <v>1</v>
+        <f>E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="104">
-        <v>1</v>
+        <f t="shared" ref="F20:O20" si="1">F19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="104">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -28920,59 +28864,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.8,(0.8*'Distribución estado nutricional'!E$14/(1-0.8*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.46695095948827287</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.8,(0.8*'Distribución estado nutricional'!F$14/(1-0.8*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.51969260326609024</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.8,(0.8*'Distribución estado nutricional'!G$14/(1-0.8*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.67377120487168329</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.8,(0.8*'Distribución estado nutricional'!H$14/(1-0.8*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.67824967824967841</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.8,(0.8*'Distribución estado nutricional'!I$14/(1-0.8*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.68866749688667506</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.8,(0.8*'Distribución estado nutricional'!J$14/(1-0.8*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.69400244798041621</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.8,(0.8*'Distribución estado nutricional'!K$14/(1-0.8*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.69059405940594076</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.8,(0.8*'Distribución estado nutricional'!L$14/(1-0.8*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.67824967824967841</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.8,(0.8*'Distribución estado nutricional'!M$14/(1-0.8*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.68866749688667506</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.8,(0.8*'Distribución estado nutricional'!N$14/(1-0.8*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.69400244798041621</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.8,(0.8*'Distribución estado nutricional'!O$14/(1-0.8*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.69059405940594076</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -29033,53 +28955,53 @@
         <v>169</v>
       </c>
       <c r="C26" s="104">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="104">
         <v>0.4</v>
       </c>
       <c r="E26" s="104">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O26" s="104">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29088,23 +29010,23 @@
         <v>174</v>
       </c>
       <c r="C27" s="104">
-        <f t="shared" ref="C27:O34" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O34" si="3">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H27" s="104">
@@ -29120,19 +29042,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29141,23 +29063,23 @@
         <v>175</v>
       </c>
       <c r="C28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H28" s="104">
@@ -29173,19 +29095,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29194,23 +29116,23 @@
         <v>176</v>
       </c>
       <c r="C29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H29" s="104">
@@ -29226,19 +29148,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29247,23 +29169,23 @@
         <v>177</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H30" s="104">
@@ -29279,19 +29201,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29300,39 +29222,39 @@
         <v>178</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K31" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L31" s="104">
@@ -29353,39 +29275,39 @@
         <v>179</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K32" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L32" s="104">
@@ -29406,39 +29328,39 @@
         <v>180</v>
       </c>
       <c r="C33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K33" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L33" s="104">
@@ -29459,11 +29381,11 @@
         <v>184</v>
       </c>
       <c r="C34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E34" s="104">
@@ -29476,35 +29398,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O34" s="104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29557,11 +29479,11 @@
         <v>190</v>
       </c>
       <c r="C36" s="104">
-        <f t="shared" ref="C36:O38" si="2">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O38" si="4">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="104">
@@ -29574,35 +29496,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O36" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -29611,56 +29533,52 @@
         <v>191</v>
       </c>
       <c r="C37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K37" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L37" s="104">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="104">
-        <f t="shared" ref="M37:O37" si="3">M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="104">
-        <f t="shared" si="3"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="104">
-        <f t="shared" si="3"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -29668,11 +29586,11 @@
         <v>204</v>
       </c>
       <c r="C38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E38" s="104">
@@ -29682,39 +29600,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O38" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -29729,55 +29647,55 @@
         <v>171</v>
       </c>
       <c r="C41" s="104">
-        <f t="shared" ref="C41:O44" si="4">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O44" si="5">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O41" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -29786,67 +29704,45 @@
         <v>172</v>
       </c>
       <c r="C42" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D42" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.54,(0.54*'Distribución estado nutricional'!E$14/(1-0.54*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.20451008197004808</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.54,(0.54*'Distribución estado nutricional'!F$14/(1-0.54*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.24101176431765312</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.54,(0.54*'Distribución estado nutricional'!G$14/(1-0.54*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.37738556075904828</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.54,(0.54*'Distribución estado nutricional'!H$14/(1-0.54*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.38220204679147979</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.54,(0.54*'Distribución estado nutricional'!I$14/(1-0.54*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.39363581239619311</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.54,(0.54*'Distribución estado nutricional'!J$14/(1-0.54*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.39961888851183797</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.54,(0.54*'Distribución estado nutricional'!K$14/(1-0.54*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.3957862659591237</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.54,(0.54*'Distribución estado nutricional'!L$14/(1-0.54*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.38220204679147979</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.54,(0.54*'Distribución estado nutricional'!M$14/(1-0.54*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.39363581239619311</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.54,(0.54*'Distribución estado nutricional'!N$14/(1-0.54*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.39961888851183797</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.54,(0.54*'Distribución estado nutricional'!O$14/(1-0.54*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.3957862659591237</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -29854,56 +29750,56 @@
         <v>173</v>
       </c>
       <c r="C43" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D43" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="104">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -29911,67 +29807,45 @@
         <v>181</v>
       </c>
       <c r="C44" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D44" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.7,(0.7*'Distribución estado nutricional'!E$14/(1-0.7*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.33818663136995358</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.7,(0.7*'Distribución estado nutricional'!F$14/(1-0.7*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.38694186165321348</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.7,(0.7*'Distribución estado nutricional'!G$14/(1-0.7*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.54643955047119874</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.7,(0.7*'Distribución estado nutricional'!H$14/(1-0.7*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.55150246673643288</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.7,(0.7*'Distribución estado nutricional'!I$14/(1-0.7*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.56338233153834949</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.7,(0.7*'Distribución estado nutricional'!J$14/(1-0.7*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.56952216960826507</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.7,(0.7*'Distribución estado nutricional'!K$14/(1-0.7*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.56559513466550837</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.7,(0.7*'Distribución estado nutricional'!L$14/(1-0.7*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.55150246673643288</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.7,(0.7*'Distribución estado nutricional'!M$14/(1-0.7*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.56338233153834949</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.7,(0.7*'Distribución estado nutricional'!N$14/(1-0.7*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.56952216960826507</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.7,(0.7*'Distribución estado nutricional'!O$14/(1-0.7*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.56559513466550837</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -30032,53 +29906,53 @@
         <v>169</v>
       </c>
       <c r="C49" s="104">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="104">
         <v>0.7</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" ref="E49:O49" si="5">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O49" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30087,23 +29961,23 @@
         <v>174</v>
       </c>
       <c r="C50" s="104">
-        <f t="shared" ref="C50:O57" si="6">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O57" si="7">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H50" s="104">
@@ -30119,19 +29993,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O50" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30140,23 +30014,23 @@
         <v>175</v>
       </c>
       <c r="C51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H51" s="104">
@@ -30172,19 +30046,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O51" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30193,23 +30067,23 @@
         <v>176</v>
       </c>
       <c r="C52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H52" s="104">
@@ -30225,19 +30099,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O52" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30246,23 +30120,23 @@
         <v>177</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H53" s="104">
@@ -30278,19 +30152,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O53" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30299,39 +30173,39 @@
         <v>178</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K54" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L54" s="104">
@@ -30352,39 +30226,39 @@
         <v>179</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K55" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L55" s="104">
@@ -30405,52 +30279,52 @@
         <v>180</v>
       </c>
       <c r="C56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K56" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="104">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -30458,11 +30332,11 @@
         <v>184</v>
       </c>
       <c r="C57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E57" s="104">
@@ -30472,39 +30346,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O57" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30557,11 +30431,11 @@
         <v>190</v>
       </c>
       <c r="C59" s="104">
-        <f t="shared" ref="C59:O61" si="7">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O61" si="8">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E59" s="104">
@@ -30574,35 +30448,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O59" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -30611,56 +30485,52 @@
         <v>191</v>
       </c>
       <c r="C60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K60" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L60" s="104">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="104">
-        <f t="shared" ref="M60:O60" si="8">M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="104">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="104">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -30668,11 +30538,11 @@
         <v>204</v>
       </c>
       <c r="C61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E61" s="104">
@@ -30682,39 +30552,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O61" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -30794,59 +30664,37 @@
         <v>1</v>
       </c>
       <c r="E65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.97,(0.97*'Distribución estado nutricional'!E$14/(1-0.97*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.87625293899269863</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.97,(0.97*'Distribución estado nutricional'!F$14/(1-0.97*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.89739555722762776</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.97,(0.97*'Distribución estado nutricional'!G$14/(1-0.97*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.94348615096732857</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.97,(0.97*'Distribución estado nutricional'!H$14/(1-0.97*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.94456660322622354</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.97,(0.97*'Distribución estado nutricional'!I$14/(1-0.97*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.94703483342455097</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.97,(0.97*'Distribución estado nutricional'!J$14/(1-0.97*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.94827497025810792</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.97,(0.97*'Distribución estado nutricional'!K$14/(1-0.97*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.94748450792983951</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.97,(0.97*'Distribución estado nutricional'!L$14/(1-0.97*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.94456660322622354</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.97,(0.97*'Distribución estado nutricional'!M$14/(1-0.97*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.94703483342455097</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.97,(0.97*'Distribución estado nutricional'!N$14/(1-0.97*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.94827497025810792</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.97,(0.97*'Distribución estado nutricional'!O$14/(1-0.97*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.94748450792983951</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -30863,47 +30711,47 @@
       </c>
       <c r="E66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="104">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -30919,63 +30767,41 @@
         <v>1</v>
       </c>
       <c r="E67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$14),0.92,(0.92*'Distribución estado nutricional'!E$14/(1-0.92*'Distribución estado nutricional'!E$14))
-/ ('Distribución estado nutricional'!E$14/(1-'Distribución estado nutricional'!E$14)))</f>
-        <v>0.71578797783146231</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$14),0.92,(0.92*'Distribución estado nutricional'!F$14/(1-0.92*'Distribución estado nutricional'!F$14))
-/ ('Distribución estado nutricional'!F$14/(1-'Distribución estado nutricional'!F$14)))</f>
-        <v>0.75673538891929704</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$14),0.92,(0.92*'Distribución estado nutricional'!G$14/(1-0.92*'Distribución estado nutricional'!G$14))
-/ ('Distribución estado nutricional'!G$14/(1-'Distribución estado nutricional'!G$14)))</f>
-        <v>0.85586278136786231</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!H$14),0.92,(0.92*'Distribución estado nutricional'!H$14/(1-0.92*'Distribución estado nutricional'!H$14))
-/ ('Distribución estado nutricional'!H$14/(1-'Distribución estado nutricional'!H$14)))</f>
-        <v>0.85836697117767868</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!I$14),0.92,(0.92*'Distribución estado nutricional'!I$14/(1-0.92*'Distribución estado nutricional'!I$14))
-/ ('Distribución estado nutricional'!I$14/(1-'Distribución estado nutricional'!I$14)))</f>
-        <v>0.86412120388613367</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!J$14),0.92,(0.92*'Distribución estado nutricional'!J$14/(1-0.92*'Distribución estado nutricional'!J$14))
-/ ('Distribución estado nutricional'!J$14/(1-'Distribución estado nutricional'!J$14)))</f>
-        <v>0.86703011767834581</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!K$14),0.92,(0.92*'Distribución estado nutricional'!K$14/(1-0.92*'Distribución estado nutricional'!K$14))
-/ ('Distribución estado nutricional'!K$14/(1-'Distribución estado nutricional'!K$14)))</f>
-        <v>0.86517459889443182</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!L$14),0.92,(0.92*'Distribución estado nutricional'!L$14/(1-0.92*'Distribución estado nutricional'!L$14))
-/ ('Distribución estado nutricional'!L$14/(1-'Distribución estado nutricional'!L$14)))</f>
-        <v>0.85836697117767868</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!M$14),0.92,(0.92*'Distribución estado nutricional'!M$14/(1-0.92*'Distribución estado nutricional'!M$14))
-/ ('Distribución estado nutricional'!M$14/(1-'Distribución estado nutricional'!M$14)))</f>
-        <v>0.86412120388613367</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!N$14),0.92,(0.92*'Distribución estado nutricional'!N$14/(1-0.92*'Distribución estado nutricional'!N$14))
-/ ('Distribución estado nutricional'!N$14/(1-'Distribución estado nutricional'!N$14)))</f>
-        <v>0.86703011767834581</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!O$14),0.92,(0.92*'Distribución estado nutricional'!O$14/(1-0.92*'Distribución estado nutricional'!O$14))
-/ ('Distribución estado nutricional'!O$14/(1-'Distribución estado nutricional'!O$14)))</f>
-        <v>0.86517459889443182</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="w4HQaC0QZYscrcK9wvy2uhKDGADIGAKeKfoP9im7Ko1jGYqww9sdhySWz7YUyEY21hGhStwDl5wx2Y6zSTDWGg==" saltValue="9lAINRRwbMaTWPSz1MvJYw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="M3mT2e3wCgG3xd4LEJ5JQpp7ptzRF39w69so3HJPn82CnpMRSIao7rINcsO2P8TnytX6m693jL4eRKR3+B+b9Q==" saltValue="Emnt0kcVLe2bMGvarNhkDA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -31027,24 +30853,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$11/(1-(1/1.33)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.74418604651162779</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$11/(1-(1/1.33)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.74891097206376045</v>
+        <f t="shared" ref="E3:G3" si="0">1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$11/(1-(1/1.33)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.74998192742905989</v>
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$11/(1-(1/1.33)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.75050381305965674</v>
+        <f t="shared" si="0"/>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31066,24 +30888,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!D$10/(1-(1/1.33)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.74137931034482751</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!E$10/(1-(1/1.33)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.74137473695379219</v>
+        <f t="shared" ref="E5:G5" si="1">1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!F$10/(1-(1/1.33)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.74367982247882258</v>
+        <f t="shared" si="1"/>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.33),((1/1.33)*'Distribución estado nutricional'!G$10/(1-(1/1.33)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.74764262641695323</v>
+        <f t="shared" si="1"/>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -31123,24 +30941,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$11/(1-(1/1.54)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.64</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$11/(1-(1/1.54)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.64573318763423793</v>
+        <f t="shared" ref="E10:G10" si="2">1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$11/(1-(1/1.54)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.64703681148148418</v>
+        <f t="shared" si="2"/>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$11/(1-(1/1.54)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.64767263413148468</v>
+        <f t="shared" si="2"/>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31162,24 +30976,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!D$10/(1-(1/1.54)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.63660834454912518</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!E$10/(1-(1/1.54)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.63660282656050271</v>
+        <f t="shared" ref="E12:G12" si="3">1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!F$10/(1-(1/1.54)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.6393875097491748</v>
+        <f t="shared" si="3"/>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.54),((1/1.54)*'Distribución estado nutricional'!G$10/(1-(1/1.54)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.64419127013395971</v>
+        <f t="shared" si="3"/>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -31219,24 +31029,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$11/(1-(1/1.16)*'Distribución estado nutricional'!D$11))
-/ ('Distribución estado nutricional'!D$11/(1-'Distribución estado nutricional'!D$11)))</f>
-        <v>0.85714285714285721</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$11/(1-(1/1.16)*'Distribución estado nutricional'!E$11))
-/ ('Distribución estado nutricional'!E$11/(1-'Distribución estado nutricional'!E$11)))</f>
-        <v>0.86017345661971134</v>
+        <f t="shared" ref="E17:G17" si="4">1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$11/(1-(1/1.16)*'Distribución estado nutricional'!F$11))
-/ ('Distribución estado nutricional'!F$11/(1-'Distribución estado nutricional'!F$11)))</f>
-        <v>0.86085802051335469</v>
+        <f t="shared" si="4"/>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$11),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$11/(1-(1/1.16)*'Distribución estado nutricional'!G$11))
-/ ('Distribución estado nutricional'!G$11/(1-'Distribución estado nutricional'!G$11)))</f>
-        <v>0.86119130020042822</v>
+        <f t="shared" si="4"/>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -31258,28 +31064,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!D$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!D$10/(1-(1/1.16)*'Distribución estado nutricional'!D$10))
-/ ('Distribución estado nutricional'!D$10/(1-'Distribución estado nutricional'!D$10)))</f>
-        <v>0.85533453887884281</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!E$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!E$10/(1-(1/1.16)*'Distribución estado nutricional'!E$10))
-/ ('Distribución estado nutricional'!E$10/(1-'Distribución estado nutricional'!E$10)))</f>
-        <v>0.85533158742052517</v>
+        <f t="shared" ref="E19:G19" si="5">1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!F$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!F$10/(1-(1/1.16)*'Distribución estado nutricional'!F$10))
-/ ('Distribución estado nutricional'!F$10/(1-'Distribución estado nutricional'!F$10)))</f>
-        <v>0.85681715347913645</v>
+        <f t="shared" si="5"/>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="104">
-        <f>IF(ISBLANK('Distribución estado nutricional'!G$10),(1/1.16),((1/1.16)*'Distribución estado nutricional'!G$10/(1-(1/1.16)*'Distribución estado nutricional'!G$10))
-/ ('Distribución estado nutricional'!G$10/(1-'Distribución estado nutricional'!G$10)))</f>
-        <v>0.8593615961490525</v>
+        <f t="shared" si="5"/>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/9wZz2FmhF9B+FitMI+q5wX4ym3ZIVhqJAIeoRdmld6BhFqSHEwu+PBNhR/Pc5OIKcfg7kvCwn0F21oAltdqjw==" saltValue="8ZmhbisS4ZzBEJ3Ew0veuw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iVpfZa0L+V8UXdUtjTEI65Fz10pcho5t23F5y4n2eFZKOzJ9WlD+omA9I+zinEQLDkQd0yp+1h1R5z1ZK6WvQA==" saltValue="xMLiq74Ne/2wyl4TSwQoaA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -32472,7 +32274,7 @@
         <v>339</v>
       </c>
       <c r="D53" s="104">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="104">
         <v>0</v>
@@ -33728,7 +33530,7 @@
         <v>339</v>
       </c>
       <c r="D108" s="104">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="104">
         <v>0</v>
@@ -34989,7 +34791,7 @@
         <v>339</v>
       </c>
       <c r="D163" s="104">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="104">
         <v>0</v>
@@ -35005,7 +34807,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mJ2fVJ5M0be/Z2LJ2MdfDBCuVbO02nP/tVkqP+DyXqE+IhZRRKNANkxtY+h6baknhQKZFMgLChl04BHHFtBDLg==" saltValue="NdFScr0vOLoSrhJbi1mzEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p6dMdLV86AN+JebQ3mjrhYOWSmomwR2J8YutIbnWVj36NwAcsFut1byLuPo7z/kdrAb+PIIi1IY/mDddFboLEA==" saltValue="FLQeBgX5dAhsYUDyHC6YHA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -35507,7 +35309,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nZsKH7eUXg9LlrFKP1cHsWT/0RrH9UTQqXi63zA5bfBPP3yUlpBj8/bzageG8xL89FZkA341VR4k2WZRLEFyEg==" saltValue="fKH6DNWwKwc5fvCibXz2LA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8r0zYoaUi2imki18RaQ+86v/RQ+WMKzi0EcQrDjdLt2Rj9FAKQsAgPoyYzxfGj70S8F85AU/SEnqT+E7I+dyrQ==" saltValue="kY/OfEzRgPtThmDo90X4og==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35939,7 +35741,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cDbrce4tBWgRm8wbxYVYXdb0Nj41yLD1Mrh5FTxQZ9HT0EjeJYvuMtqENDzeJpj7lLCsHJyi+LM/HE8YFGX64g==" saltValue="uFLbZQMwjIKayfX34tbljw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bpAHrOh3+BefP5WlcnHbLCytDUpS3LeSUJ9MeRFIMm84ZSKFqWRcYOlLP4ECEobjSSs02xJeMg7HyRQ01s8wow==" saltValue="sRJwPRPDwUtnAaq0VFfX8w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -35999,15 +35801,15 @@
       </c>
       <c r="E2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.40847634403930777</v>
+        <v>0.39571950531782307</v>
       </c>
       <c r="F2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.22074857548762972</v>
+        <v>0.21538848080661976</v>
       </c>
       <c r="G2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.20249364172902928</v>
+        <v>0.20291379751882221</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36024,15 +35826,15 @@
       </c>
       <c r="E3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.37043861497708613</v>
+        <v>0.37328049468217694</v>
       </c>
       <c r="F3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.37033471885022728</v>
+        <v>0.3686115191933802</v>
       </c>
       <c r="G3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.36392076328140976</v>
+        <v>0.36408620248117773</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36046,13 +35848,13 @@
         <v>0.107</v>
       </c>
       <c r="E4" s="59">
-        <v>0.14443032786885199</v>
+        <v>0.154</v>
       </c>
       <c r="F4" s="59">
-        <v>0.256731867103416</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G4" s="59">
-        <v>0.27929610299234497</v>
+        <v>0.27900000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36066,13 +35868,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E5" s="59">
-        <v>7.6654713114754094E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="F5" s="59">
-        <v>0.152184838558727</v>
+        <v>0.152</v>
       </c>
       <c r="G5" s="59">
-        <v>0.15428949199721601</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36358,7 +36160,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9fQ1r1atO9EQa8XHwNGGG/kKyVyZXVIcu4jGKRJQppeoHErH+OcImr87MN2bVma9DP3gEgh7xs+xz0KQW3kcaA==" saltValue="SmjRvk5aps+9KR8sRW6bRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xyWRv/UFDUjmvCnPI5Xb7MD1BwQmOusBE0PcMtQTFMvyRVzZctZRJsyIDHHBqepEDBnWXOkGGXykE7J0y091Kg==" saltValue="LWauj1x43RPx69LRrz4ROA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -36490,7 +36292,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a7z8CuMKB7Qs+qfq5CMvUL1/l8SfTX+jV3xYKsgSGoKGDKRrREZzBJ4mD+4QQEudmMhzdntwh5hyD47VSWtSsw==" saltValue="/XBA90EEiwivP0Vps4ya9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ldtr8wddbhqBfwniTN/bGAjEL7vgR/tHgEJnThKdBHEMnCT1g0JPx2u0wV9dFG6a3385B+kkj/R/PgX9jXHyfg==" saltValue="vRpVIfrSJnLkJTSDsNfwCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36692,7 +36494,7 @@
       <c r="K14" s="115"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8lmUs3m7TGXvbFjBY2jGh3qD/uecN5yAaIGBpTr/EAwcJ4LbhunMAkQy+xmnnQEz7mg9dweFsh5pK0kqSMneOw==" saltValue="XZEIr7w763PFfSZGLRhYow==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4TP/ozqnSWfXBvOjJTHvgf+2WsPBSgaHFuZqUnmdwXsMNT8UXCjTvpEkUbdf+LjPsjAYwsSb4zrljrMqpB86UA==" saltValue="PlAFXmzGj5iYOvxyZWc1Zw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36768,7 +36570,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p7KpRaEx4xgAqyE+uOv8ZnGbAgQFT7NRXUnlpemDpUIu4o5kBugc8zFMz64CnBuNgvYvCoIrnDR2H4fjukZ8tg==" saltValue="+WmXTpliIxI1moElzYs+/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tIJZ4LD0IZTehx7+PZByTqiQYSzp9Q5zPeFLHUOw399tN0s0it4CjeSVO2jRaeJObgLQiiOFP65MiZ/A6bhZ+g==" saltValue="cYrU/CjFKwsKbwDLYDcX8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -37023,7 +36825,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IX30Uo3Tf73OQPBmbKrcDHFts9mHpQmBzC7/WoWZQiVKJ0BgWJoC5w0ZqU19a/3zHVes5ogbaNjz+iVoyyNrHg==" saltValue="qWAvLjHTDVb8dG4NawLZUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UhvFX5BLXyh3MdbKMjxfEOdrd2MGLRWPGb8d9LuNP7PkYo2QEi0pHkhSa3aInmjWnl0zWqQqWcpfEp0ecdxFFw==" saltValue="evnJT5/GNnE4YbRhr4vaYA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -37082,7 +36884,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YqZCVpE5d5C1MX0hP9pd1/nYDqi6Fu+fHixuo7Wqqppa56SHV9kCNTPmJwL7dQhW0nLqo9uQLFIWvCu9ODSd/w==" saltValue="9km0nOUkbq6tDfLAnlqo4A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2zYQqZEcvo/lG8zg6ok0Yeeg8j5rM5sRLdZ8a4HvuN5mgf97r8rL4CnNZeg6I4MgddoXuTfIp2xYBuKT65GOQg==" saltValue="UXx2D061D9Cg6OntI9KwGQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/es/demo_region3_input.xlsx
+++ b/inputs/es/demo_region3_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DD57AC4-52F5-43EB-9B7E-A6F8F2E563EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73263C0E-12BB-49C1-A6D1-0CD21EE2367F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -508,6 +508,304 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Nick Scott</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{7F5E27CE-1436-4C41-A7F1-63F83A7F0B04}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{B41F646A-8FD6-4852-BF16-B5442AB7C7D9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{CC986596-2B0F-42A9-9A47-88DAE772D109}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Heidkamp R, Guida R, Phillips E, Clermont A. The Lives Saved Tool (LiST) as a Model for Prevention of Anemia in Women of Reproductive Age. J Nutr. 2017;147(11):2156S-2162S</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D66" authorId="0" shapeId="0" xr:uid="{3F4E7CBA-2B10-4502-8317-5655216D1A3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{70995A78-B3A6-4CBF-84F2-73260F6E3697}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{6DD196E0-C02E-4DCD-8399-4DB5DA640B82}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0" xr:uid="{AC599970-9F13-47AA-8593-282B4B25AE84}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D86" authorId="0" shapeId="0" xr:uid="{B90C3FE6-0710-44A3-BA91-58AF31680641}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{AF883F52-57AF-4371-B93E-04D28670E1E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0" xr:uid="{06FA942C-64E9-47C9-A605-62CF64FBD212}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D98" authorId="0" shapeId="0" xr:uid="{0270CB67-F57B-49D6-8659-A0C53EC25924}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D105" authorId="0" shapeId="0" xr:uid="{F2FA744C-6A87-4925-8C09-A199439E98F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Nick Scott</author>
@@ -1701,7 +1999,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1871,6 +2169,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -5681,7 +5992,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BTeOL4PuKmSLPjjCSOs80FItv7MNSLC4tKf32uxMpBD/Yypocvcwh1Hy4eoGBKAkU9vbKVi22bABdIJXMLkrZg==" saltValue="aHKCf9lb9r6Lx8Ozr1n4JQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="O44NQb0KPVAo9WcE4AMLaBY8cQ3+MYvq6IAt46sprIdxtJRRkuhnX+VrnpLp+bXSCAtwPIi/Pa/Ca7UDXPAn0w==" saltValue="w31ZDWTurLEkl2cY+KZ5Kg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -6605,7 +6916,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vhBZbloXbd9z7Nu+qubRg1Jy0idiQKuj1K/sQQqy4S9pBqy+Y5mhRIjAQPjx853I0kPrFahHnutzNCiHPFXOyA==" saltValue="4QjKFaOjeUySIA/Z7mxOzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eeu7TOS0Ih8Fds8i6L3ZJwB+E0ZqUFoAmb5YeZ1p93AU227XkJuxgUf0Orc7+vYs6Cq5o7ZEA2hP0DEuk7awCg==" saltValue="Wd8UWM6o4eHHr/SkYSKPUw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -6764,7 +7075,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jiWB00uK7Buh7QPwIgfwe6Ho/x0HcT5hcXg8b8kh9XS4lQJzK22f9eudbviuKUnYrUVrw+J5liux0jDvsLBVvw==" saltValue="/lehf6I6FAWveTRqQvwdKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yIcQsO+bqNvloSdJcynu719exjxphUBVSuV7saAFb/Kzhq8+/VVLVVE1mp3BXrQJK92WFMRVWir9NxyDsCuurQ==" saltValue="a9Df6Ww0o0pmrTn9yVRITA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -6859,7 +7170,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ph11QfXaZwUwbp6PSi5tTIBwlVY+qQSdyxmajd132Hb9GqpsmH2O7pOUQkO3qDSU8a9n0NFRVrtKGPggHVszQw==" saltValue="xVg08oGhAwgtkpBnA35eFw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VES3aL+Si+OXS7sw/Dl65fWUK+ICoZUOz0Lm5wRPPVdetMfpqU5xOKMNr/bc+tePVik25k9fkjWqOyEZqfhf+w==" saltValue="Q3pljGmSRtemiutd98Qc5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -6924,23 +7235,23 @@
       </c>
       <c r="B3" s="21">
         <f>frac_mam_1month * 2.6</f>
-        <v>0.1404</v>
+        <v>0.19239999999999999</v>
       </c>
       <c r="C3" s="21">
         <f>frac_mam_1_5months * 2.6</f>
-        <v>0.1404</v>
+        <v>0.19239999999999999</v>
       </c>
       <c r="D3" s="21">
         <f>frac_mam_6_11months * 2.6</f>
-        <v>0.14045866666666668</v>
+        <v>0.19245866666666667</v>
       </c>
       <c r="E3" s="21">
         <f>frac_mam_12_23months * 2.6</f>
-        <v>0.11062404115996258</v>
+        <v>0.16262404115996246</v>
       </c>
       <c r="F3" s="21">
         <f>frac_mam_24_59months * 2.6</f>
-        <v>5.8059717622450747E-2</v>
+        <v>0.1100597176224507</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6949,11 +7260,11 @@
       </c>
       <c r="B4" s="21">
         <f>frac_sam_1month * 2.6</f>
-        <v>0.10400000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="C4" s="21">
         <f>frac_sam_1_5months * 2.6</f>
-        <v>0.10400000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="D4" s="21">
         <f>frac_sam_6_11months * 2.6</f>
@@ -6969,7 +7280,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6xH+Dpn6un7VgESq2QYltSkucy+OJohTteitO2QsBo78MJFaKzkQDaJKxCl0fOoGa0GBL2MOk0vQtV+ikSfURw==" saltValue="lJXdIcAhpHKmQQ4oB+EoUA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6H9Em+wJh+Uhaza5Zs+IBOoc1lq1lbexdyUMrPivLlVc6nxW6duC4P5n0k0v6sRvnhJzoORq74ALEYkV/qxtVA==" saltValue="g0A6XNF4oSVb8WSokmNc/w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -8725,7 +9036,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ODQVTVPe9ia9KmL3614urMB61n7QTu/6BiGrmtrMnp73ol8QK0HXS3nxCWdJ+w+SWcfYp72tKlx6Zg4W6Cd2yA==" saltValue="TKDFvL1YekVc4Av22QkZ3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="41j5fIzL/NhcbZioi8nyWaS0K2PpBJhUxBIZAh/WpKSeyyNTeUwJAYaIQnY9WFZ/EP+y/OskWO1Zwf6XKb3zyQ==" saltValue="KHuqz2l21lsdMZFdFOmFaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -8760,7 +9071,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CnKNMk0+sHNsSE3w7qKDdCiomc3E+G0YdaKhL+15H7Lhrhr3NOubTlKJWPA8dysC8jtammFO6B5NI//mcUIM3A==" saltValue="nKfgK54MNECcV7U7frUhSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YosZLxYafyNwGThbuXQETFw0Hi4r38h9ildll7RPjE4oEfykqIAWeHU8CCYpmjN7RxVALEkS+FUF1fF0Ut/71w==" saltValue="hEysRmPB/dftNojkdSX/8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8960,7 +9271,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SaMQGX7D/HQLzReIsuxqBpLFHnIS/0fid32ddoCVYrsJj326RrszSnYDi8vX199CneYctOnMsfdszDzw5KllJA==" saltValue="puqRpilpJ5cKmZfUhrQeew==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="m00gLnn05yEKRy6pikIObOIFNSoGbGOhFZf1+/0YL+rWfFbw7PYq/J4UIEgiFhPPvwN/kYDQPs8YHfN7hCLvhA==" saltValue="izMYyCbVUgw4Fo/6UqiSyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10769,7 +11080,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+sOyrC2SmtgEpNbdCZJCp2B7G1V1caAS/8CTeGvOEg9K8/wrGvfZkUQerDm4jQr3YXGog6j6AT3p7AgMUrIYpQ==" saltValue="qQrI++mlSwcxfvJ9sJpMQQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WEC1Ltb3xvu/6WIZm+RQlzQJ37xE190ulPJ67H1fiyC3H333kMvAGlJ388IPXdhEFlxV2l9yLHC3gdwmbGbAUw==" saltValue="IMhi3/yn2dtOt5ME8g4NGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11531,7 +11842,7 @@
       <c r="K39" s="101"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dYeUc+bkN8hRwef88lEyephmy7yKvBG8vvnO3q7HikgvCSKQxvbOCKOf6ExBu/bRtRAehdmzk7u2Wtw49h4Q5g==" saltValue="bIC8SEmfbPQFcJ1jCr5p4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dwUmMkGGB9+q58qTAZ/0q3Q5p2tXiraQM20nNyi3eQ7ChHg8qtobeCtcSClB1NpH15sf75ZWI2JevTgRXrUGOw==" saltValue="Zn013j0LQbyq3M/7pm0lwg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11900,7 +12211,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="k1yJv1brA/8tFEWIirVpGcBG/oTQVGu6QrlDKZEkJ3zlJIWefgyuheiDBe1cIO2Pwn2QyZAtyxkOBpJvgKXSyw==" saltValue="qv82NSkN9Kt2kDavBJf23A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5SOUfE6plZbjCf9RZlVjlj0P0ElUDEyJncEgj9xRb2KhW9pha4e+S9PBsAzXMSHfF9cYLWREuJZhqKLU//GYuw==" saltValue="vjbdcc98EStZncGyGS97pA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12984,7 +13295,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Vnnv3UKzpJIcm9o1XHJGe26Ovc8KEhMj4elDooxYtPc8VQzEgBaa1Ml8O1BdwnLQOv4TEFYPm0bGOHBt/a4UIQ==" saltValue="DtBAGxQgPg1LRU3U1mOX/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4iIURKB1JYl5ZjY2u7Qsv3VN15MPqY9Sb4CzKpGpu0Hy6yu8A1xsJWDfkoT6BYvarKK4f7CgRS0fCLBEcOXxUQ==" saltValue="CSS16/87/9FRqOACAImkEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -13113,7 +13424,7 @@
         <v>150</v>
       </c>
       <c r="D5" s="102">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="102">
         <v>1</v>
@@ -13134,7 +13445,7 @@
         <v>149</v>
       </c>
       <c r="D6" s="102">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E6" s="102">
         <v>1</v>
@@ -13181,7 +13492,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="102">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F8" s="102">
         <v>1</v>
@@ -13202,7 +13513,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="102">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F9" s="102">
         <v>1</v>
@@ -13249,7 +13560,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G11" s="102">
         <v>1</v>
@@ -13270,7 +13581,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G12" s="102">
         <v>1</v>
@@ -13317,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H14" s="102">
         <v>1</v>
@@ -13338,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="102">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H15" s="102">
         <v>1</v>
@@ -14179,7 +14490,7 @@
         <v>149</v>
       </c>
       <c r="D56" s="102">
-        <f t="shared" ref="D56:H59" si="1">IF(D3=1,1,D3*0.9)</f>
+        <f t="shared" ref="D56:H68" si="1">IF(D3=1,1,D3*0.9)</f>
         <v>1</v>
       </c>
       <c r="E56" s="102">
@@ -14233,7 +14544,7 @@
         <v>150</v>
       </c>
       <c r="D58" s="102">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E58" s="102">
         <f t="shared" si="1"/>
@@ -14258,7 +14569,7 @@
         <v>149</v>
       </c>
       <c r="D59" s="102">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E59" s="102">
         <f t="shared" si="1"/>
@@ -14299,7 +14610,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14315,7 +14626,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="102">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F61" s="102">
         <f t="shared" si="2"/>
@@ -14326,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14340,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="102">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F62" s="102">
         <f t="shared" si="2"/>
@@ -14351,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14377,7 +14688,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14397,14 +14708,14 @@
         <v>1</v>
       </c>
       <c r="F64" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G64" s="102">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H64" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14422,14 +14733,14 @@
         <v>1</v>
       </c>
       <c r="F65" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G65" s="102">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H65" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14455,7 +14766,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14479,10 +14790,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H67" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -14504,10 +14815,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="102">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H68" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -15516,7 +15827,7 @@
         <v>149</v>
       </c>
       <c r="D109" s="102">
-        <f t="shared" ref="D109:H112" si="8">IF(D3=1,1,D3*1.05)</f>
+        <f t="shared" ref="D109:H121" si="8">IF(D3=1,1,D3*1.05)</f>
         <v>1</v>
       </c>
       <c r="E109" s="102">
@@ -15570,18 +15881,18 @@
         <v>150</v>
       </c>
       <c r="D111" s="102">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E111:G112" si="9">IF(E58=1,1,E58*0.9)</f>
         <v>1</v>
       </c>
       <c r="F111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G111" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H111" s="102">
@@ -15595,18 +15906,18 @@
         <v>149</v>
       </c>
       <c r="D112" s="102">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G112" s="102">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H112" s="102">
@@ -15620,23 +15931,23 @@
         <v>155</v>
       </c>
       <c r="D113" s="102">
-        <f t="shared" ref="D113:H123" si="9">IF(D7=1,1,D7*1.05)</f>
+        <f t="shared" ref="D113:G121" si="10">IF(D60=1,1,D60*0.9)</f>
         <v>1</v>
       </c>
       <c r="E113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H113" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15648,22 +15959,22 @@
         <v>150</v>
       </c>
       <c r="D114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E114" s="102">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H114" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15673,22 +15984,22 @@
         <v>149</v>
       </c>
       <c r="D115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E115" s="102">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H115" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15698,23 +16009,23 @@
         <v>155</v>
       </c>
       <c r="D116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H116" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15726,22 +16037,22 @@
         <v>150</v>
       </c>
       <c r="D117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F117" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H117" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15751,22 +16062,22 @@
         <v>149</v>
       </c>
       <c r="D118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F118" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H118" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15776,23 +16087,23 @@
         <v>155</v>
       </c>
       <c r="D119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H119" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15804,22 +16115,22 @@
         <v>150</v>
       </c>
       <c r="D120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G120" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H120" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15829,22 +16140,22 @@
         <v>149</v>
       </c>
       <c r="D121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G121" s="102">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H121" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -15854,23 +16165,23 @@
         <v>155</v>
       </c>
       <c r="D122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D122:H123" si="11">IF(D16=1,1,D16*1.05)</f>
         <v>1</v>
       </c>
       <c r="E122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H122" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -15882,23 +16193,23 @@
         <v>155</v>
       </c>
       <c r="D123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="E123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="F123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="G123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1.1025</v>
       </c>
       <c r="H123" s="102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -15924,19 +16235,19 @@
         <v>1</v>
       </c>
       <c r="E125" s="102">
-        <f t="shared" ref="E125:H125" si="10">IF(E19=1,1,E19*1.05)</f>
+        <f t="shared" ref="E125:H125" si="12">IF(E19=1,1,E19*1.05)</f>
         <v>1</v>
       </c>
       <c r="F125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H125" s="102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -15946,23 +16257,23 @@
         <v>149</v>
       </c>
       <c r="D126" s="102">
-        <f t="shared" ref="D126:H140" si="11">IF(D20=1,1,D20*1.05)</f>
+        <f t="shared" ref="D126:H140" si="13">IF(D20=1,1,D20*1.05)</f>
         <v>1</v>
       </c>
       <c r="E126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H126" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -15972,23 +16283,23 @@
         <v>155</v>
       </c>
       <c r="D127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H127" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16000,23 +16311,23 @@
         <v>150</v>
       </c>
       <c r="D128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H128" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16026,23 +16337,23 @@
         <v>149</v>
       </c>
       <c r="D129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H129" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16052,23 +16363,23 @@
         <v>155</v>
       </c>
       <c r="D130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H130" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16080,23 +16391,23 @@
         <v>150</v>
       </c>
       <c r="D131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H131" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16106,23 +16417,23 @@
         <v>149</v>
       </c>
       <c r="D132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H132" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16132,23 +16443,23 @@
         <v>155</v>
       </c>
       <c r="D133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H133" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16160,23 +16471,23 @@
         <v>150</v>
       </c>
       <c r="D134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H134" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16186,23 +16497,23 @@
         <v>149</v>
       </c>
       <c r="D135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H135" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16212,23 +16523,23 @@
         <v>155</v>
       </c>
       <c r="D136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H136" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16240,23 +16551,23 @@
         <v>150</v>
       </c>
       <c r="D137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H137" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16266,23 +16577,23 @@
         <v>149</v>
       </c>
       <c r="D138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H138" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16292,23 +16603,23 @@
         <v>155</v>
       </c>
       <c r="D139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H139" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16320,23 +16631,23 @@
         <v>155</v>
       </c>
       <c r="D140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H140" s="102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -16362,19 +16673,19 @@
         <v>1</v>
       </c>
       <c r="E142" s="102">
-        <f t="shared" ref="E142:H142" si="12">IF(E36=1,1,E36*1.05)</f>
+        <f t="shared" ref="E142:H142" si="14">IF(E36=1,1,E36*1.05)</f>
         <v>1</v>
       </c>
       <c r="F142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="G142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H142" s="102">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -16384,23 +16695,23 @@
         <v>149</v>
       </c>
       <c r="D143" s="102">
-        <f t="shared" ref="D143:H157" si="13">IF(D37=1,1,D37*1.05)</f>
+        <f t="shared" ref="D143:H157" si="15">IF(D37=1,1,D37*1.05)</f>
         <v>1</v>
       </c>
       <c r="E143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H143" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16410,23 +16721,23 @@
         <v>155</v>
       </c>
       <c r="D144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H144" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16438,23 +16749,23 @@
         <v>150</v>
       </c>
       <c r="D145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H145" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16464,23 +16775,23 @@
         <v>149</v>
       </c>
       <c r="D146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H146" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16490,23 +16801,23 @@
         <v>155</v>
       </c>
       <c r="D147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H147" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16518,23 +16829,23 @@
         <v>150</v>
       </c>
       <c r="D148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H148" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16544,23 +16855,23 @@
         <v>149</v>
       </c>
       <c r="D149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H149" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16570,23 +16881,23 @@
         <v>155</v>
       </c>
       <c r="D150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H150" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16598,23 +16909,23 @@
         <v>150</v>
       </c>
       <c r="D151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H151" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16624,23 +16935,23 @@
         <v>149</v>
       </c>
       <c r="D152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H152" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16650,23 +16961,23 @@
         <v>155</v>
       </c>
       <c r="D153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H153" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16678,23 +16989,23 @@
         <v>150</v>
       </c>
       <c r="D154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H154" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16704,23 +17015,23 @@
         <v>149</v>
       </c>
       <c r="D155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H155" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16730,23 +17041,23 @@
         <v>155</v>
       </c>
       <c r="D156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H156" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -16758,28 +17069,28 @@
         <v>155</v>
       </c>
       <c r="D157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H157" s="102">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NtBIRwIFOjO2Igv6B3NzMNGtLK1fjLsPFK/UmebI2EkheY1PiJS+X/I9l6NA4GqZwtBzeD5D9BYqLBSLzhfkHg==" saltValue="6PCQ0GyGhs1xyNg4yulDcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EmgU2aL3QPkumRnIZ0ZLyArdOA9sunrTQFFCzAV3La3VvMr52puM5h3EeKoRz+RaMhp0nB1k4oBNKxs5iWNX+g==" saltValue="7rEhgeKVJgtsTAuwLMfaaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -18040,14 +18351,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="D+SVSSiuH8NeX8GvkUbRALVeKtNKu11HFZ+OTmLI0CVLM36TNFG5pY0HgxIZMaiDVHvWeSI1CxTdAWghUYVzJQ==" saltValue="5IjgGYpw4c2jrIEZT1dMCw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="23ekwyoWprwnMuRcUBQ0bcABc6DpABFC8nj2b3T4Qr2P/B2isxXjsuIXcz1grID/jb549cFL0a82S9PtJZpYOQ==" saltValue="kIep0eRCAI++zMfoLQssww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
@@ -18057,7 +18368,7 @@
     <col min="1" max="1" width="27.26953125" style="27" customWidth="1"/>
     <col min="2" max="2" width="26.81640625" style="27" customWidth="1"/>
     <col min="3" max="3" width="18.26953125" style="27" customWidth="1"/>
-    <col min="4" max="8" width="14.7265625" style="27" customWidth="1"/>
+    <col min="4" max="8" width="14.81640625" style="27" customWidth="1"/>
     <col min="9" max="12" width="15.26953125" style="27" bestFit="1" customWidth="1"/>
     <col min="13" max="16" width="16.81640625" style="27" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="12.7265625" style="27"/>
@@ -19532,7 +19843,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A56" s="92" t="s">
         <v>105</v>
       </c>
@@ -19753,8 +20064,8 @@
       <c r="C66" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D66" s="103">
-        <v>1.35</v>
+      <c r="D66" s="104">
+        <v>1</v>
       </c>
       <c r="E66" s="103">
         <v>1</v>
@@ -19868,8 +20179,8 @@
       <c r="C70" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D70" s="103">
-        <v>1.35</v>
+      <c r="D70" s="104">
+        <v>1</v>
       </c>
       <c r="E70" s="103">
         <v>1</v>
@@ -19983,8 +20294,8 @@
       <c r="C74" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D74" s="103">
-        <v>1.35</v>
+      <c r="D74" s="104">
+        <v>1</v>
       </c>
       <c r="E74" s="103">
         <v>1</v>
@@ -22269,7 +22580,7 @@
       <c r="G165" s="79"/>
       <c r="H165" s="79"/>
     </row>
-    <row r="166" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
       <c r="A166" s="92" t="s">
         <v>105</v>
       </c>
@@ -22487,7 +22798,7 @@
       </c>
       <c r="D176" s="105">
         <f>IF(D66=1,1,D66*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E176" s="105">
         <f t="shared" ref="E176:G176" si="8">IF(E66=1,1,E66*0.9)</f>
@@ -22586,7 +22897,7 @@
       </c>
       <c r="D180" s="105">
         <f t="shared" si="9"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E180" s="105">
         <f t="shared" si="9"/>
@@ -22685,7 +22996,7 @@
       </c>
       <c r="D184" s="105">
         <f t="shared" si="9"/>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E184" s="105">
         <f t="shared" si="9"/>
@@ -24893,7 +25204,7 @@
       <c r="H275" s="79"/>
       <c r="I275" s="79"/>
     </row>
-    <row r="276" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A276" s="92" t="s">
         <v>105</v>
       </c>
@@ -25113,7 +25424,7 @@
       </c>
       <c r="D286" s="105">
         <f>IF(D66=1,1,D66*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E286" s="105">
         <f t="shared" ref="E286:G286" si="22">IF(E66=1,1,E66*1.1)</f>
@@ -25216,7 +25527,7 @@
       </c>
       <c r="D290" s="105">
         <f t="shared" si="23"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E290" s="105">
         <f t="shared" si="23"/>
@@ -25319,7 +25630,7 @@
       </c>
       <c r="D294" s="105">
         <f t="shared" si="23"/>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E294" s="105">
         <f t="shared" si="23"/>
@@ -26173,9 +26484,10 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/VZzj8y0LwE/VxoCQ+H6qCKtATYCqb68ZT9Ig715zr9m5+wG4vmTAVMu/Ybmg+wnryJ5ifHQxsZAozMqYTN0LQ==" saltValue="VA2cpEiv/Ws1ggCx1KfxcA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PQX+WqALGqfchqgiJf68sUW8boqC5MGl2koK6oVOD62+DgXyyohBpiVTpQS5tDSeHIMVVUqHOieVNpruNKv9HA==" saltValue="7G0m7LIFfhW7gW4Q1JQGKw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26368,7 +26680,7 @@
         <v>182</v>
       </c>
       <c r="C12" s="104">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="104">
         <v>1.39</v>
@@ -26400,19 +26712,19 @@
         <v>294</v>
       </c>
       <c r="C15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G15" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -26421,19 +26733,19 @@
         <v>291</v>
       </c>
       <c r="C16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G16" s="104">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -26563,24 +26875,19 @@
         <v>287</v>
       </c>
       <c r="C27" s="104">
-        <f>IF(C4=1,1,C4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" ref="D27:G27" si="1">IF(D4=1,1,D4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26597,7 +26904,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" ref="D29:G29" si="2">IF(D6=1,1,D6*0.9)</f>
+        <f t="shared" ref="D29:G29" si="1">IF(D6=1,1,D6*0.9)</f>
         <v>1</v>
       </c>
       <c r="E29" s="104">
@@ -26609,7 +26916,7 @@
         <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -26618,11 +26925,11 @@
         <v>305</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" ref="C30:G32" si="3">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:G32" si="2">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
@@ -26632,7 +26939,7 @@
         <v>0.85</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26641,11 +26948,11 @@
         <v>319</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
@@ -26655,7 +26962,7 @@
         <v>0.85</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26664,23 +26971,23 @@
         <v>317</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -26709,7 +27016,7 @@
         <v>303</v>
       </c>
       <c r="C35" s="104">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="D35" s="104">
         <v>1.1100000000000001</v>
@@ -26747,24 +27054,19 @@
         <v>295</v>
       </c>
       <c r="C38" s="104">
-        <f>IF(C15=1,1,C15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" ref="D38:G38" si="4">IF(D15=1,1,D15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="4"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26773,24 +27075,19 @@
         <v>292</v>
       </c>
       <c r="C39" s="104">
-        <f t="shared" ref="C39:G40" si="5">IF(C16=1,1,C16*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G39" s="104">
-        <f t="shared" si="5"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26801,23 +27098,23 @@
         <v>298</v>
       </c>
       <c r="C40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C40:G40" si="3">IF(C17=1,1,C17*0.9)</f>
         <v>1</v>
       </c>
       <c r="D40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G40" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -26912,19 +27209,19 @@
         <v>8</v>
       </c>
       <c r="D49" s="104">
-        <f t="shared" ref="D49:G50" si="6">D3*1.05</f>
+        <f t="shared" ref="D49:G49" si="4">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>183.435</v>
       </c>
     </row>
@@ -26934,24 +27231,19 @@
         <v>288</v>
       </c>
       <c r="C50" s="104">
-        <f>C4*1.05</f>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="6"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -26968,7 +27260,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" ref="D52:G52" si="7">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="5">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="104">
@@ -26980,7 +27272,7 @@
         <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -26989,11 +27281,11 @@
         <v>306</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" ref="C53:G55" si="8">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G55" si="6">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
@@ -27003,7 +27295,7 @@
         <v>0.91</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27012,11 +27304,11 @@
         <v>320</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
@@ -27026,7 +27318,7 @@
         <v>0.91</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27035,23 +27327,23 @@
         <v>318</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -27080,7 +27372,7 @@
         <v>304</v>
       </c>
       <c r="C58" s="104">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="D58" s="104">
         <v>1.74</v>
@@ -27118,24 +27410,19 @@
         <v>296</v>
       </c>
       <c r="C61" s="104">
-        <f>IF(C15=1,1,C15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" ref="D61:G61" si="9">IF(D15=1,1,D15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="9"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -27144,24 +27431,19 @@
         <v>293</v>
       </c>
       <c r="C62" s="104">
-        <f t="shared" ref="C62:G63" si="10">IF(C16=1,1,C16*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G62" s="104">
-        <f t="shared" si="10"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -27172,23 +27454,23 @@
         <v>299</v>
       </c>
       <c r="C63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C63:G63" si="7">IF(C17=1,1,C17*1.1)</f>
         <v>1</v>
       </c>
       <c r="D63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G63" s="104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -27239,7 +27521,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EwxCuQXTLhqtNsMIsSZCjMSPBF/lZ2dzOl1G/52wtAk91b+t2nOjWBAUfl7JIV3WzbqlS2ndixow8bV9atLBMg==" saltValue="EN0D6eb/ZWFY/LHaUVXUIA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wvd7Ndu0t7wCYPW1sozerGaPQ3e9KRt4EUJT2slzrOqRTRGbGxC8wAHPsgsUxKAr1eas2Vv2vtQekZZp5CvSxg==" saltValue="61sJ4fHykBdUCenSh26G2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -28060,7 +28342,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bDgA55LHnnOYlYED/NtVwQaVlI1QGvlpKfjqcRPDLfnmrLUSjQdCtDh599aneDXTvmxRCwY4UcI6Mi2puv7sJQ==" saltValue="V0AkeUJLm6m2GhyGcK1RzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AkkRwc4NFxs9vqin0MUpyymoXOSw5KhaPpY14Pm1LxjIxqytYFwI5ElvOYI2QhMpq7K4wr1P4jHXe0CCV/BfvQ==" saltValue="ogfEm6KOaL1CIUF05fH0Fw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -28136,10 +28418,10 @@
         <v>0.92</v>
       </c>
       <c r="D3" s="104">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E3" s="104">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F3" s="104">
         <v>1</v>
@@ -28721,37 +29003,37 @@
         <v>1</v>
       </c>
       <c r="E18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O18" s="104">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -28809,47 +29091,36 @@
         <v>1</v>
       </c>
       <c r="E20" s="104">
-        <f>E19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="104">
-        <f t="shared" ref="F20:O20" si="1">F19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="104">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
     </row>
@@ -28902,7 +29173,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="82" t="s">
@@ -28958,50 +29229,49 @@
         <v>0.87</v>
       </c>
       <c r="D26" s="104">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="E26" s="104">
-        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="F26:O26" si="1">IF(F3=1,1,F3*0.9)</f>
         <v>1</v>
       </c>
       <c r="G26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -29010,23 +29280,23 @@
         <v>174</v>
       </c>
       <c r="C27" s="104">
-        <f t="shared" ref="C27:O34" si="3">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O34" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="104">
@@ -29042,19 +29312,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29063,23 +29333,23 @@
         <v>175</v>
       </c>
       <c r="C28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="104">
@@ -29095,19 +29365,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29116,23 +29386,23 @@
         <v>176</v>
       </c>
       <c r="C29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="104">
@@ -29148,19 +29418,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O29" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29169,23 +29439,23 @@
         <v>177</v>
       </c>
       <c r="C30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="104">
@@ -29201,19 +29471,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O30" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29222,39 +29492,39 @@
         <v>178</v>
       </c>
       <c r="C31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K31" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L31" s="104">
@@ -29275,39 +29545,39 @@
         <v>179</v>
       </c>
       <c r="C32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K32" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L32" s="104">
@@ -29328,39 +29598,39 @@
         <v>180</v>
       </c>
       <c r="C33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K33" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L33" s="104">
@@ -29381,11 +29651,11 @@
         <v>184</v>
       </c>
       <c r="C34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E34" s="104">
@@ -29398,35 +29668,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O34" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -29479,11 +29749,11 @@
         <v>190</v>
       </c>
       <c r="C36" s="104">
-        <f t="shared" ref="C36:O38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O38" si="3">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E36" s="104">
@@ -29496,35 +29766,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O36" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29533,39 +29803,39 @@
         <v>191</v>
       </c>
       <c r="C37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K37" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L37" s="104">
@@ -29586,11 +29856,11 @@
         <v>204</v>
       </c>
       <c r="C38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E38" s="104">
@@ -29600,39 +29870,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O38" s="104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -29647,56 +29917,45 @@
         <v>171</v>
       </c>
       <c r="C41" s="104">
-        <f t="shared" ref="C41:O44" si="5">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:D44" si="4">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O41" s="104">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -29704,11 +29963,11 @@
         <v>172</v>
       </c>
       <c r="C42" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D42" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E42" s="104">
@@ -29750,56 +30009,45 @@
         <v>173</v>
       </c>
       <c r="C43" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D43" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O43" s="104">
-        <f t="shared" si="5"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -29807,11 +30055,11 @@
         <v>181</v>
       </c>
       <c r="C44" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D44" s="104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E44" s="104">
@@ -29909,50 +30157,49 @@
         <v>0.99</v>
       </c>
       <c r="D49" s="104">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="E49" s="104">
-        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F49:O49" si="5">IF(F3=1,1,F3*1.05)</f>
         <v>1</v>
       </c>
       <c r="G49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O49" s="104">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -29961,23 +30208,23 @@
         <v>174</v>
       </c>
       <c r="C50" s="104">
-        <f t="shared" ref="C50:O57" si="7">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O57" si="6">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H50" s="104">
@@ -29993,19 +30240,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O50" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30014,23 +30261,23 @@
         <v>175</v>
       </c>
       <c r="C51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H51" s="104">
@@ -30046,19 +30293,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O51" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30067,23 +30314,23 @@
         <v>176</v>
       </c>
       <c r="C52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H52" s="104">
@@ -30099,19 +30346,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O52" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30120,23 +30367,23 @@
         <v>177</v>
       </c>
       <c r="C53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H53" s="104">
@@ -30152,19 +30399,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O53" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30173,39 +30420,39 @@
         <v>178</v>
       </c>
       <c r="C54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K54" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L54" s="104">
@@ -30226,39 +30473,39 @@
         <v>179</v>
       </c>
       <c r="C55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K55" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L55" s="104">
@@ -30279,39 +30526,39 @@
         <v>180</v>
       </c>
       <c r="C56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K56" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L56" s="104">
@@ -30332,11 +30579,11 @@
         <v>184</v>
       </c>
       <c r="C57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="D57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E57" s="104">
@@ -30346,39 +30593,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O57" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30431,11 +30678,11 @@
         <v>190</v>
       </c>
       <c r="C59" s="104">
-        <f t="shared" ref="C59:O61" si="8">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O61" si="7">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E59" s="104">
@@ -30448,35 +30695,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O59" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30485,39 +30732,39 @@
         <v>191</v>
       </c>
       <c r="C60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K60" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L60" s="104">
@@ -30538,11 +30785,11 @@
         <v>204</v>
       </c>
       <c r="C61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E61" s="104">
@@ -30552,39 +30799,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O61" s="104">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -30599,56 +30846,45 @@
         <v>171</v>
       </c>
       <c r="C64" s="104">
-        <f t="shared" ref="C64:O67" si="9">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="8">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O64" s="104">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
@@ -30656,11 +30892,11 @@
         <v>172</v>
       </c>
       <c r="C65" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D65" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E65" s="104">
@@ -30702,56 +30938,45 @@
         <v>173</v>
       </c>
       <c r="C66" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D66" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O66" s="104">
-        <f t="shared" si="9"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -30759,11 +30984,11 @@
         <v>181</v>
       </c>
       <c r="C67" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D67" s="104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E67" s="104">
@@ -30801,7 +31026,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M3mT2e3wCgG3xd4LEJ5JQpp7ptzRF39w69so3HJPn82CnpMRSIao7rINcsO2P8TnytX6m693jL4eRKR3+B+b9Q==" saltValue="Emnt0kcVLe2bMGvarNhkDA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1htUzC9Cm3eouhcjf54rF+auHqthmNRuKSa12hYlYtYOYn0fYygbyvxnbDrfxIhHybsw7MHqhn2ekjyTKmu9kw==" saltValue="x/uvoQhR6DqVatR2YqfaMg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -31081,7 +31306,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="iVpfZa0L+V8UXdUtjTEI65Fz10pcho5t23F5y4n2eFZKOzJ9WlD+omA9I+zinEQLDkQd0yp+1h1R5z1ZK6WvQA==" saltValue="xMLiq74Ne/2wyl4TSwQoaA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hsiEgiWAD4q3xpZBAWbsOtfALd/7FlE/RWWJc1bVetEDWJPm93RIEnliNPJYnChW3QpyVWgVjj8WNo1OjGhpaw==" saltValue="QDrZ3GXXrKefqOHGqKYMeg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -31502,13 +31727,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_6_11months+(frac_sam_6_11months*0.89)),0),1)</f>
+        <v>0.10845784237982603</v>
       </c>
       <c r="G18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_12_23months+(frac_sam_12_23months*0.89)),0),1)</f>
+        <v>0.10901055997751219</v>
       </c>
       <c r="H18" s="104">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_24_59months+(frac_sam_24_59months*0.89)),0),1)</f>
+        <v>0.10928137311800357</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -31545,13 +31773,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_6_11months+(frac_mam_6_11months*0.89)),0),1)</f>
+        <v>0.102693699554117</v>
       </c>
       <c r="G20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_12_23months+(frac_mam_12_23months*0.89)),0),1)</f>
+        <v>0.10383415684384856</v>
       </c>
       <c r="H20" s="104">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_24_59months+(frac_mam_24_59months*0.89)),0),1)</f>
+        <v>0.10583644124371139</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -31723,19 +31954,19 @@
         <v>339</v>
       </c>
       <c r="D28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="104">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -32719,13 +32950,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_6_11months+(frac_sam_6_11months*0.99)),0),1)</f>
+        <v>9.8442967462329944E-3</v>
       </c>
       <c r="G73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_12_23months+(frac_sam_12_23months*0.99)),0),1)</f>
+        <v>9.9000452880145806E-3</v>
       </c>
       <c r="H73" s="104">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_24_59months+(frac_sam_24_59months*0.99)),0),1)</f>
+        <v>9.9273831696513604E-3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -32744,15 +32978,12 @@
         <v>0</v>
       </c>
       <c r="F74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H74" s="104">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -32769,13 +33000,16 @@
         <v>0</v>
       </c>
       <c r="F75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_6_11months+(frac_mam_6_11months*0.99)),0),1)</f>
+        <v>9.2666337588885872E-3</v>
       </c>
       <c r="G75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_12_23months+(frac_mam_12_23months*0.99)),0),1)</f>
+        <v>9.3803901376610099E-3</v>
       </c>
       <c r="H75" s="104">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_24_59months+(frac_mam_24_59months*0.99)),0),1)</f>
+        <v>9.5807489880992414E-3</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -32974,19 +33208,19 @@
         <v>339</v>
       </c>
       <c r="D83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H83" s="104">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -33975,13 +34209,16 @@
         <v>0</v>
       </c>
       <c r="F128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_6_11months+(frac_sam_6_11months*0.8)),0),1)</f>
+        <v>0.1974760415732103</v>
       </c>
       <c r="G128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_12_23months+(frac_sam_12_23months*0.8)),0),1)</f>
+        <v>0.19838146543966784</v>
       </c>
       <c r="H128" s="104">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_24_59months+(frac_sam_24_59months*0.8)),0),1)</f>
+        <v>0.19882475677586242</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -34000,15 +34237,12 @@
         <v>0</v>
       </c>
       <c r="F129" s="104">
-        <f t="shared" ref="F129:H129" si="10">IF($C74="Affected fraction",F74,IF(F74=1,1,F74*0.9))</f>
         <v>1</v>
       </c>
       <c r="G129" s="104">
-        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H129" s="104">
-        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -34025,13 +34259,16 @@
         <v>0</v>
       </c>
       <c r="F130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_6_11months+(frac_mam_6_11months*0.8)),0),1)</f>
+        <v>0.18797841604987719</v>
       </c>
       <c r="G130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_12_23months+(frac_mam_12_23months*0.8)),0),1)</f>
+        <v>0.18986558987248614</v>
       </c>
       <c r="H130" s="104">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_24_59months+(frac_mam_24_59months*0.8)),0),1)</f>
+        <v>0.19316926438997273</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -34045,7 +34282,7 @@
         <v>337</v>
       </c>
       <c r="D131" s="104">
-        <f t="shared" ref="D131" si="11">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
+        <f t="shared" ref="D131" si="10">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
         <v>1</v>
       </c>
       <c r="E131" s="104">
@@ -34100,7 +34337,7 @@
         <v>337</v>
       </c>
       <c r="D133" s="104">
-        <f t="shared" ref="D133" si="12">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
+        <f t="shared" ref="D133" si="11">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
         <v>1</v>
       </c>
       <c r="E133" s="104">
@@ -34155,7 +34392,7 @@
         <v>337</v>
       </c>
       <c r="D135" s="104">
-        <f t="shared" ref="D135" si="13">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
+        <f t="shared" ref="D135" si="12">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
         <v>1</v>
       </c>
       <c r="E135" s="104">
@@ -34230,19 +34467,19 @@
         <v>339</v>
       </c>
       <c r="D138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H138" s="104">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -34540,23 +34777,23 @@
         <v>337</v>
       </c>
       <c r="D152" s="104">
-        <f t="shared" ref="D152:H153" si="14">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
+        <f t="shared" ref="D152:H153" si="13">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
         <v>0</v>
       </c>
       <c r="E152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H152" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -34565,23 +34802,23 @@
         <v>339</v>
       </c>
       <c r="D153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H153" s="104">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -34807,7 +35044,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p6dMdLV86AN+JebQ3mjrhYOWSmomwR2J8YutIbnWVj36NwAcsFut1byLuPo7z/kdrAb+PIIi1IY/mDddFboLEA==" saltValue="FLQeBgX5dAhsYUDyHC6YHA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rI6a/tM5EOYYbN+nSThhp82W8556jNQ+a1fHE1Q/yFjw+nEiNP3qKt19xZYQHwAnyK5hOaEKxX1AXdc/n9xNPw==" saltValue="tNLAFyXjntKHtHJjMweknQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -34879,16 +35116,16 @@
         <v>339</v>
       </c>
       <c r="D3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="E3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="F3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="G3" s="104">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="H3" s="31"/>
     </row>
@@ -35200,16 +35437,16 @@
         <v>339</v>
       </c>
       <c r="D21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="F21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G21" s="104">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -35309,7 +35546,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8r0zYoaUi2imki18RaQ+86v/RQ+WMKzi0EcQrDjdLt2Rj9FAKQsAgPoyYzxfGj70S8F85AU/SEnqT+E7I+dyrQ==" saltValue="kY/OfEzRgPtThmDo90X4og==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wMQ/sp02YImBwCWIuqFoXuFgpbt+xb1+yRf3BV+zpJwilhbYu8CXQ6r/vFfGbtSyUOwLCm1zCHLaETkQTKkX4A==" saltValue="KO7XnA39Q3eU4iaFWWyFfA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -35741,7 +35978,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bpAHrOh3+BefP5WlcnHbLCytDUpS3LeSUJ9MeRFIMm84ZSKFqWRcYOlLP4ECEobjSSs02xJeMg7HyRQ01s8wow==" saltValue="sRJwPRPDwUtnAaq0VFfX8w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s7rsjq2Hq6Tt80zivrXzIPceD3fU6gD1mHPCwGcl8Oq1S8wFu6YBhhZe1ynLnA+adzISIFB6ufHdmylVPrCOqw==" saltValue="/W1HQOCyOZSgDzrZbpQs6Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -35801,15 +36038,15 @@
       </c>
       <c r="E2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.39571950531782307</v>
+        <v>0.39561189127189544</v>
       </c>
       <c r="F2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.21538848080661976</v>
+        <v>0.21320949938660438</v>
       </c>
       <c r="G2" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.20291379751882221</v>
+        <v>0.20249364172902928</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35826,15 +36063,15 @@
       </c>
       <c r="E3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.37328049468217694</v>
+        <v>0.37330306774449845</v>
       </c>
       <c r="F3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.3686115191933802</v>
+        <v>0.36787379495125261</v>
       </c>
       <c r="G3" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.36408620248117773</v>
+        <v>0.36392076328140976</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35848,13 +36085,13 @@
         <v>0.107</v>
       </c>
       <c r="E4" s="59">
-        <v>0.154</v>
+        <v>0.154430327868852</v>
       </c>
       <c r="F4" s="59">
-        <v>0.26400000000000001</v>
+        <v>0.26673186710341601</v>
       </c>
       <c r="G4" s="59">
-        <v>0.27900000000000003</v>
+        <v>0.27929610299234497</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35868,13 +36105,13 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="E5" s="59">
-        <v>7.6999999999999999E-2</v>
+        <v>7.6654713114754094E-2</v>
       </c>
       <c r="F5" s="59">
-        <v>0.152</v>
+        <v>0.152184838558727</v>
       </c>
       <c r="G5" s="59">
-        <v>0.154</v>
+        <v>0.15428949199721601</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35902,23 +36139,23 @@
       </c>
       <c r="C8" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.6241955901533508</v>
+        <v>0.54287526907834005</v>
       </c>
       <c r="D8" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.6241955901533508</v>
+        <v>0.54287526907834005</v>
       </c>
       <c r="E8" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.68355843805440353</v>
+        <v>0.63394133132364583</v>
       </c>
       <c r="F8" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.73228840888273117</v>
+        <v>0.6759433871062428</v>
       </c>
       <c r="G8" s="114">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.81212055177975573</v>
+        <v>0.74154276352799009</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35927,23 +36164,23 @@
       </c>
       <c r="C9" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE) - SUM(C10:C11), "")</f>
-        <v>0.28180440984664923</v>
+        <v>0.32312473092165994</v>
       </c>
       <c r="D9" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE) - SUM(D10:D11), "")</f>
-        <v>0.28180440984664923</v>
+        <v>0.32312473092165994</v>
       </c>
       <c r="E9" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE) - SUM(E10:E11), "")</f>
-        <v>0.2466938696379041</v>
+        <v>0.27631097636866186</v>
       </c>
       <c r="F9" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE) - SUM(F10:F11), "")</f>
-        <v>0.21506846670192739</v>
+        <v>0.25141348847841583</v>
       </c>
       <c r="G9" s="114">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE) - SUM(G10:G11), "")</f>
-        <v>0.15821429221536368</v>
+        <v>0.20879208046712927</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35951,19 +36188,19 @@
         <v>107</v>
       </c>
       <c r="C10" s="59">
-        <v>5.3999999999999999E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="D10" s="59">
-        <v>5.3999999999999999E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="E10" s="59">
-        <v>5.4022564102564105E-2</v>
+        <v>7.4022564102564095E-2</v>
       </c>
       <c r="F10" s="59">
-        <v>4.2547708138447146E-2</v>
+        <v>6.2547708138447095E-2</v>
       </c>
       <c r="G10" s="59">
-        <v>2.2330660624019519E-2</v>
+        <v>4.2330660624019502E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -35971,10 +36208,10 @@
         <v>119</v>
       </c>
       <c r="C11" s="59">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D11" s="59">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E11" s="59">
         <v>1.5725128205128207E-2</v>
@@ -36160,7 +36397,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xyWRv/UFDUjmvCnPI5Xb7MD1BwQmOusBE0PcMtQTFMvyRVzZctZRJsyIDHHBqepEDBnWXOkGGXykE7J0y091Kg==" saltValue="LWauj1x43RPx69LRrz4ROA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pyhjPjQReeUZ2f/0D9g5sMRojFujXOQLtwqcbFpDZaPrZA4EzGy2HC3DjiUjsmWwLdDBwXi0GrtHE5qyzXedeg==" saltValue="ErflAZ8XYoFyP86E9UYvoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -36292,7 +36529,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ldtr8wddbhqBfwniTN/bGAjEL7vgR/tHgEJnThKdBHEMnCT1g0JPx2u0wV9dFG6a3385B+kkj/R/PgX9jXHyfg==" saltValue="vRpVIfrSJnLkJTSDsNfwCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oUDLAqcFKDt9XWZjd8qBLHLt3NHQwEMMiiJDIRzaf8bvgPSEuiaVT/We6cYRKCDvyLVWKMzKfN5kECxLOr+JZg==" saltValue="tx33IVhtrw7mBcRKIAYSsw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36494,7 +36731,7 @@
       <c r="K14" s="115"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4TP/ozqnSWfXBvOjJTHvgf+2WsPBSgaHFuZqUnmdwXsMNT8UXCjTvpEkUbdf+LjPsjAYwsSb4zrljrMqpB86UA==" saltValue="PlAFXmzGj5iYOvxyZWc1Zw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LVTRo1oYO3DvHBo6sEAdQgxKn7nv/undyCkRxNZTOU0qFyeqkuphkU0Wvo63VTXVbaIZTOfYoPQFvCAd7hCy/g==" saltValue="Sk2K/Iqkh7toc9TcerZ3sw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -36570,7 +36807,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tIJZ4LD0IZTehx7+PZByTqiQYSzp9Q5zPeFLHUOw399tN0s0it4CjeSVO2jRaeJObgLQiiOFP65MiZ/A6bhZ+g==" saltValue="cYrU/CjFKwsKbwDLYDcX8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SP5Dh/ouVJnKPcb6yJ2vIlvxgoqog8a+nChZO0/Bk9f+t7h+Shx81+3fci9ozWd2GO9hGlpYNnFgQzuxYvnugg==" saltValue="sTHN8WNWRXHI4CU0baBvww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -36825,7 +37062,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UhvFX5BLXyh3MdbKMjxfEOdrd2MGLRWPGb8d9LuNP7PkYo2QEi0pHkhSa3aInmjWnl0zWqQqWcpfEp0ecdxFFw==" saltValue="evnJT5/GNnE4YbRhr4vaYA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ydxRJX34UVGR86hpLnk/yJv1bhcqYncl6KSjAxL+upgllJFlzK6qDrg0Y+1X8nTXB9j2THj7D+vT1Kx7py1ifw==" saltValue="QGEwH6R7CpbJaEXzQqdIAw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -36884,7 +37121,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2zYQqZEcvo/lG8zg6ok0Yeeg8j5rM5sRLdZ8a4HvuN5mgf97r8rL4CnNZeg6I4MgddoXuTfIp2xYBuKT65GOQg==" saltValue="UXx2D061D9Cg6OntI9KwGQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GbcduoTAJrDoeafXGiSAH7tIP7dkj8KVp41Z8CDGwnLKawohS1YG+h/RuTr3uNkXROswMO+mfa4BtNynirCh2Q==" saltValue="HvEIXUh0w4Zj29LIpCrSHA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/es/demo_region3_input.xlsx
+++ b/inputs/es/demo_region3_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47A79DA4-22FE-4F07-AACF-354C0DA1F37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655284AA-B5BA-4FA6-9261-EC40C9BC70B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10180" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Distribución estado nutricional" sheetId="5" r:id="rId4"/>
     <sheet name="Distribución de lactancia" sheetId="50" r:id="rId5"/>
     <sheet name="Tendencias temporales" sheetId="75" r:id="rId6"/>
-    <sheet name="Variables económicas   " sheetId="76" r:id="rId7"/>
+    <sheet name="Variables económicas" sheetId="76" r:id="rId7"/>
     <sheet name="Paquetes de IYCF" sheetId="55" r:id="rId8"/>
     <sheet name="Tratamiento de la MAS" sheetId="60" r:id="rId9"/>
     <sheet name="Costo y cobertura del programa" sheetId="56" r:id="rId10"/>
@@ -11686,7 +11686,7 @@
     <col min="8" max="16384" width="14.453125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="39" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
         <v>192</v>
       </c>
@@ -22834,12 +22834,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="OOm6nRrfkprxzThu4Vk0eZ8tKEiLVdAwOmDuXXVBJ6/ByHDJ7IXLTDsPlTsvDuqQ7o/5KbzROGOEp5LUhDwoUA==" saltValue="QzqIRqpP29hML2TeeD3Csw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -22849,36 +22873,12 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -25585,7 +25585,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="92" t="s">
         <v>124</v>
       </c>
@@ -28322,7 +28322,7 @@
       <c r="G165" s="79"/>
       <c r="H165" s="79"/>
     </row>
-    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A166" s="92" t="s">
         <v>124</v>
       </c>
@@ -30946,7 +30946,7 @@
       <c r="H275" s="79"/>
       <c r="I275" s="79"/>
     </row>
-    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A276" s="92" t="s">
         <v>124</v>
       </c>
@@ -35113,7 +35113,7 @@
       <c r="N23" s="121"/>
       <c r="O23" s="121"/>
     </row>
-    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="52" x14ac:dyDescent="0.3">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="122" t="s">
@@ -36056,7 +36056,7 @@
       <c r="N46" s="121"/>
       <c r="O46" s="121"/>
     </row>
-    <row r="47" spans="1:15" ht="26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="52" x14ac:dyDescent="0.3">
       <c r="A47" s="29"/>
       <c r="B47" s="29"/>
       <c r="C47" s="122" t="s">

--- a/inputs/es/demo_region3_input.xlsx
+++ b/inputs/es/demo_region3_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655284AA-B5BA-4FA6-9261-EC40C9BC70B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B17A955-6F76-4C21-8A33-A4A4322F58D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -2910,7 +2910,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{3B583BF4-0EF6-4900-A9DE-A70CE96445F7}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{0E21E312-5284-47EE-AD0E-6B1F7C858E75}">
       <text>
         <r>
           <rPr>
@@ -2924,7 +2924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{DB26C487-C236-4843-BCC9-67811F7468CB}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{3CE91DD0-0D69-40B3-B791-151F73F78778}">
       <text>
         <r>
           <rPr>
@@ -2938,7 +2938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{952BB287-57C9-47D6-9337-3B520ADF068D}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{1BCF1FF3-6563-4B3C-97B4-41D2942D5622}">
       <text>
         <r>
           <rPr>
@@ -2952,7 +2952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{C47538FA-20F3-4291-98F5-556B265A7656}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{CC8EBA3B-2CE7-47D1-B946-E65D9D137F8E}">
       <text>
         <r>
           <rPr>
@@ -2966,7 +2966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{D770E6AC-5175-4560-B670-91F17DB93430}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{F1277F3E-238E-4430-8668-4C49FEAB9881}">
       <text>
         <r>
           <rPr>
@@ -2980,7 +2980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{F473B3C0-710C-4186-8DEB-68FEF90CA8E9}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{3144D64E-BB28-41E2-9779-08D0DD66973C}">
       <text>
         <r>
           <rPr>
@@ -2994,7 +2994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{D20C7F37-E201-4045-9252-6C02D218CAE3}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{16914398-887C-4DA1-89A7-698EB93D17AE}">
       <text>
         <r>
           <rPr>
@@ -3008,7 +3008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{F792B940-DBED-4508-BE34-C9E3EC633577}">
+    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{D979CE02-6E44-4A29-8262-FB30971286B8}">
       <text>
         <r>
           <rPr>
@@ -3022,7 +3022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{3C6321E6-3445-47EC-A207-3F624F0E6D43}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{E08CBB4B-EF9A-427E-A111-853344BBFDFD}">
       <text>
         <r>
           <rPr>
@@ -3036,7 +3036,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{9ABE3370-C1FA-4290-A444-5106D3962806}">
+    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{45D2850C-7E55-44C6-991B-B25310E9B0F8}">
       <text>
         <r>
           <rPr>
@@ -3050,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{E613B17F-28D4-452E-8251-EB5545E21C16}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{A1E55BFC-57B7-47A2-A54E-F6E3797C914D}">
       <text>
         <r>
           <rPr>
@@ -3064,7 +3064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{250DAAAE-B921-4E5D-93A4-C8559F1C6595}">
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{99CFF617-DAFC-4B28-BAFD-FBFA1504F3DD}">
       <text>
         <r>
           <rPr>
@@ -3078,7 +3078,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{C692F5BC-9242-4398-875F-EFB21EC98913}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{ED4DABD3-2BEA-433B-BDCA-397566F80411}">
       <text>
         <r>
           <rPr>
@@ -3092,7 +3092,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{97A60E98-20A4-4C1D-A096-A7A88B61E6E6}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{3054DDB8-F190-4173-94F2-92C374B9CC09}">
       <text>
         <r>
           <rPr>
@@ -3106,7 +3106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{B7A62F8F-C655-44DF-92C3-311B9FF08BF8}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{57798CEA-F92E-4290-9FA0-1D0F40644889}">
       <text>
         <r>
           <rPr>
@@ -3120,7 +3120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{877EEFE7-CF37-4AB8-8125-034C9E25DF8A}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{598F0FA3-6C3A-4446-9623-0FD1E78918F2}">
       <text>
         <r>
           <rPr>
@@ -3134,7 +3134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{920D6387-A5A2-4EB0-B763-3746954F1DC8}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{112BF811-F3CB-4FC2-9F1B-3C21B047AD91}">
       <text>
         <r>
           <rPr>
@@ -3148,7 +3148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{110B8BCC-A18F-4482-9706-214A33C1D035}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{FE8E42B1-9B4E-49EE-B6C8-F67DAA2B5642}">
       <text>
         <r>
           <rPr>
@@ -3162,7 +3162,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="1" shapeId="0" xr:uid="{9311E7C8-6DF9-441C-9F8D-E21702435127}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{9EA94BB8-C02E-471E-A42C-5489646EB345}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Until clear effect evidence is found, assume no effect</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{6F8F532E-AC6F-4473-B83F-03B541B5FC46}">
       <text>
         <r>
           <rPr>
@@ -3176,7 +3200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{77FA98D7-61BE-429E-A5AA-428007243040}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{F01866B1-DEB5-46F1-AB62-28A4273A0B0A}">
       <text>
         <r>
           <rPr>
@@ -3190,7 +3214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{93CC1998-BFB8-4B62-BCB5-E1BBBACE6830}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{F37CACC5-5CBC-4A6A-A6EF-BA406A9E1583}">
       <text>
         <r>
           <rPr>
@@ -3205,7 +3229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{EF338D2F-A208-4CE3-B808-8AC74AF8E5EF}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{BA5B34C2-0A3F-4F80-95F6-64D24385C473}">
       <text>
         <r>
           <rPr>
@@ -3220,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{CAAEA887-57C5-43F3-9495-1DEB3D5679A3}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{8BCB1780-915E-40CA-AFE6-BA754FE5968E}">
       <text>
         <r>
           <rPr>
@@ -3235,7 +3259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="1" shapeId="0" xr:uid="{0135FFD5-224E-44D6-89F4-8E19B3F26984}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{E70D4D62-2A75-48AB-B89D-5A02A2738D92}">
       <text>
         <r>
           <rPr>
@@ -3250,7 +3274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E28" authorId="1" shapeId="0" xr:uid="{087D42A2-DDA0-4EED-96A0-F816CA261B2B}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{5C905BC4-6109-47E8-8479-31286E90D5BE}">
       <text>
         <r>
           <rPr>
@@ -3265,7 +3289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{26E7E445-DC62-4BD8-9BA3-94D1A3A915FA}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{2DC92E3C-9C59-4C4E-B582-7D2DEDCCE893}">
       <text>
         <r>
           <rPr>
@@ -3280,7 +3304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="1" shapeId="0" xr:uid="{288E52AB-6BF7-4AAB-9108-064316FD5C9A}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{CA7D52E1-FCC2-46F6-AC73-961F3446743F}">
       <text>
         <r>
           <rPr>
@@ -3295,7 +3319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="1" shapeId="0" xr:uid="{4799CEDE-3E07-4F5C-A7FD-D476484E84ED}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{684EF6D2-CED1-4D40-AF2E-917A5EE4F809}">
       <text>
         <r>
           <rPr>
@@ -3310,7 +3334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{8393718F-9D1E-4E53-BC37-5F6B053D0601}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{C84A5B5A-61F6-4E8F-9E0F-B525A8D33045}">
       <text>
         <r>
           <rPr>
@@ -3324,7 +3348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{AAB9CB4B-0B96-4D0C-83ED-BB195F323ED5}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{F1797476-979C-4AA4-B329-E94E4115D01F}">
       <text>
         <r>
           <rPr>
@@ -3338,7 +3362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{D95C0DFF-F126-4A4C-9069-F298BF3D5946}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{53B5AA46-37DF-40EA-9D39-87B3B8D9E1C4}">
       <text>
         <r>
           <rPr>
@@ -3352,7 +3376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G43" authorId="0" shapeId="0" xr:uid="{B5844301-F8EC-4F3A-9817-196B9209D97A}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{F92AA795-608B-40DD-8AA4-6147B4791958}">
       <text>
         <r>
           <rPr>
@@ -3366,7 +3390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H43" authorId="0" shapeId="0" xr:uid="{8686E6B8-3CF0-48DD-94B5-57FC95305DFC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{8D2FAE20-99A2-45F5-8577-C76F5C8F57AE}">
       <text>
         <r>
           <rPr>
@@ -3380,7 +3404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{C0D7BB50-1552-4541-B85E-2A739302DB38}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{939F8845-9FFB-4B5E-8EB8-3423C1245875}">
       <text>
         <r>
           <rPr>
@@ -3394,7 +3418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{22CC649A-F611-4A6F-B169-34E4FCE004EA}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{7D9F4DFB-B288-4077-B027-4AF5C0D2F956}">
       <text>
         <r>
           <rPr>
@@ -3408,7 +3432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{070F384F-6483-4AC9-B7ED-38B4F2DDA14C}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{3531AB6A-FE00-4535-975A-30654AD46785}">
       <text>
         <r>
           <rPr>
@@ -3422,7 +3446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G44" authorId="0" shapeId="0" xr:uid="{D9E9C5B2-783C-4AF8-B771-863C5ACC6ACE}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{1943F941-C35E-42E4-88B9-E72EECC90D56}">
       <text>
         <r>
           <rPr>
@@ -3436,7 +3460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H44" authorId="0" shapeId="0" xr:uid="{5DCCDA08-9FDA-4BEA-A37F-1CAF7C50C05D}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{C8C6E747-33AD-41A1-8BA0-C6EBEAB51708}">
       <text>
         <r>
           <rPr>
@@ -3450,7 +3474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{87CE9237-E7B9-4256-B0F4-6398C8974F6E}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{A01569FA-98BE-494E-AA71-8678904732E7}">
       <text>
         <r>
           <rPr>
@@ -3465,7 +3489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E47" authorId="0" shapeId="0" xr:uid="{EF251290-B9E3-4088-98E7-8E0EE3F64386}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{06ACA698-E8FC-49E8-96B0-4058CC8BFDD5}">
       <text>
         <r>
           <rPr>
@@ -3480,7 +3504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{F831ED86-2646-4AD8-91A7-5E7B52E7541C}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{D80A217D-143F-4B80-A377-997DD2A73EEE}">
       <text>
         <r>
           <rPr>
@@ -3495,7 +3519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{7A6102BC-F1AA-426A-9F94-322B5CF717CA}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{4E31EEB4-D3AC-4D17-9385-A3099E2DCBDD}">
       <text>
         <r>
           <rPr>
@@ -3510,7 +3534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H47" authorId="0" shapeId="0" xr:uid="{15DD3F71-E83E-420A-A0B2-E33077CAC167}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{639D5D68-FD72-4082-9C88-0FB519E3B06A}">
       <text>
         <r>
           <rPr>
@@ -3525,7 +3549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{86C0A37B-7F6B-4635-AB9E-E73E6F45A238}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{DBB8DB45-78BB-445C-9E3C-A05786DD4217}">
       <text>
         <r>
           <rPr>
@@ -3541,7 +3565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{D0AA5939-B07B-454D-93E1-5439F3EF05BF}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{18A5EEAD-5494-4F9C-973E-FD23F1382692}">
       <text>
         <r>
           <rPr>
@@ -3557,7 +3581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{A2526AAA-C8D4-4BC4-B08F-A93419C9A866}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{EBC8C955-B3F7-4CEC-96C5-0149CCB9ED9F}">
       <text>
         <r>
           <rPr>
@@ -3573,7 +3597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{ED88F435-71AC-4D5D-A328-7673C102E0CA}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{BE023C7D-2462-48C5-B6C2-9B18F3738A32}">
       <text>
         <r>
           <rPr>
@@ -3589,7 +3613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{A7B2D29D-5B87-412D-8065-663376F457DD}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{59C90B3D-6CCE-4359-BAE3-ECB32EC364D1}">
       <text>
         <r>
           <rPr>
@@ -3605,7 +3629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{BD15B3BB-7B50-4253-82FE-9DEF1EEBAC5D}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{6C9B27F9-C683-40E4-B05C-2DD2BE2DECC9}">
       <text>
         <r>
           <rPr>
@@ -3620,7 +3644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{E2E384F1-E5BF-4AF5-B4AB-048D4F77BBDC}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{A4BEAE24-B9F5-49DF-93BD-5907E779E5E3}">
       <text>
         <r>
           <rPr>
@@ -3635,7 +3659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{D4213AC5-2500-4F01-B3FC-2F4D8787D30C}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{6D8EAAAC-4468-431F-ADE3-D35134CB62E6}">
       <text>
         <r>
           <rPr>
@@ -3650,7 +3674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{3607F6EA-97FE-48B6-AFFB-F689044AA3C1}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{EFC32373-895A-4B5A-9ED3-D2D801EA1B49}">
       <text>
         <r>
           <rPr>
@@ -3665,7 +3689,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{5D8A957C-01EA-4249-B9A1-69B9F32F608E}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{C288D36F-9C49-4337-8632-0ECD0875F117}">
       <text>
         <r>
           <rPr>
@@ -3680,7 +3704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="1" shapeId="0" xr:uid="{412926CC-5A0B-457A-8988-74ABB8BCE8AD}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{AC7C6FC6-AE72-49CC-9C45-489232EB76ED}">
       <text>
         <r>
           <rPr>
@@ -3694,7 +3718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{44BEB1FC-80EA-40A2-A377-0E76FBE8C2D0}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{8D586D4E-1737-40D5-BEFA-663E2FFEF507}">
       <text>
         <r>
           <rPr>
@@ -3708,7 +3732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{6F468163-C302-40D7-9F7C-D271694799E9}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{5C31A1C4-B867-4DFC-A7D1-D57036257514}">
       <text>
         <r>
           <rPr>
@@ -3722,7 +3746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{CED83395-DD57-4867-AD1D-3D938938DD9A}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{684ED7FF-1FB7-4B01-BA3A-7E4ABA94E5EA}">
       <text>
         <r>
           <rPr>
@@ -3736,7 +3760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{5642B808-E3E5-41D6-B03D-93D57C960EFD}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{835E9660-1EF5-455E-978D-D543BDFE9A8C}">
       <text>
         <r>
           <rPr>
@@ -3750,7 +3774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{042CAAA7-648F-4928-8B52-16C52C1CB9F8}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{0E9F30B8-8F69-4FA3-B5EC-87310625BDD1}">
       <text>
         <r>
           <rPr>
@@ -3764,7 +3788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H59" authorId="0" shapeId="0" xr:uid="{9BA6A879-065C-4211-B29E-6899A259625C}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{D1098C46-BD19-4681-8488-8EF64689556E}">
       <text>
         <r>
           <rPr>
@@ -3778,7 +3802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="1" shapeId="0" xr:uid="{565D6423-01E0-47AE-A062-7832C4E375C5}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{85AC6454-39F1-4BB0-9861-59DA3B013423}">
       <text>
         <r>
           <rPr>
@@ -3792,7 +3816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="1" shapeId="0" xr:uid="{A2040727-4AFC-4417-8173-7FB0863C5CBD}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{87D4E0B4-790D-4153-9B6E-9A670FCC7BE2}">
       <text>
         <r>
           <rPr>
@@ -3806,7 +3830,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{6AA85311-F8C0-49FB-8E21-7376530BDE97}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{D508E260-868D-4E4C-88AF-6B27FAA2BAFA}">
       <text>
         <r>
           <rPr>
@@ -3820,7 +3844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{3374B95E-CE9A-4D2E-9C9D-BFBA7E40C0B8}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{2B7807B8-233A-4648-A8AE-0FDBD3D0764F}">
       <text>
         <r>
           <rPr>
@@ -3834,7 +3858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{2F6B7874-ED49-4990-8F59-FA104F498ACF}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{7931FD69-CED2-48D4-8417-B715316EDDED}">
       <text>
         <r>
           <rPr>
@@ -3848,7 +3872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{9281230B-7F13-4BF3-A15E-5C91DC580EB9}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{850A57CC-BF66-463A-B038-E225C813F534}">
       <text>
         <r>
           <rPr>
@@ -3862,7 +3886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{265BA4C5-B482-4466-9EE5-DE8BF4B05171}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{115BC45F-8F77-49A7-8C0F-A24709FD5BC0}">
       <text>
         <r>
           <rPr>
@@ -3876,7 +3900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{31729F40-4AEA-4429-AE4C-44E7C56D5A06}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{245BAAF3-0BFB-4AD3-94CC-E570C934ECFC}">
       <text>
         <r>
           <rPr>
@@ -3890,7 +3914,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{40FCD69E-E273-45F9-AD9C-D85ADC8881D3}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{C50A6EE9-7977-479B-A36F-D948E109FB78}">
       <text>
         <r>
           <rPr>
@@ -3904,7 +3928,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{574F8A5E-D331-4E39-AF86-D500131B6BD8}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{90A5940D-EFEF-4091-9ABB-5CDFB3D8ED00}">
       <text>
         <r>
           <rPr>
@@ -3918,7 +3942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{D8C1EC10-412B-4103-8C9F-F26240D6EA92}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{A23A3784-14E8-4E0F-83B5-FA6272DF98F4}">
       <text>
         <r>
           <rPr>
@@ -3932,7 +3956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0623E9F4-682F-42D6-BB68-F47E7264F4A0}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{AAFBB65D-7C9B-471D-A627-08C81EAE313A}">
       <text>
         <r>
           <rPr>
@@ -3946,7 +3970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{35D28F66-4ED6-4803-A236-4854CEC56423}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{64AE9CC1-9689-4D94-84D1-57FFA5EDB305}">
       <text>
         <r>
           <rPr>
@@ -3961,7 +3985,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{1B9AA6C2-E8E3-42A6-8C99-E7CB524687D7}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{C81C4855-ED0A-4DA8-9A93-AC1DE967BE53}">
       <text>
         <r>
           <rPr>
@@ -3976,7 +4000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{75F6BF46-ED4F-4722-B92B-9CA93DEC07A7}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{D5037819-EC04-4545-BDDE-9A94C02F30A5}">
       <text>
         <r>
           <rPr>
@@ -3991,7 +4015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{23D5BD1C-E21E-484D-B255-C1DFA4048ED1}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{02D239B4-A767-46D1-965B-9754CB6E1D64}">
       <text>
         <r>
           <rPr>
@@ -4006,7 +4030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{1AF8F7AB-5D3C-4F8F-B525-26B903297536}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{1E87513A-00A3-489B-975C-32F2D2706789}">
       <text>
         <r>
           <rPr>
@@ -4021,7 +4045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="1" shapeId="0" xr:uid="{E259BDDF-039F-45BC-9F58-6D46E98C9816}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{BFFCC65B-1D52-4266-A41B-8F11CA933A4E}">
       <text>
         <r>
           <rPr>
@@ -4036,7 +4060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E83" authorId="1" shapeId="0" xr:uid="{3106F71E-119F-491A-8533-0339B6FF1A50}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{CC0A9E9F-5340-4261-9869-3175D8D88E69}">
       <text>
         <r>
           <rPr>
@@ -4051,7 +4075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F83" authorId="1" shapeId="0" xr:uid="{E2C10219-0353-498A-A3D2-FF6CC2144909}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{C14396FC-850B-441C-BCB7-DA0D83B195CA}">
       <text>
         <r>
           <rPr>
@@ -4066,7 +4090,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G83" authorId="1" shapeId="0" xr:uid="{A7D9DA6B-332D-41A5-84EC-DD96731D452A}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{1919809B-3465-4421-A79B-674A31095283}">
       <text>
         <r>
           <rPr>
@@ -4081,7 +4105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H83" authorId="1" shapeId="0" xr:uid="{6B6B8972-68C2-42CC-B8BF-FA49C3091C8A}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{F1E1B4DC-49A0-4FAC-9FD7-04B5AF5F2482}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0" xr:uid="{DEBAE134-2B56-4018-A42F-24680B56D64A}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{D73AFD98-062C-4F23-B74C-23E762CBE9BB}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0" xr:uid="{23DD1570-2BBD-4337-B53F-9F651BBDEFF3}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{7D592B1A-E533-4D64-97F4-5ED1FB22E2B3}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0" xr:uid="{BAD62E7A-3F80-48DF-B0D5-DDED4DF5386C}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{226850EC-4597-4861-AC41-D6740BAF2DE2}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G99" authorId="0" shapeId="0" xr:uid="{35FB1CFC-F274-4B88-906F-154D53F8CB00}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{27A045F1-8DFF-49F9-AD69-8ED90C3ABF42}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H99" authorId="0" shapeId="0" xr:uid="{7AC31835-F6B4-4D56-B100-048A495E78FC}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{696AEDA0-A7EF-41A5-8DED-3DEF02C7E239}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{48D4A664-87D5-4D1F-B8F7-E15EFB01A5C0}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{3C4B2EA6-1E8B-4E48-8831-80C4CBFE03F7}">
       <text>
         <r>
           <rPr>
@@ -4181,7 +4205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0" xr:uid="{8846AEC1-EB5A-4BE7-BCF6-04754BF83056}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{A7FDD18D-2823-48EE-9A73-83C7FD8E08BC}">
       <text>
         <r>
           <rPr>
@@ -4196,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0" xr:uid="{2B2BADA3-43AE-4E0C-8AB8-9039C5E80A06}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{AC0DD932-BD6C-430E-BDDC-6AA23F778B21}">
       <text>
         <r>
           <rPr>
@@ -4211,7 +4235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{36540EE3-5D09-4E35-B1C8-1ECD214C4750}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{46A885BC-2EE6-4152-A961-65F0E9BCA490}">
       <text>
         <r>
           <rPr>
@@ -4226,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H102" authorId="0" shapeId="0" xr:uid="{780B86AF-212A-4888-BB06-B31872654F00}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{34672723-4F3D-4E81-957E-2D7B9382C73F}">
       <text>
         <r>
           <rPr>
@@ -4241,7 +4265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0" xr:uid="{6A58E3BA-ABDD-4DF7-80BD-49A331A247C1}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{CA608B37-EEF2-4A17-BA30-1DB7E100B190}">
       <text>
         <r>
           <rPr>
@@ -4257,7 +4281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0" xr:uid="{9DD7F15B-9294-49B7-9959-F2D5E8EEFBFD}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{C2DD496B-C666-490D-A51C-D213D4EA6157}">
       <text>
         <r>
           <rPr>
@@ -4273,7 +4297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0" xr:uid="{33668BAB-AEDA-46A5-B6D9-E02930970AB5}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{10C4DD09-11EA-4A3C-BBFD-1A88AD0323FC}">
       <text>
         <r>
           <rPr>
@@ -4289,7 +4313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G104" authorId="0" shapeId="0" xr:uid="{DA4B34E5-4F18-4451-8CD9-C426C43A25EC}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{782F2ECC-69FC-49C5-94A1-493FEA291DF0}">
       <text>
         <r>
           <rPr>
@@ -4305,7 +4329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0" xr:uid="{3014986A-A482-4CFA-AD26-BF3706F3E892}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{9E48CF13-9F1E-4AD7-9F0D-B6A75E54AE20}">
       <text>
         <r>
           <rPr>
@@ -4321,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{75E7F49B-310A-447A-8ADF-EF511931023E}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{E4CFE502-4C36-4624-9745-8A2D9634B817}">
       <text>
         <r>
           <rPr>
@@ -4336,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E164CB8D-3C40-4D8A-84A8-3F8A07364EF6}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{7964B084-8F7E-4949-B969-0B3A340FF956}">
       <text>
         <r>
           <rPr>
@@ -4351,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{BB0B4186-80E5-4EEC-96AB-DB35514465A2}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{8FE91EFF-8834-43D0-9E03-E9DD2FC332C9}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E0C637E4-020C-4C67-AC99-39A5E8CA7CB5}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{488AE239-0C63-4041-B81E-B82D820902D0}">
       <text>
         <r>
           <rPr>
@@ -4381,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{D1456B7B-6C16-4BA5-8D14-3EF959BCB090}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{84C7379F-1012-44D4-9826-8DAC159D44F3}">
       <text>
         <r>
           <rPr>
@@ -4396,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="1" shapeId="0" xr:uid="{70887060-8F15-4389-BEF3-44B3C31D441D}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{473D8D25-9F40-44B9-AB6B-527BB4D0730F}">
       <text>
         <r>
           <rPr>
@@ -4410,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F113" authorId="0" shapeId="0" xr:uid="{E956E280-885D-43E2-8987-C6EECC5CA377}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{45E6B7D4-8C3C-456C-979F-492FB9CB58A0}">
       <text>
         <r>
           <rPr>
@@ -4424,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{5169C578-9E37-44F7-8D68-EFE6C44320E3}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{665DBA0B-A179-42A3-A78C-7712B074D996}">
       <text>
         <r>
           <rPr>
@@ -4438,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{88882124-535A-47B0-A04F-4D7A84CA192F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{CB45F1F9-DADA-4E17-AD02-3DC0D5116921}">
       <text>
         <r>
           <rPr>
@@ -4452,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F114" authorId="0" shapeId="0" xr:uid="{0478BDF9-30D0-45EA-884D-3922C12787E1}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{48D72F81-FA83-45A5-B7E0-D4F767169788}">
       <text>
         <r>
           <rPr>
@@ -4466,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{DA315D78-6983-47D7-AE51-1D117C78E1D2}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{EB967D55-3F49-4CF3-827D-0FD4065F035C}">
       <text>
         <r>
           <rPr>
@@ -4480,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{F7F565BF-40D4-477B-BA08-889762E1B1E5}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{8A5631DF-221F-4B53-A146-6732065087E6}">
       <text>
         <r>
           <rPr>
@@ -4494,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F116" authorId="1" shapeId="0" xr:uid="{DB71F7C1-336A-45E3-963D-847FA568D415}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{3FB9F799-4D45-4904-8DB4-7013BECB0AF9}">
       <text>
         <r>
           <rPr>
@@ -4508,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G116" authorId="1" shapeId="0" xr:uid="{522309E7-7A0B-472F-8064-C29F3FB505F1}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{9F4B02BA-8149-4077-9810-886EB9281379}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="1" shapeId="0" xr:uid="{B3735AF6-982F-47B2-BE1D-6FBBB633F3F8}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{D389AB12-F8A9-4DD5-8647-ED41014E9985}">
       <text>
         <r>
           <rPr>
@@ -4536,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="1" shapeId="0" xr:uid="{55CC32A9-C242-413D-95ED-5A78B821B340}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{6CF32E8D-3578-4C35-8D95-F3FDAEE3F6C4}">
       <text>
         <r>
           <rPr>
@@ -4550,7 +4574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{AC7BB7EF-7B75-412F-8492-B76564E0C14A}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{4EC5B9BF-5F79-48E0-AEEB-3BE048359C2F}">
       <text>
         <r>
           <rPr>
@@ -4564,7 +4588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{28DD649B-C821-4AD3-A0FD-07992B1C0C35}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{3A00B4A4-9086-49FD-A973-E57ACF41519A}">
       <text>
         <r>
           <rPr>
@@ -4578,7 +4602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B37653CB-E528-4EB3-A892-BEED4F971924}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{B753A3E5-5850-4333-B255-138735532FF6}">
       <text>
         <r>
           <rPr>
@@ -4592,7 +4616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{D81352B8-E49B-4ED4-9260-068FE9EA87A4}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{5F533C4F-14BE-4FFD-AFF0-4F363C6DB46A}">
       <text>
         <r>
           <rPr>
@@ -4606,7 +4630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="0" shapeId="0" xr:uid="{C81B46EA-4AE6-426F-8E29-6687826CD77E}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{24DEB51A-3B71-4F4F-8B1A-554B96477B64}">
       <text>
         <r>
           <rPr>
@@ -4620,7 +4644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{2A5DAA9E-044F-4BC1-9CC5-853C778F0A5D}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{5B1E2943-05E3-425E-81FA-B470E0201842}">
       <text>
         <r>
           <rPr>
@@ -4634,7 +4658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{2FDE9FF6-3094-4FF5-9705-AC05C2A21CF1}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{4873B8C3-3DC1-4ABA-9CA2-041EDFEAA8E7}">
       <text>
         <r>
           <rPr>
@@ -4648,7 +4672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="0" shapeId="0" xr:uid="{34C2D730-9539-4A84-8FB9-60449CC1C9F8}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{4C01B86B-8434-41C9-AA91-62393B829718}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{1CBE3B8E-0A71-484E-8AB5-2E4A9737E416}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{B533D00F-40C7-422E-B637-7480A633E0EE}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{C9BE8D4E-F1CF-450A-9F7F-FE3A76054555}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{A23BD60A-3F08-4056-BBE4-5BC9BF9DBAC1}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0" xr:uid="{CE13D13D-74D4-4C89-9F75-91B5D8538FEE}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{8F00096D-9328-4957-BCBE-20B060541427}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D134" authorId="0" shapeId="0" xr:uid="{252912B5-BBAA-4AE9-8277-3A1466458B1E}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{791D4741-6C69-4394-BDA7-746940250271}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4746,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0" xr:uid="{3E59560A-0C84-48D7-852B-E82392F25AC9}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{B95D491F-0995-4634-BB75-0A2B65DA521D}">
       <text>
         <r>
           <rPr>
@@ -4737,7 +4761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="1" shapeId="0" xr:uid="{DB3A1C43-FFBD-4811-96DB-7411C396D242}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{836F7DA3-3746-45EC-9F91-75F43F69B75D}">
       <text>
         <r>
           <rPr>
@@ -4752,7 +4776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E138" authorId="1" shapeId="0" xr:uid="{96EC8E96-7B87-4BE6-B2FB-A3593F869427}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{015B127F-3ACD-448E-B7AE-EE2AF821A620}">
       <text>
         <r>
           <rPr>
@@ -4767,7 +4791,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F138" authorId="1" shapeId="0" xr:uid="{DD5F88FD-E3D2-4EFC-8913-98A6325A2F9D}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{4117A4CF-A7A4-4A59-A708-41648375B963}">
       <text>
         <r>
           <rPr>
@@ -4782,7 +4806,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G138" authorId="1" shapeId="0" xr:uid="{5BB9A2A7-6CE4-4189-BE50-9DCBB089C592}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{971DA0E7-9694-49B2-B341-0F42CEE4FDBF}">
       <text>
         <r>
           <rPr>
@@ -4797,7 +4821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H138" authorId="1" shapeId="0" xr:uid="{157AB19B-CD3A-4FD7-B3E7-DAD07F11858B}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{7C15A418-97F2-48E8-992E-453798CC1DEC}">
       <text>
         <r>
           <rPr>
@@ -4812,7 +4836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D154" authorId="0" shapeId="0" xr:uid="{018E70A7-45A0-46D3-B6EA-DEF79DD16FBC}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{6164A66E-F113-4BBF-BF3A-8966970C6007}">
       <text>
         <r>
           <rPr>
@@ -4826,7 +4850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E154" authorId="0" shapeId="0" xr:uid="{BE34538E-8418-421B-95F3-555ADE6D22A4}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{F7F4BAB9-AB0B-4436-AC09-996DE9B577D6}">
       <text>
         <r>
           <rPr>
@@ -4840,7 +4864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F154" authorId="0" shapeId="0" xr:uid="{A119FDE3-73FC-49AA-961D-75632DF59D6A}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{9989CDBB-8F11-4CDD-883C-0C902FEECF77}">
       <text>
         <r>
           <rPr>
@@ -4854,7 +4878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G154" authorId="0" shapeId="0" xr:uid="{A49858A8-A08E-4899-AB2B-CDA800BD9C7F}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{7E86D7CC-FFDF-480C-A748-42D8159559C1}">
       <text>
         <r>
           <rPr>
@@ -4868,7 +4892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H154" authorId="0" shapeId="0" xr:uid="{3E200C1B-B72C-4241-BAA2-2E363086D185}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C774D9A5-3ABF-47A9-A38D-5AB1A3809E2E}">
       <text>
         <r>
           <rPr>
@@ -4882,7 +4906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D157" authorId="0" shapeId="0" xr:uid="{4A1C8AC9-D54D-429B-ADAB-B3734C83BE23}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{829B6F07-CFE0-4770-8526-355FDCE82E97}">
       <text>
         <r>
           <rPr>
@@ -4897,7 +4921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E157" authorId="0" shapeId="0" xr:uid="{3BB8C26D-459A-4072-9E89-696F518731B1}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{095883B0-AB44-4AFF-AD9C-1999BE44C8D6}">
       <text>
         <r>
           <rPr>
@@ -4912,7 +4936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F157" authorId="0" shapeId="0" xr:uid="{1C6E857F-6C5D-4FD4-9EE4-2F09705C761A}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{509F1B53-9B24-47B5-968C-11359092BFFF}">
       <text>
         <r>
           <rPr>
@@ -4927,7 +4951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G157" authorId="0" shapeId="0" xr:uid="{8287F70E-A738-4D8A-881F-7D338A40EC3B}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{2EEAE878-FBE4-4D03-8FFA-67100DF53E5C}">
       <text>
         <r>
           <rPr>
@@ -4942,7 +4966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H157" authorId="0" shapeId="0" xr:uid="{014C8729-0CF6-41A9-8D99-FF6BB2C4394C}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{00840D25-5C48-4AF0-B0E9-867DDA5EC481}">
       <text>
         <r>
           <rPr>
@@ -4957,7 +4981,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D159" authorId="0" shapeId="0" xr:uid="{D354A556-8714-4D21-80ED-1573194C767A}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{6E6AF3A9-ADC6-4103-BB07-F68C791F46CD}">
       <text>
         <r>
           <rPr>
@@ -4973,7 +4997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E159" authorId="0" shapeId="0" xr:uid="{485A1108-54DB-42E3-A6F2-C5940A4806C2}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{F0BF211F-E613-4551-BC35-FD9052946C15}">
       <text>
         <r>
           <rPr>
@@ -4989,7 +5013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F159" authorId="0" shapeId="0" xr:uid="{3EB095CD-A559-42E4-98B4-7A881E399DE6}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{0799FE11-2ED5-432A-94B9-FBCD868D64C3}">
       <text>
         <r>
           <rPr>
@@ -5005,7 +5029,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G159" authorId="0" shapeId="0" xr:uid="{B93A0BBF-6FEC-42F4-8430-29B5F3F939E7}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{432A415C-8309-455D-9525-76E5D04A061F}">
       <text>
         <r>
           <rPr>
@@ -5021,7 +5045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H159" authorId="0" shapeId="0" xr:uid="{8E450807-067F-4B57-B220-14D51887F290}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{B2416FE8-AF34-4C68-84A8-3AA3F35C143D}">
       <text>
         <r>
           <rPr>
@@ -5037,7 +5061,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D161" authorId="0" shapeId="0" xr:uid="{AD46B5B9-39B8-4156-847F-4FF3309E3C00}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{039A0291-77A2-4F56-BD36-FA5B90375231}">
       <text>
         <r>
           <rPr>
@@ -5052,7 +5076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E161" authorId="0" shapeId="0" xr:uid="{E43BA91C-6EAB-4A12-AFB0-A40BD4601DDD}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{9304167C-11E2-4ACE-9287-AFFE3701CE67}">
       <text>
         <r>
           <rPr>
@@ -5067,7 +5091,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F161" authorId="0" shapeId="0" xr:uid="{D3FC5AB3-B8D4-487D-B89B-06521004E67B}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{AE0B8211-22DB-4C3B-B2EA-8C1DE747BD3B}">
       <text>
         <r>
           <rPr>
@@ -5082,7 +5106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G161" authorId="0" shapeId="0" xr:uid="{51C19B28-3606-4A3C-AE28-9BB4EA3F06E4}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{B3A4E65C-5017-4C6E-8A49-644FD0141BD4}">
       <text>
         <r>
           <rPr>
@@ -5097,7 +5121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H161" authorId="0" shapeId="0" xr:uid="{C9E9A396-CD69-464D-9C3D-544305C89BCD}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{D67F04CE-D918-4BB4-BA97-B8D34A8E23C1}">
       <text>
         <r>
           <rPr>
@@ -5112,7 +5136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="1" shapeId="0" xr:uid="{992C4CD7-8C10-4363-A95D-2D8B15120731}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{E7EEB3A4-6E86-497F-9BA3-C00A3BE62948}">
       <text>
         <r>
           <rPr>
@@ -6509,7 +6533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="373">
   <si>
     <t>Meningitis</t>
   </si>
@@ -7625,6 +7649,9 @@
   </si>
   <si>
     <t>Condición objetivo</t>
+  </si>
+  <si>
+    <t>Todas las causas</t>
   </si>
 </sst>
 </file>
@@ -11661,7 +11688,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cUZ/3KoS2Tyh7Bn5M2y/AW+z3iAkFxWL0foWQD8eXTIfPHgneAvUv3EQ1I39dL1HTheUp4FJoMCDIjCdssmihA==" saltValue="8m1MEkO7cSYXB0Axt4PMTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nlCkvOYX1UbZROdF6iWUTBJsByfjz7oJ+y99dVjpvzU/kZi7JjyEe+Yy5hxxtIYGB5J7NAFTogPdJRaMe6kYtA==" saltValue="lG8c18XPgHIPj0C+wA8v7g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -11686,7 +11713,7 @@
     <col min="8" max="16384" width="14.453125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
         <v>192</v>
       </c>
@@ -12585,7 +12612,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NSfMnFxlPnHyA/4sbAFn8PiyKlup58j4PzwgD0xt8gPF39RtgKAQCZQXhLIMnFbERcoaGIuTz2XbifdWyRZTaA==" saltValue="Du+pnKd/CckPVTJu0XisnA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5n9N8JkQaF89hLNpI+MrcHHUk121soS9xbb7uMF5TJJNafyFEDYKF97c6XsEomXrviVyBzp1Tw/HlCD6E+5YrQ==" saltValue="WL+KNGNDZcPiKRr92YwbzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -12661,21 +12688,29 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="62"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="C5" s="62"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
-      <c r="B6" s="67"/>
+      <c r="B6" s="67" t="s">
+        <v>233</v>
+      </c>
       <c r="C6" s="67"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
+      <c r="A7" s="66" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>233</v>
+      </c>
       <c r="C7" s="67"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -12744,7 +12779,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6WqwcvHCv0qmk1smGVbtJChECDG3u+6V6JDOvdrbbY3hQzD5hlmWe4BdToECoZnLXq6xHlnyIzHVT9c4EhSpng==" saltValue="TmonaH5NBa9ZDw6906V/ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+YHescoDoZGNgqr2B/f4gF4J1pWtVhP5KbFPUP0mxPJdP4C7DleP4xQH/ZoXgt6/AaNt5HDp5ooM5u7lvQvqrA==" saltValue="3OptCr16nkugcXh390RtGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -12839,7 +12874,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dgvyI6zG5yg7OqwbpyoM4mMumfrOaRMBBKa0gCd9xtg6QP2EEqrN8PMmqVCWTHneWxnt6SvvdG/ySPZqycKxpQ==" saltValue="FZrEPVyLE0aTKNuKru+d0A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lNHeh22ZyJwcpaC593oxZM/8brR2Udd0iTQC+imJQN8CrJd3/BVB5NdtQ/uAzG2zuJjAbrpKJWkcAj9tFmvuYQ==" saltValue="h8W664iv6+lb+uTqmH4m9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -12949,7 +12984,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NTDwvEmCT10hBEgIcBAbsaU7hdq03hjKOWHe1KgzjUJUAt4cKxAQVIVqapu3rqWV2/x3A6ERRtB+CK1k7eFJfg==" saltValue="BbFj9XU05Rr766aPspoVcw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="j58SAp1qVXp/yV7VtJMb9cnq7O+JYyKIGIpnw/ApvmIbHCNBl7UK9x5gwQIiQeruyW5exzpL7bGGYCwE964qlA==" saltValue="bdVCu6qn2yLb1Zihgf/T5w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -14707,7 +14742,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zGg4YXYkJqDHTCPE/er42LqzX75QboA4Xqw5l6Obx/Dymi1xpLwz7EG5zbd+RJkT1rJl233q+lZjS8mTl6vNaA==" saltValue="n/ZQke9Ee3eCgQscu/yj0w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HmuBaSF/Yi5XITt0V0ur7NhFIq/kHxNxTUT6eW1pfGUxizmq36CjLhyB3V3OqNceGQN1kxDdqKMphC3p5p3duQ==" saltValue="XooRESioeFWwN9LMTDzTLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -14742,7 +14777,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DYBZkAzISeZpzGST7h7u9LHNv0U8vWIRkxvhnDG1liV3VcUXr5TmvsQjrYo+FK44CEER65wxi9W2Y3zROujrQA==" saltValue="xvuXT74PCHiam5b771lilg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eTE6lSoeHDWCvkq5t4TFRNRTTpTpM4eaG3so4KeN5++wzJUprodNaC2zWn3YXfu5zZmHuH+3orqxQV/OeTeIFQ==" saltValue="RC58ld1YOuaDfHtlKeVbJg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14942,7 +14977,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ef3UOei/uNGJyocH44wn2YrPmKvZpKwTtHHUL0cmMYT87t/DajVMni3ngTroL/6ORWNfj1TLGz1f9uipBvO0PA==" saltValue="7IopZ7AgXsljC4puwg+2MA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gQNu32f6V58z+BDcipJi0pwovAfsLzecf/svHOG4ozW5ThJkS5iORg9Nd0HUR7PArCDYb0h6CGtMz2MZn8/mlg==" saltValue="LGpPOHgbsm9iRn7HPIoQVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -16751,7 +16786,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jZLiqbd0M9Sa76/yFsIuhRc2Wq/8G6vNmXWawjMmsDXUoe5x0HED/e0MOshvbtX5t0ceDTQKDLi9/PFimFQsVw==" saltValue="TgalN7gffqF6gALE1m5OzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1CrwyaUy4r1pnjazH9xEUxnqZeIBsGGYNS3MLaGwWArfQZ08cF4F9pY32TAZsFxPUNrY/cOxgm/QUVrxNOFLgA==" saltValue="S6N0ic7ss38i/SwHZdTc9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17375,7 +17410,9 @@
       <c r="E30" s="100"/>
       <c r="F30" s="100"/>
       <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
+      <c r="H30" s="100" t="s">
+        <v>5</v>
+      </c>
       <c r="I30" s="100"/>
       <c r="J30" s="100"/>
       <c r="K30" s="100"/>
@@ -17560,7 +17597,7 @@
       <c r="L39" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IphmRCFjo2K9eC1paPacg70j0UbF9lY8VNvk7tAUAs3j6B0KAhUejS6MMZB/nXbEczvLqz4waVkOEwwfXI+/pQ==" saltValue="vlc+zYzU3ZW7qDIzsLSR5g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="n4lIOP4sAh5bgOOlNRoUw+VUkoRNHH+bErmLfQix7B3KV7V31qplXMEgs8beWd4GPOXW1iTtQQTA/JlJiwLoQg==" saltValue="HXznFJiwb2+uFipvSsjlDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17953,7 +17990,7 @@
       <c r="L14" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8zdzN6iI5X5CKeFdJmfX8HtCgQZsfHfCmWQFs2dxLSOrBUpJ8q8myTzMD8mF6i23U8fgwD/zi/21YPoQJV5xxg==" saltValue="3NipCkuvZYK/Rcm9pS7opw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RfIi4GbExdNCJSshvGKVfpmffGOdGpa7tonHYk5K5rxpBeUQtlpA5a751hA+biL0mCMHJx5mwxosOmCvSTF5zw==" saltValue="br8k76gjyesQ2fJcfQsSlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19037,7 +19074,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hEWT9+0+qDj7I0Ozv+ohGmkXyTwOJpnx3K0/BCNav7d1ja6pvcKZZW69C3IKYZO/QpuX5l/M5Oe3CPlnIZXV5Q==" saltValue="Z0/kYP46SshiD1LkzDpKxw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PmyhSofeRoWsDWuKL90+u18VWaFQ2KLsAipT0keeWSGCwbJ9GM/SbUWB5GzJC/x8Cgx5Afyc/msjhWLxEIGKsg==" saltValue="ep2dqkEXf1+5gYMy10KXmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -22832,8 +22869,44 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OOm6nRrfkprxzThu4Vk0eZ8tKEiLVdAwOmDuXXVBJ6/ByHDJ7IXLTDsPlTsvDuqQ7o/5KbzROGOEp5LUhDwoUA==" saltValue="QzqIRqpP29hML2TeeD3Csw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tg/5A8V3CpE1EuOYw2/WmFS71hxU92ZHMkYQWsRTBA669RCFJUkZ1YCBLsnOEwnsqmRubhlrLEnKG/6Z7U0Lxw==" saltValue="LRYZzIU2j8CkmatRZkBybw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -22843,42 +22916,6 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -24093,7 +24130,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AW+Y2F8VdAGuwS05QIUk9dekU3/3HzQDrz3xSErGbyCM36K8i90gwwlb5uhnF8bYfspVBImnTDZ41OAp0XHODg==" saltValue="EKt7jd/pYevD+drqDClYpA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AdJlCpx0/Z43GIvaTB4vRRmtOfsai7oQpiMdLAEzZMYWIw/Sow21LTwsjUQ7XoAwsaZCK2bGMsDIobJaYZr+9A==" saltValue="P5riOOCaCl6tLFcZS/enEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -25585,7 +25622,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A56" s="92" t="s">
         <v>124</v>
       </c>
@@ -28322,7 +28359,7 @@
       <c r="G165" s="79"/>
       <c r="H165" s="79"/>
     </row>
-    <row r="166" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
       <c r="A166" s="92" t="s">
         <v>124</v>
       </c>
@@ -30946,7 +30983,7 @@
       <c r="H275" s="79"/>
       <c r="I275" s="79"/>
     </row>
-    <row r="276" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A276" s="92" t="s">
         <v>124</v>
       </c>
@@ -32226,7 +32263,7 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NuXGru0ZX/TSwr2APUtkW+t6TDOFeyTAdZZiesRzTB0g3uLWsyBtAj4j64LA9NrQaMHqn1klO4J9JHuyojTSJw==" saltValue="nRMJkzsilMMOVhRQVP28KA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9f/64YhwssC4OqRZgAYhHAxPTB2w7juwvRYhbkcTQae00IiaZuMNQsCRS0hNq2Izc+Xn57o/kVFLukLQrp0fzg==" saltValue="Tjm8DvO+gEn2O/CgxUOuJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33327,7 +33364,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+bsfpIOSK7ciKSHwHCxHXToPBwiEuLzi1hNrNFusZcl9jQNXz4Fqfu7KJVPMPcF+YGxM7zfQIdHzk7XOj0ynzw==" saltValue="kR780Rt4G2FwWJrZv/iTgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JY0E76bjBj6ESxQHGLjTDrK1tqpT9wenNo1MwQMyRguLDG8GeUAiJiNcEOngV2m/MCtxdCDnxrLA9QX11UnvuQ==" saltValue="2jEeUamTqGVtsRIqvSs2tQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34268,7 +34305,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="96Bh3e+2WrYMMwRTkPzFf3+B/vtasYJONBVrXUFQrHZuyI9/0eRtpasZ/K9a7CeCmzCTrA/y9xyjhl6IJvwerg==" saltValue="4yV+wSRTtQ+muqsyrqaaLg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FqdFUx2pd/tW2+1kfgWFIWaoTRAnTA9hu5wSAndFiUeXt8U2umPTfWUQlPOg5Kr00o7xSBSN6oIMz1E5VBycug==" saltValue="p7bWhNKu12bQ4DdAi9xaew==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35113,7 +35150,7 @@
       <c r="N23" s="121"/>
       <c r="O23" s="121"/>
     </row>
-    <row r="24" spans="1:15" ht="52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="122" t="s">
@@ -36056,7 +36093,7 @@
       <c r="N46" s="121"/>
       <c r="O46" s="121"/>
     </row>
-    <row r="47" spans="1:15" ht="52" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A47" s="29"/>
       <c r="B47" s="29"/>
       <c r="C47" s="122" t="s">
@@ -36983,7 +37020,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="idII853JS+PBVr2m5rjWUG7ThV4jF+MMJ1oAeCbHI24DskVbXYgQXx1+P61/x352XVFR+kZVB3O3fFmbZRvbuQ==" saltValue="/G8dKwJLG7+pftEKgOrdHw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3HCyt8pnL0JAi0SyZjkVbtE5MCO2OykaGuYu5xX2NYiFvJciSUYpJlba6/XweHcO4tkqj50bC8mRMlowL1JBMA==" saltValue="kOQhyxB3bYuwhLpOEEov9A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37274,7 +37311,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5qwIRBnbm/SQM8vVKxG3TU12CI1czsd6b2RetHOEqQztMgEIE8b7pLOIsYdrtGagUtoWRo8eazc8HW3ok3FRpg==" saltValue="YxkFESjajdHPfhzVffrrcw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="POLtJ9x/WtL7Mx66ZuPiBfNTNn3xbBfMf3VvmVrRTwIxP5hYxxXJ6CIUx0s+0WvtWi7yCuNu1+AnunxrcEbqPg==" saltValue="nPs/TLiB3eLAdqYuRBZZGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -37286,7 +37323,7 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="39" customWidth="1"/>
@@ -37660,11 +37697,8 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>196</v>
-      </c>
       <c r="B17" s="39" t="s">
-        <v>236</v>
+        <v>372</v>
       </c>
       <c r="C17" s="39" t="s">
         <v>368</v>
@@ -37682,12 +37716,12 @@
         <v>1</v>
       </c>
       <c r="H17" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="39" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D18" s="120">
         <v>0</v>
@@ -37706,8 +37740,11 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>196</v>
+      </c>
       <c r="B19" s="39" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C19" s="39" t="s">
         <v>368</v>
@@ -37749,37 +37786,34 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>202</v>
-      </c>
       <c r="B21" s="39" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="C21" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D21" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="120">
         <v>0</v>
       </c>
       <c r="F21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D22" s="120">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E22" s="120">
         <v>0</v>
@@ -37796,7 +37830,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B23" s="39" t="s">
         <v>111</v>
@@ -37842,7 +37876,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B25" s="39" t="s">
         <v>111</v>
@@ -37888,10 +37922,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C27" s="39" t="s">
         <v>368</v>
@@ -37900,16 +37934,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -37917,483 +37951,483 @@
         <v>370</v>
       </c>
       <c r="D28" s="120">
+        <v>0.13</v>
+      </c>
+      <c r="E28" s="120">
+        <v>0</v>
+      </c>
+      <c r="F28" s="120">
+        <v>0</v>
+      </c>
+      <c r="G28" s="120">
+        <v>0</v>
+      </c>
+      <c r="H28" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D29" s="120">
+        <v>1</v>
+      </c>
+      <c r="E29" s="120">
+        <v>1</v>
+      </c>
+      <c r="F29" s="120">
+        <v>1</v>
+      </c>
+      <c r="G29" s="120">
+        <v>1</v>
+      </c>
+      <c r="H29" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C30" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D30" s="120">
         <v>0.3</v>
       </c>
-      <c r="E28" s="120">
+      <c r="E30" s="120">
         <v>0.3</v>
       </c>
-      <c r="F28" s="120">
+      <c r="F30" s="120">
         <v>0.3</v>
       </c>
-      <c r="G28" s="120">
+      <c r="G30" s="120">
         <v>0.3</v>
       </c>
-      <c r="H28" s="120">
+      <c r="H30" s="120">
         <v>0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D29" s="120">
-        <v>0</v>
-      </c>
-      <c r="E29" s="120">
-        <v>0</v>
-      </c>
-      <c r="F29" s="120">
-        <v>0</v>
-      </c>
-      <c r="G29" s="120">
-        <v>0</v>
-      </c>
-      <c r="H29" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="D30" s="120">
-        <v>1</v>
-      </c>
-      <c r="E30" s="120">
-        <v>1</v>
-      </c>
-      <c r="F30" s="120">
-        <v>1</v>
-      </c>
-      <c r="G30" s="120">
-        <v>1</v>
-      </c>
-      <c r="H30" s="120">
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D31" s="120">
+        <v>0</v>
+      </c>
+      <c r="E31" s="120">
+        <v>0</v>
+      </c>
+      <c r="F31" s="120">
+        <v>0</v>
+      </c>
+      <c r="G31" s="120">
+        <v>0</v>
+      </c>
+      <c r="H31" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" s="120">
+        <v>1</v>
+      </c>
+      <c r="E32" s="120">
+        <v>1</v>
+      </c>
+      <c r="F32" s="120">
+        <v>1</v>
+      </c>
+      <c r="G32" s="120">
+        <v>1</v>
+      </c>
+      <c r="H32" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D31" s="120">
-        <v>0</v>
-      </c>
-      <c r="E31" s="120">
-        <v>0</v>
-      </c>
-      <c r="F31" s="120">
-        <v>0</v>
-      </c>
-      <c r="G31" s="120">
-        <v>0</v>
-      </c>
-      <c r="H31" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C32" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D32" s="120">
-        <v>0</v>
-      </c>
-      <c r="E32" s="120">
-        <v>0</v>
-      </c>
-      <c r="F32" s="120">
-        <v>0</v>
-      </c>
-      <c r="G32" s="120">
-        <v>0</v>
-      </c>
-      <c r="H32" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D34" s="120">
+        <v>0</v>
+      </c>
+      <c r="E34" s="120">
+        <v>0</v>
+      </c>
+      <c r="F34" s="120">
+        <v>0</v>
+      </c>
+      <c r="G34" s="120">
+        <v>0</v>
+      </c>
+      <c r="H34" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" s="120">
+        <v>1</v>
+      </c>
+      <c r="E35" s="120">
+        <v>1</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1</v>
+      </c>
+      <c r="G35" s="120">
+        <v>1</v>
+      </c>
+      <c r="H35" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D34" s="120">
-        <v>0</v>
-      </c>
-      <c r="E34" s="120">
-        <v>0</v>
-      </c>
-      <c r="F34" s="120">
-        <v>0</v>
-      </c>
-      <c r="G34" s="120">
-        <v>0</v>
-      </c>
-      <c r="H34" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D35" s="120">
-        <v>0</v>
-      </c>
-      <c r="E35" s="120">
-        <v>0</v>
-      </c>
-      <c r="F35" s="120">
-        <v>0</v>
-      </c>
-      <c r="G35" s="120">
-        <v>0</v>
-      </c>
-      <c r="H35" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D37" s="120">
+        <v>0</v>
+      </c>
+      <c r="E37" s="120">
+        <v>0</v>
+      </c>
+      <c r="F37" s="120">
+        <v>0</v>
+      </c>
+      <c r="G37" s="120">
+        <v>0</v>
+      </c>
+      <c r="H37" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D38" s="120">
+        <v>1</v>
+      </c>
+      <c r="E38" s="120">
+        <v>1</v>
+      </c>
+      <c r="F38" s="120">
+        <v>1</v>
+      </c>
+      <c r="G38" s="120">
+        <v>1</v>
+      </c>
+      <c r="H38" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D37" s="120">
-        <v>0</v>
-      </c>
-      <c r="E37" s="120">
-        <v>0</v>
-      </c>
-      <c r="F37" s="120">
-        <v>0</v>
-      </c>
-      <c r="G37" s="120">
-        <v>0</v>
-      </c>
-      <c r="H37" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D38" s="120">
-        <v>0</v>
-      </c>
-      <c r="E38" s="120">
-        <v>0</v>
-      </c>
-      <c r="F38" s="120">
-        <v>0</v>
-      </c>
-      <c r="G38" s="120">
-        <v>0</v>
-      </c>
-      <c r="H38" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D40" s="120">
+        <v>0</v>
+      </c>
+      <c r="E40" s="120">
+        <v>0</v>
+      </c>
+      <c r="F40" s="120">
+        <v>0</v>
+      </c>
+      <c r="G40" s="120">
+        <v>0</v>
+      </c>
+      <c r="H40" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D41" s="120">
+        <v>1</v>
+      </c>
+      <c r="E41" s="120">
+        <v>1</v>
+      </c>
+      <c r="F41" s="120">
+        <v>1</v>
+      </c>
+      <c r="G41" s="120">
+        <v>1</v>
+      </c>
+      <c r="H41" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D40" s="120">
-        <v>0</v>
-      </c>
-      <c r="E40" s="120">
-        <v>0</v>
-      </c>
-      <c r="F40" s="120">
-        <v>0</v>
-      </c>
-      <c r="G40" s="120">
-        <v>0</v>
-      </c>
-      <c r="H40" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D41" s="120">
-        <v>0</v>
-      </c>
-      <c r="E41" s="120">
-        <v>0</v>
-      </c>
-      <c r="F41" s="120">
-        <v>0</v>
-      </c>
-      <c r="G41" s="120">
-        <v>0</v>
-      </c>
-      <c r="H41" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D42" s="120">
         <v>0</v>
       </c>
       <c r="E42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D43" s="120">
+        <v>0</v>
+      </c>
+      <c r="E43" s="120">
+        <v>0</v>
+      </c>
+      <c r="F43" s="120">
+        <v>0</v>
+      </c>
+      <c r="G43" s="120">
+        <v>0</v>
+      </c>
+      <c r="H43" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D44" s="120">
+        <v>0</v>
+      </c>
+      <c r="E44" s="120">
+        <v>1</v>
+      </c>
+      <c r="F44" s="120">
+        <v>1</v>
+      </c>
+      <c r="G44" s="120">
+        <v>1</v>
+      </c>
+      <c r="H44" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D43" s="120">
-        <v>0</v>
-      </c>
-      <c r="E43" s="120">
-        <v>0</v>
-      </c>
-      <c r="F43" s="120">
-        <v>0</v>
-      </c>
-      <c r="G43" s="120">
-        <v>0</v>
-      </c>
-      <c r="H43" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C44" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="E44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="F44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="G44" s="120">
-        <v>0.09</v>
-      </c>
-      <c r="H44" s="120">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D45" s="120">
         <v>0</v>
       </c>
       <c r="E45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="E46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="F46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="G46" s="120">
+        <v>0.09</v>
+      </c>
+      <c r="H46" s="120">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D47" s="120">
+        <v>0</v>
+      </c>
+      <c r="E47" s="120">
+        <v>1</v>
+      </c>
+      <c r="F47" s="120">
+        <v>1</v>
+      </c>
+      <c r="G47" s="120">
+        <v>1</v>
+      </c>
+      <c r="H47" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C48" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D46" s="120">
-        <v>0</v>
-      </c>
-      <c r="E46" s="120">
-        <v>0</v>
-      </c>
-      <c r="F46" s="120">
-        <v>0</v>
-      </c>
-      <c r="G46" s="120">
-        <v>0</v>
-      </c>
-      <c r="H46" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C47" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D47" s="120">
-        <v>0</v>
-      </c>
-      <c r="E47" s="120">
-        <v>0</v>
-      </c>
-      <c r="F47" s="120">
-        <v>0</v>
-      </c>
-      <c r="G47" s="120">
-        <v>0</v>
-      </c>
-      <c r="H47" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B48" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="E49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="F49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="G49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="H49" s="120">
-        <v>0.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B50" s="39" t="s">
         <v>103</v>
@@ -38422,27 +38456,27 @@
         <v>370</v>
       </c>
       <c r="D51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="E51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="F51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="G51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
       <c r="H51" s="120">
-        <v>0.76</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C52" s="39" t="s">
         <v>368</v>
@@ -38451,16 +38485,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -38468,158 +38502,156 @@
         <v>370</v>
       </c>
       <c r="D53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="E53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="F53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="G53" s="120">
+        <v>0.76</v>
+      </c>
+      <c r="H53" s="120">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D54" s="120">
+        <v>1</v>
+      </c>
+      <c r="E54" s="120">
+        <v>0</v>
+      </c>
+      <c r="F54" s="120">
+        <v>0</v>
+      </c>
+      <c r="G54" s="120">
+        <v>0</v>
+      </c>
+      <c r="H54" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C55" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D55" s="120">
         <v>0.32</v>
       </c>
-      <c r="E53" s="120">
-        <v>0</v>
-      </c>
-      <c r="F53" s="120">
-        <v>0</v>
-      </c>
-      <c r="G53" s="120">
-        <v>0</v>
-      </c>
-      <c r="H53" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A55" s="109" t="s">
+      <c r="E55" s="120">
+        <v>0</v>
+      </c>
+      <c r="F55" s="120">
+        <v>0</v>
+      </c>
+      <c r="G55" s="120">
+        <v>0</v>
+      </c>
+      <c r="H55" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A57" s="109" t="s">
         <v>360</v>
       </c>
-      <c r="B55" s="110"/>
-      <c r="C55" s="110"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="124"/>
-      <c r="F55" s="124"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="124"/>
-    </row>
-    <row r="56" spans="1:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="A56" s="29" t="s">
+      <c r="B57" s="110"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="124"/>
+    </row>
+    <row r="58" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A58" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B58" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="C56" s="96" t="s">
+      <c r="C58" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="39" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="39" t="s">
+      <c r="B59" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C59" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D57" s="120">
+      <c r="D59" s="120">
         <f>IF($C2="Affected fraction",D2,IF(D2=1,1,D2*0.9))</f>
         <v>0</v>
       </c>
-      <c r="E57" s="120">
+      <c r="E59" s="120">
         <f>IF($C2="Affected fraction",E2,IF(E2=1,1,E2*0.9))</f>
         <v>0</v>
       </c>
-      <c r="F57" s="120">
+      <c r="F59" s="120">
         <f>IF($C2="Affected fraction",F2,IF(F2=1,1,F2*0.9))</f>
         <v>1</v>
       </c>
-      <c r="G57" s="120">
+      <c r="G59" s="120">
         <f>IF($C2="Affected fraction",G2,IF(G2=1,1,G2*0.9))</f>
         <v>1</v>
       </c>
-      <c r="H57" s="120">
+      <c r="H59" s="120">
         <f>IF($C2="Affected fraction",H2,IF(H2=1,1,H2*0.9))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="39" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C60" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D58" s="120">
+      <c r="D60" s="120">
         <f>IF($C3="Affected fraction",D3,IF(D3=1,1,D3*0.9))</f>
         <v>0</v>
       </c>
-      <c r="E58" s="120">
+      <c r="E60" s="120">
         <f>IF($C3="Affected fraction",E3,IF(E3=1,1,E3*0.9))</f>
         <v>0</v>
       </c>
-      <c r="F58" s="120">
+      <c r="F60" s="120">
         <v>0.02</v>
       </c>
-      <c r="G58" s="120">
+      <c r="G60" s="120">
         <v>0.02</v>
       </c>
-      <c r="H58" s="120">
+      <c r="H60" s="120">
         <v>0.02</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D59" s="120">
-        <f>IF($C4="Affected fraction",D4,IF(D4=1,1,D4*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="120">
-        <f>IF($C4="Affected fraction",E4,IF(E4=1,1,E4*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="120">
-        <v>0.13</v>
-      </c>
-      <c r="G59" s="120">
-        <v>0.13</v>
-      </c>
-      <c r="H59" s="120">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="B60" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C60" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="D60" s="120">
-        <v>0</v>
-      </c>
-      <c r="E60" s="120">
-        <v>0</v>
-      </c>
-      <c r="F60" s="120">
-        <v>1</v>
-      </c>
-      <c r="G60" s="120">
-        <v>1</v>
-      </c>
-      <c r="H60" s="120">
-        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -38627,24 +38659,29 @@
         <v>369</v>
       </c>
       <c r="D61" s="120">
+        <f>IF($C4="Affected fraction",D4,IF(D4=1,1,D4*0.9))</f>
         <v>0</v>
       </c>
       <c r="E61" s="120">
+        <f>IF($C4="Affected fraction",E4,IF(E4=1,1,E4*0.9))</f>
         <v>0</v>
       </c>
       <c r="F61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="G61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H61" s="120">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="39" t="s">
+        <v>222</v>
+      </c>
       <c r="B62" s="39" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C62" s="39" t="s">
         <v>368</v>
@@ -38686,11 +38723,8 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="39" t="s">
-        <v>213</v>
-      </c>
       <c r="B64" s="39" t="s">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="C64" s="39" t="s">
         <v>368</v>
@@ -38732,8 +38766,11 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="39" t="s">
+        <v>213</v>
+      </c>
       <c r="B66" s="39" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C66" s="39" t="s">
         <v>368</v>
@@ -38775,11 +38812,8 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="39" t="s">
-        <v>233</v>
-      </c>
       <c r="B68" s="39" t="s">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="C68" s="39" t="s">
         <v>368</v>
@@ -38805,49 +38839,44 @@
         <v>369</v>
       </c>
       <c r="D69" s="120">
-        <f t="shared" ref="D69:H81" si="0">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*0.9))</f>
         <v>0</v>
       </c>
       <c r="E69" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F69" s="120">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G69" s="120">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H69" s="120">
-        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="39" t="s">
+        <v>233</v>
+      </c>
       <c r="B70" s="39" t="s">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="C70" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D70" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E70" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F70" s="120">
-        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*0.9))</f>
         <v>1</v>
       </c>
       <c r="G70" s="120">
-        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*0.9))</f>
         <v>1</v>
       </c>
       <c r="H70" s="120">
-        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*0.9))</f>
         <v>0</v>
       </c>
     </row>
@@ -38856,7 +38885,7 @@
         <v>369</v>
       </c>
       <c r="D71" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D71:E73" si="0">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*0.9))</f>
         <v>0</v>
       </c>
       <c r="E71" s="120">
@@ -38864,22 +38893,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="120">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G71" s="120">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H71" s="120">
-        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*0.9))</f>
+        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="39" t="s">
-        <v>196</v>
-      </c>
       <c r="B72" s="39" t="s">
-        <v>236</v>
+        <v>3</v>
       </c>
       <c r="C72" s="39" t="s">
         <v>368</v>
@@ -38893,16 +38919,16 @@
         <v>0</v>
       </c>
       <c r="F72" s="120">
-        <f>IF($C17="Affected fraction",F17,IF(F17=1,1,F17*0.9))</f>
+        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*0.9))</f>
         <v>1</v>
       </c>
       <c r="G72" s="120">
-        <f>IF($C17="Affected fraction",G17,IF(G17=1,1,G17*0.9))</f>
+        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*0.9))</f>
         <v>1</v>
       </c>
       <c r="H72" s="120">
-        <f>IF($C17="Affected fraction",H17,IF(H17=1,1,H17*0.9))</f>
-        <v>1</v>
+        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*0.9))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -38924,22 +38950,21 @@
         <v>0</v>
       </c>
       <c r="H73" s="120">
+        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*0.9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74" s="39" t="s">
-        <v>3</v>
+        <v>372</v>
       </c>
       <c r="C74" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D74" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E74" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F74" s="120">
@@ -38949,19 +38974,17 @@
         <v>1</v>
       </c>
       <c r="H74" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C75" s="39" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D75" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E75" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F75" s="120">
@@ -38976,117 +38999,107 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="39" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="C76" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D76" s="120">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>IF($C19="Affected fraction",D19,IF(D19=1,1,D19*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E76" s="120">
-        <f t="shared" si="0"/>
+        <f>IF($C19="Affected fraction",E19,IF(E19=1,1,E19*0.9))</f>
         <v>0</v>
       </c>
       <c r="F76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",F19,IF(F19=1,1,F19*0.9))</f>
+        <v>1</v>
       </c>
       <c r="G76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",G19,IF(G19=1,1,G19*0.9))</f>
+        <v>1</v>
       </c>
       <c r="H76" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",H19,IF(H19=1,1,H19*0.9))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C77" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D77" s="120">
-        <v>0.11</v>
+        <f t="shared" ref="D77:H85" si="1">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E77" s="120">
-        <f>IF($C22="Affected fraction",E22,IF(E22=1,1,E22*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H77" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="39" t="s">
-        <v>200</v>
-      </c>
       <c r="B78" s="39" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="C78" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D78" s="120">
-        <f>IF($C23="Affected fraction",D23,IF(D23=1,1,D23*0.9))</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E78" s="120">
-        <f>IF($C23="Affected fraction",E23,IF(E23=1,1,E23*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C79" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D79" s="120">
-        <v>0.11</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E79" s="120">
-        <f>IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H79" s="120">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B80" s="39" t="s">
         <v>111</v>
@@ -39095,23 +39108,23 @@
         <v>368</v>
       </c>
       <c r="D80" s="120">
-        <f>IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E80" s="120">
-        <f>IF($C25="Affected fraction",E25,IF(E25=1,1,E25*0.9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H80" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -39123,46 +39136,51 @@
         <v>0.11</v>
       </c>
       <c r="E81" s="120">
-        <f>IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
+        <f>IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
         <v>0</v>
       </c>
       <c r="F81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H81" s="120">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="39" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C82" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D82" s="120">
+        <f>IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
         <v>1</v>
       </c>
       <c r="E82" s="120">
-        <v>1</v>
+        <f>IF($C25="Affected fraction",E25,IF(E25=1,1,E25*0.9))</f>
+        <v>0</v>
       </c>
       <c r="F82" s="120">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G82" s="120">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H82" s="120">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -39170,537 +39188,550 @@
         <v>370</v>
       </c>
       <c r="D83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <v>0.11</v>
       </c>
       <c r="E83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f>IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
+        <v>0</v>
       </c>
       <c r="F83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H83" s="120">
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="B84" s="39" t="s">
+        <v>111</v>
+      </c>
       <c r="C84" s="39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D84" s="120">
-        <v>0</v>
+        <f>IF($C27="Affected fraction",D27,IF(D27=1,1,D27*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E84" s="120">
+        <f>IF($C27="Affected fraction",E27,IF(E27=1,1,E27*0.9))</f>
         <v>0</v>
       </c>
       <c r="F84" s="120">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G84" s="120">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H84" s="120">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="B85" s="39" t="s">
+      <c r="C85" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D85" s="120">
+        <v>0.11</v>
+      </c>
+      <c r="E85" s="120">
+        <f>IF($C28="Affected fraction",E28,IF(E28=1,1,E28*0.9))</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B86" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="39" t="s">
+      <c r="C86" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D85" s="120">
-        <v>1</v>
-      </c>
-      <c r="E85" s="120">
-        <v>1</v>
-      </c>
-      <c r="F85" s="120">
-        <v>1</v>
-      </c>
-      <c r="G85" s="120">
-        <v>1</v>
-      </c>
-      <c r="H85" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C86" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C87" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H87" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C88" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D87" s="120">
-        <v>0</v>
-      </c>
-      <c r="E87" s="120">
-        <v>0</v>
-      </c>
-      <c r="F87" s="120">
-        <v>0</v>
-      </c>
-      <c r="G87" s="120">
-        <v>0</v>
-      </c>
-      <c r="H87" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="B88" s="39" t="s">
+      <c r="D88" s="120">
+        <v>0</v>
+      </c>
+      <c r="E88" s="120">
+        <v>0</v>
+      </c>
+      <c r="F88" s="120">
+        <v>0</v>
+      </c>
+      <c r="G88" s="120">
+        <v>0</v>
+      </c>
+      <c r="H88" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B89" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="39" t="s">
+      <c r="C89" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D88" s="120">
-        <v>1</v>
-      </c>
-      <c r="E88" s="120">
-        <v>1</v>
-      </c>
-      <c r="F88" s="120">
-        <v>1</v>
-      </c>
-      <c r="G88" s="120">
-        <v>1</v>
-      </c>
-      <c r="H88" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C89" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C90" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D90" s="120">
+        <v>0</v>
+      </c>
+      <c r="E90" s="120">
+        <v>0</v>
+      </c>
+      <c r="F90" s="120">
+        <v>0</v>
+      </c>
+      <c r="G90" s="120">
+        <v>0</v>
+      </c>
+      <c r="H90" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C91" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D90" s="120">
-        <v>0</v>
-      </c>
-      <c r="E90" s="120">
-        <v>0</v>
-      </c>
-      <c r="F90" s="120">
-        <v>0</v>
-      </c>
-      <c r="G90" s="120">
-        <v>0</v>
-      </c>
-      <c r="H90" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B91" s="39" t="s">
+      <c r="D91" s="120">
+        <v>0</v>
+      </c>
+      <c r="E91" s="120">
+        <v>0</v>
+      </c>
+      <c r="F91" s="120">
+        <v>0</v>
+      </c>
+      <c r="G91" s="120">
+        <v>0</v>
+      </c>
+      <c r="H91" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B92" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C91" s="39" t="s">
+      <c r="C92" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D91" s="120">
-        <v>1</v>
-      </c>
-      <c r="E91" s="120">
-        <v>1</v>
-      </c>
-      <c r="F91" s="120">
-        <v>1</v>
-      </c>
-      <c r="G91" s="120">
-        <v>1</v>
-      </c>
-      <c r="H91" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C92" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C93" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D93" s="120">
+        <v>0</v>
+      </c>
+      <c r="E93" s="120">
+        <v>0</v>
+      </c>
+      <c r="F93" s="120">
+        <v>0</v>
+      </c>
+      <c r="G93" s="120">
+        <v>0</v>
+      </c>
+      <c r="H93" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C94" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D93" s="120">
-        <v>0</v>
-      </c>
-      <c r="E93" s="120">
-        <v>0</v>
-      </c>
-      <c r="F93" s="120">
-        <v>0</v>
-      </c>
-      <c r="G93" s="120">
-        <v>0</v>
-      </c>
-      <c r="H93" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="B94" s="39" t="s">
+      <c r="D94" s="120">
+        <v>0</v>
+      </c>
+      <c r="E94" s="120">
+        <v>0</v>
+      </c>
+      <c r="F94" s="120">
+        <v>0</v>
+      </c>
+      <c r="G94" s="120">
+        <v>0</v>
+      </c>
+      <c r="H94" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B95" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C94" s="39" t="s">
+      <c r="C95" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D94" s="120">
-        <v>1</v>
-      </c>
-      <c r="E94" s="120">
-        <v>1</v>
-      </c>
-      <c r="F94" s="120">
-        <v>1</v>
-      </c>
-      <c r="G94" s="120">
-        <v>1</v>
-      </c>
-      <c r="H94" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C95" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C96" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D96" s="120">
+        <v>0</v>
+      </c>
+      <c r="E96" s="120">
+        <v>0</v>
+      </c>
+      <c r="F96" s="120">
+        <v>0</v>
+      </c>
+      <c r="G96" s="120">
+        <v>0</v>
+      </c>
+      <c r="H96" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C97" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D96" s="120">
-        <v>0</v>
-      </c>
-      <c r="E96" s="120">
-        <v>0</v>
-      </c>
-      <c r="F96" s="120">
-        <v>0</v>
-      </c>
-      <c r="G96" s="120">
-        <v>0</v>
-      </c>
-      <c r="H96" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="B97" s="39" t="s">
+      <c r="D97" s="120">
+        <v>0</v>
+      </c>
+      <c r="E97" s="120">
+        <v>0</v>
+      </c>
+      <c r="F97" s="120">
+        <v>0</v>
+      </c>
+      <c r="G97" s="120">
+        <v>0</v>
+      </c>
+      <c r="H97" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="39" t="s">
+      <c r="C98" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D97" s="120">
-        <f>IF($C42="Affected fraction",D42,IF(D42=1,1,D42*0.9))</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="120">
-        <f>IF($C42="Affected fraction",E42,IF(E42=1,1,E42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="F97" s="120">
-        <f>IF($C42="Affected fraction",F42,IF(F42=1,1,F42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="G97" s="120">
-        <f>IF($C42="Affected fraction",G42,IF(G42=1,1,G42*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="H97" s="120">
-        <f>IF($C42="Affected fraction",H42,IF(H42=1,1,H42*0.9))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C98" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C99" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D99" s="120">
+        <v>0</v>
+      </c>
+      <c r="E99" s="120">
+        <v>0</v>
+      </c>
+      <c r="F99" s="120">
+        <v>0</v>
+      </c>
+      <c r="G99" s="120">
+        <v>0</v>
+      </c>
+      <c r="H99" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C100" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H99" s="120">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B100" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="C100" s="39" t="s">
+      <c r="D100" s="120">
+        <v>0</v>
+      </c>
+      <c r="E100" s="120">
+        <v>0</v>
+      </c>
+      <c r="F100" s="120">
+        <v>0</v>
+      </c>
+      <c r="G100" s="120">
+        <v>0</v>
+      </c>
+      <c r="H100" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="B101" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C101" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D100" s="120">
-        <v>0</v>
-      </c>
-      <c r="E100" s="120">
-        <v>1</v>
-      </c>
-      <c r="F100" s="120">
-        <v>1</v>
-      </c>
-      <c r="G100" s="120">
-        <v>1</v>
-      </c>
-      <c r="H100" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C101" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D101" s="120">
+        <f>IF($C44="Affected fraction",D44,IF(D44=1,1,D44*0.9))</f>
         <v>0</v>
       </c>
       <c r="E101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",E44,IF(E44=1,1,E44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="F101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",F44,IF(F44=1,1,F44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="G101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",G44,IF(G44=1,1,G44*0.9))</f>
+        <v>1</v>
       </c>
       <c r="H101" s="120">
-        <v>0</v>
+        <f>IF($C44="Affected fraction",H44,IF(H44=1,1,H44*0.9))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C102" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D102" s="120">
+        <v>0</v>
+      </c>
+      <c r="E102" s="120">
+        <v>0</v>
+      </c>
+      <c r="F102" s="120">
+        <v>0</v>
+      </c>
+      <c r="G102" s="120">
+        <v>0</v>
+      </c>
+      <c r="H102" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C103" s="39" t="s">
         <v>369</v>
       </c>
-      <c r="D102" s="120">
-        <v>0</v>
-      </c>
-      <c r="E102" s="120">
-        <v>0</v>
-      </c>
-      <c r="F102" s="120">
-        <v>0</v>
-      </c>
-      <c r="G102" s="120">
-        <v>0</v>
-      </c>
-      <c r="H102" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B103" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C103" s="39" t="s">
+      <c r="D103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H103" s="120">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C104" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D103" s="120">
-        <v>1</v>
-      </c>
-      <c r="E103" s="120">
-        <v>1</v>
-      </c>
-      <c r="F103" s="120">
-        <v>1</v>
-      </c>
-      <c r="G103" s="120">
-        <v>1</v>
-      </c>
-      <c r="H103" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C104" s="39" t="s">
+      <c r="D104" s="120">
+        <v>0</v>
+      </c>
+      <c r="E104" s="120">
+        <v>1</v>
+      </c>
+      <c r="F104" s="120">
+        <v>1</v>
+      </c>
+      <c r="G104" s="120">
+        <v>1</v>
+      </c>
+      <c r="H104" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C105" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="E104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="F104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="G104" s="120">
-        <v>0.51</v>
-      </c>
-      <c r="H104" s="120">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="B105" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C105" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C106" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="E106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="F106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="G106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="H106" s="120">
-        <v>0.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="39" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B107" s="39" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C107" s="39" t="s">
         <v>368</v>
@@ -39709,16 +39740,16 @@
         <v>1</v>
       </c>
       <c r="E107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -39726,201 +39757,202 @@
         <v>370</v>
       </c>
       <c r="D108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="E108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="F108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="G108" s="120">
+        <v>0.51</v>
+      </c>
+      <c r="H108" s="120">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B109" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D109" s="120">
+        <v>1</v>
+      </c>
+      <c r="E109" s="120">
+        <v>1</v>
+      </c>
+      <c r="F109" s="120">
+        <v>1</v>
+      </c>
+      <c r="G109" s="120">
+        <v>1</v>
+      </c>
+      <c r="H109" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C110" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="E110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="F110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="G110" s="120">
+        <v>0.62</v>
+      </c>
+      <c r="H110" s="120">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C111" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D111" s="120">
+        <v>1</v>
+      </c>
+      <c r="E111" s="120">
+        <v>0</v>
+      </c>
+      <c r="F111" s="120">
+        <v>0</v>
+      </c>
+      <c r="G111" s="120">
+        <v>0</v>
+      </c>
+      <c r="H111" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C112" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D112" s="120">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E108" s="120">
-        <v>0</v>
-      </c>
-      <c r="F108" s="120">
-        <v>0</v>
-      </c>
-      <c r="G108" s="120">
-        <v>0</v>
-      </c>
-      <c r="H108" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A110" s="109" t="s">
+      <c r="E112" s="120">
+        <v>0</v>
+      </c>
+      <c r="F112" s="120">
+        <v>0</v>
+      </c>
+      <c r="G112" s="120">
+        <v>0</v>
+      </c>
+      <c r="H112" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" s="106" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A114" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="B110" s="110"/>
-      <c r="C110" s="110"/>
-      <c r="D110" s="124"/>
-      <c r="E110" s="124"/>
-      <c r="F110" s="124"/>
-      <c r="G110" s="124"/>
-      <c r="H110" s="124"/>
-    </row>
-    <row r="111" spans="1:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="A111" s="29" t="s">
+      <c r="B114" s="110"/>
+      <c r="C114" s="110"/>
+      <c r="D114" s="124"/>
+      <c r="E114" s="124"/>
+      <c r="F114" s="124"/>
+      <c r="G114" s="124"/>
+      <c r="H114" s="124"/>
+    </row>
+    <row r="115" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="A115" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="B115" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="C111" s="96" t="s">
+      <c r="C115" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F115" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G115" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H111" s="4" t="s">
+      <c r="H115" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="39" t="s">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="B112" s="39" t="s">
+      <c r="B116" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="C112" s="39" t="s">
+      <c r="C116" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D112" s="120">
-        <f t="shared" ref="D112:E114" si="1">IF($C2="Affected fraction",D2,IF(D2=1,1,D2*1.05))</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F112" s="120">
-        <f>IF($C57="Affected fraction",F57,IF(F57=1,1,F57*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="G112" s="120">
-        <f>IF($C57="Affected fraction",G57,IF(G57=1,1,G57*0.9))</f>
-        <v>1</v>
-      </c>
-      <c r="H112" s="120">
-        <f>IF($C57="Affected fraction",H57,IF(H57=1,1,H57*0.9))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C113" s="39" t="s">
+      <c r="D116" s="120">
+        <f t="shared" ref="D116:E118" si="2">IF($C2="Affected fraction",D2,IF(D2=1,1,D2*1.05))</f>
+        <v>0</v>
+      </c>
+      <c r="E116" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="120">
+        <f>IF($C59="Affected fraction",F59,IF(F59=1,1,F59*0.9))</f>
+        <v>1</v>
+      </c>
+      <c r="G116" s="120">
+        <f>IF($C59="Affected fraction",G59,IF(G59=1,1,G59*0.9))</f>
+        <v>1</v>
+      </c>
+      <c r="H116" s="120">
+        <f>IF($C59="Affected fraction",H59,IF(H59=1,1,H59*0.9))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C117" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D113" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E113" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="120">
+      <c r="D117" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E117" s="120">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="120">
         <v>0.21</v>
       </c>
-      <c r="G113" s="120">
+      <c r="G117" s="120">
         <v>0.21</v>
       </c>
-      <c r="H113" s="120">
+      <c r="H117" s="120">
         <v>0.21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C114" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D114" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E114" s="120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="120">
-        <v>0.18</v>
-      </c>
-      <c r="G114" s="120">
-        <v>0.18</v>
-      </c>
-      <c r="H114" s="120">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="B115" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C115" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="D115" s="120">
-        <v>0</v>
-      </c>
-      <c r="E115" s="120">
-        <v>0</v>
-      </c>
-      <c r="F115" s="120">
-        <v>1</v>
-      </c>
-      <c r="G115" s="120">
-        <v>1</v>
-      </c>
-      <c r="H115" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C116" s="39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D116" s="120">
-        <v>0</v>
-      </c>
-      <c r="E116" s="120">
-        <v>0</v>
-      </c>
-      <c r="F116" s="120">
-        <v>0</v>
-      </c>
-      <c r="G116" s="120">
-        <v>0</v>
-      </c>
-      <c r="H116" s="120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B117" s="39" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="D117" s="120">
-        <v>0</v>
-      </c>
-      <c r="E117" s="120">
-        <v>0</v>
-      </c>
-      <c r="F117" s="120">
-        <v>1</v>
-      </c>
-      <c r="G117" s="120">
-        <v>1</v>
-      </c>
-      <c r="H117" s="120">
-        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -39928,24 +39960,26 @@
         <v>369</v>
       </c>
       <c r="D118" s="120">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E118" s="120">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H118" s="120">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="39" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B119" s="39" t="s">
         <v>236</v>
@@ -40034,7 +40068,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="39" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B123" s="39" t="s">
         <v>236</v>
@@ -40063,21 +40097,18 @@
         <v>369</v>
       </c>
       <c r="D124" s="120">
-        <f t="shared" ref="D124:H136" si="2">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
         <v>0</v>
       </c>
       <c r="E124" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="120">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="G124" s="120">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H124" s="120">
-        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40089,23 +40120,18 @@
         <v>368</v>
       </c>
       <c r="D125" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E125" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="120">
-        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*1.05))</f>
         <v>1</v>
       </c>
       <c r="G125" s="120">
-        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*1.05))</f>
         <v>1</v>
       </c>
       <c r="H125" s="120">
-        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40114,27 +40140,24 @@
         <v>369</v>
       </c>
       <c r="D126" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E126" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="120">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G126" s="120">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="120">
-        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*1.05))</f>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="39" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="B127" s="39" t="s">
         <v>236</v>
@@ -40143,24 +40166,19 @@
         <v>368</v>
       </c>
       <c r="D127" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E127" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="120">
-        <f>IF($C17="Affected fraction",F17,IF(F17=1,1,F17*1.05))</f>
         <v>1</v>
       </c>
       <c r="G127" s="120">
-        <f>IF($C17="Affected fraction",G17,IF(G17=1,1,G17*1.05))</f>
         <v>1</v>
       </c>
       <c r="H127" s="120">
-        <f>IF($C17="Affected fraction",H17,IF(H17=1,1,H17*1.05))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -40168,20 +40186,21 @@
         <v>369</v>
       </c>
       <c r="D128" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D128:E130" si="3">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
         <v>0</v>
       </c>
       <c r="E128" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F128" s="120">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G128" s="120">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H128" s="120">
+        <f>IF($C14="Affected fraction",H14,IF(H14=1,1,H14*1.05))</f>
         <v>0</v>
       </c>
     </row>
@@ -40193,21 +40212,24 @@
         <v>368</v>
       </c>
       <c r="D129" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E129" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F129" s="120">
+        <f>IF($C15="Affected fraction",F15,IF(F15=1,1,F15*1.05))</f>
         <v>1</v>
       </c>
       <c r="G129" s="120">
+        <f>IF($C15="Affected fraction",G15,IF(G15=1,1,G15*1.05))</f>
         <v>1</v>
       </c>
       <c r="H129" s="120">
-        <v>1</v>
+        <f>IF($C15="Affected fraction",H15,IF(H15=1,1,H15*1.05))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -40215,51 +40237,44 @@
         <v>369</v>
       </c>
       <c r="D130" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E130" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F130" s="120">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G130" s="120">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H130" s="120">
+        <f>IF($C16="Affected fraction",H16,IF(H16=1,1,H16*1.05))</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="39" t="s">
-        <v>202</v>
-      </c>
       <c r="B131" s="39" t="s">
-        <v>111</v>
+        <v>372</v>
       </c>
       <c r="C131" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D131" s="120">
-        <f>IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -40268,159 +40283,150 @@
         <v>370</v>
       </c>
       <c r="D132" s="120">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H132" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="39" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B133" s="39" t="s">
-        <v>111</v>
+        <v>236</v>
       </c>
       <c r="C133" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D133" s="120">
-        <f>IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
-        <v>1</v>
+        <f>IF($C19="Affected fraction",D19,IF(D19=1,1,D19*1.05))</f>
+        <v>0</v>
       </c>
       <c r="E133" s="120">
-        <f t="shared" si="2"/>
+        <f>IF($C19="Affected fraction",E19,IF(E19=1,1,E19*1.05))</f>
         <v>0</v>
       </c>
       <c r="F133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",F19,IF(F19=1,1,F19*1.05))</f>
+        <v>1</v>
       </c>
       <c r="G133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",G19,IF(G19=1,1,G19*1.05))</f>
+        <v>1</v>
       </c>
       <c r="H133" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF($C19="Affected fraction",H19,IF(H19=1,1,H19*1.05))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C134" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D134" s="120">
-        <v>0.16</v>
+        <f t="shared" ref="D134:H142" si="4">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*1.05))</f>
+        <v>0</v>
       </c>
       <c r="E134" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H134" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="39" t="s">
-        <v>201</v>
-      </c>
       <c r="B135" s="39" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="C135" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D135" s="120">
-        <f>IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="E135" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="120">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C136" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D136" s="120">
-        <v>0.16</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="E136" s="120">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H136" s="120">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="B137" s="39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C137" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D137" s="120">
+        <f>IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
         <v>1</v>
       </c>
       <c r="E137" s="120">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="F137" s="120">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="G137" s="120">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="H137" s="120">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -40428,110 +40434,138 @@
         <v>370</v>
       </c>
       <c r="D138" s="120">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="E138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="F138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="G138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="H138" s="120">
-        <v>0.51</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B139" s="39" t="s">
+        <v>111</v>
+      </c>
       <c r="C139" s="39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D139" s="120">
-        <v>0</v>
+        <f>IF($C82="Affected fraction",D82,IF(D82=1,1,D82*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E139" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F139" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G139" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H139" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="B140" s="39" t="s">
-        <v>103</v>
-      </c>
       <c r="C140" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D140" s="120">
+        <v>0.16</v>
+      </c>
+      <c r="E140" s="120">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="120">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G140" s="120">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H140" s="120">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="B141" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C141" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D140" s="120">
-        <v>1</v>
-      </c>
-      <c r="E140" s="120">
-        <v>1</v>
-      </c>
-      <c r="F140" s="120">
-        <v>1</v>
-      </c>
-      <c r="G140" s="120">
-        <v>1</v>
-      </c>
-      <c r="H140" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C141" s="39" t="s">
-        <v>370</v>
-      </c>
       <c r="D141" s="120">
-        <v>0</v>
+        <f>IF($C84="Affected fraction",D84,IF(D84=1,1,D84*0.9))</f>
+        <v>1</v>
       </c>
       <c r="E141" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F141" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G141" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H141" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C142" s="39" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D142" s="120">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="E142" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F142" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G142" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H142" s="120">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B143" s="39" t="s">
         <v>103</v>
@@ -40560,19 +40594,19 @@
         <v>370</v>
       </c>
       <c r="D144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H144" s="120">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -40597,7 +40631,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="39" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B146" s="39" t="s">
         <v>103</v>
@@ -40663,7 +40697,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B149" s="39" t="s">
         <v>103</v>
@@ -40729,7 +40763,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B152" s="39" t="s">
         <v>103</v>
@@ -40738,23 +40772,18 @@
         <v>368</v>
       </c>
       <c r="D152" s="120">
-        <f t="shared" ref="D152:H153" si="3">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H152" s="120">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -40763,23 +40792,18 @@
         <v>370</v>
       </c>
       <c r="D153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H153" s="120">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -40788,30 +40812,33 @@
         <v>369</v>
       </c>
       <c r="D154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H154" s="120">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="39" t="s">
+        <v>226</v>
+      </c>
       <c r="B155" s="39" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C155" s="39" t="s">
         <v>368</v>
       </c>
       <c r="D155" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" s="120">
         <v>1</v>
@@ -40868,7 +40895,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="39" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B158" s="39" t="s">
         <v>103</v>
@@ -40877,18 +40904,23 @@
         <v>368</v>
       </c>
       <c r="D158" s="120">
-        <v>1</v>
+        <f t="shared" ref="D158:H159" si="5">IF($C101="Affected fraction",D101,IF(D101=1,1,D101*0.9))</f>
+        <v>0</v>
       </c>
       <c r="E158" s="120">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F158" s="120">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G158" s="120">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H158" s="120">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -40897,79 +40929,75 @@
         <v>370</v>
       </c>
       <c r="D159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="E159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="F159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="G159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H159" s="120">
-        <v>0.8</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="B160" s="39" t="s">
-        <v>103</v>
-      </c>
       <c r="C160" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="E160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="F160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="G160" s="120">
+        <v>0.1</v>
+      </c>
+      <c r="H160" s="120">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B161" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C161" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="D160" s="120">
-        <v>1</v>
-      </c>
-      <c r="E160" s="120">
-        <v>1</v>
-      </c>
-      <c r="F160" s="120">
-        <v>1</v>
-      </c>
-      <c r="G160" s="120">
-        <v>1</v>
-      </c>
-      <c r="H160" s="120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C161" s="39" t="s">
+      <c r="D161" s="120">
+        <v>0</v>
+      </c>
+      <c r="E161" s="120">
+        <v>1</v>
+      </c>
+      <c r="F161" s="120">
+        <v>1</v>
+      </c>
+      <c r="G161" s="120">
+        <v>1</v>
+      </c>
+      <c r="H161" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C162" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="E161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="F161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="G161" s="120">
-        <v>0.85</v>
-      </c>
-      <c r="H161" s="120">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="B162" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C162" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="D162" s="120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="120">
         <v>0</v>
@@ -40986,26 +41014,164 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C163" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D163" s="120">
+        <v>0</v>
+      </c>
+      <c r="E163" s="120">
+        <v>0</v>
+      </c>
+      <c r="F163" s="120">
+        <v>0</v>
+      </c>
+      <c r="G163" s="120">
+        <v>0</v>
+      </c>
+      <c r="H163" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="B164" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C164" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D164" s="120">
+        <v>1</v>
+      </c>
+      <c r="E164" s="120">
+        <v>1</v>
+      </c>
+      <c r="F164" s="120">
+        <v>1</v>
+      </c>
+      <c r="G164" s="120">
+        <v>1</v>
+      </c>
+      <c r="H164" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C165" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="D163" s="120">
+      <c r="D165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="E165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="F165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="G165" s="120">
+        <v>0.8</v>
+      </c>
+      <c r="H165" s="120">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B166" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C166" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D166" s="120">
+        <v>1</v>
+      </c>
+      <c r="E166" s="120">
+        <v>1</v>
+      </c>
+      <c r="F166" s="120">
+        <v>1</v>
+      </c>
+      <c r="G166" s="120">
+        <v>1</v>
+      </c>
+      <c r="H166" s="120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C167" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="E167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="F167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="G167" s="120">
+        <v>0.85</v>
+      </c>
+      <c r="H167" s="120">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B168" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C168" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="D168" s="120">
+        <v>1</v>
+      </c>
+      <c r="E168" s="120">
+        <v>0</v>
+      </c>
+      <c r="F168" s="120">
+        <v>0</v>
+      </c>
+      <c r="G168" s="120">
+        <v>0</v>
+      </c>
+      <c r="H168" s="120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C169" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D169" s="120">
         <v>0.47</v>
       </c>
-      <c r="E163" s="120">
-        <v>0</v>
-      </c>
-      <c r="F163" s="120">
-        <v>0</v>
-      </c>
-      <c r="G163" s="120">
-        <v>0</v>
-      </c>
-      <c r="H163" s="120">
+      <c r="E169" s="120">
+        <v>0</v>
+      </c>
+      <c r="F169" s="120">
+        <v>0</v>
+      </c>
+      <c r="G169" s="120">
+        <v>0</v>
+      </c>
+      <c r="H169" s="120">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Xklxjcy//qPTjGjkOZsaDhZu/NPrEtmZJSAW2SgZvo0C7jOK3hRAq3c5xMncaQeP1/zwTkGRyVZcwguzwkyizA==" saltValue="ccmcEV8oDWI1nB4PYfVMtA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NQDraY2spfYYVqzQl8LZ0IRapA92gjwtELgJ5fK6J8OybvPWszF5yIEiRFd/q/28uvnkyHd/XnQGO8UFRz8trw==" saltValue="R9mKlxhzrk50HvWT01xhCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -41646,7 +41812,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LvY12DXCFCvJiTXblMmWEVlJtT/DirB1JMUTxrfwI6+SYQ8euLn3Z3cWTBVJbySks/BTkzHU8RJ0hGhVnFQhPg==" saltValue="NcdJ2dOhfyX8DreGz3nx8A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fSFUK4/veL4EaDNsOZQzTiVRQqDUFkgwYbfpkrXoffRtOGhO5P1hYAe18C1SoyYsFLLMeSb9j+A5uO0RX90bew==" saltValue="JsYs5PT74m4SVF0fzJpSvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -42079,7 +42245,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CFQoHJM/rRM188FHErslsSZeNpEQ3C2UY71a9hkCnT4Biaf998KvWcCPK48OaVvh6r9iYaenjVOsVpgNLe5mFw==" saltValue="/+LJzmxJZ0I0OwGXB5Tr/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1Yu4H4DRz1UO8PL6PV+PNo5owm9GelHdFHHv2iu/4MFmk65SrIFfLBW1HKjo/H1VPd2UAjDhW8b+unJkeaJ9Ng==" saltValue="HFTbGshtnjb4DtzopHTp6Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -42498,7 +42664,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OwPcCuEcGz7d1zjyYMzilUrRjsNMQru1VXCWYqMjEN5l/cWatfuHcpNCHuWM5DZwS/W2KW9SI9le0ShCOSJZNw==" saltValue="IITMpQrarL0wCu3mu0k5+Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="f3Il73s6TGtPmfwNHai934JBTN8TQTmPf9NJ5danll8elA9x0AZtD2OZaSPLkfsGlMc2O/Wq8uL9aE3ZE4qfpg==" saltValue="TkCytuo6mPYBnXRCHrEmBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -42630,7 +42796,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wyYplzFvKRtPp3IbhxTWsSZb+kTz3BWLkfCokdDxMdNHxFmtzZ3m7Ws5Qx746WSTrzb9iWbef3PLf+Gm/RpmZg==" saltValue="0zWN56rqPqZc3ziqGYftoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="M/0c4dB0TZ0VaNxDXrNCGdYT4rsc0QnFuqBh5mT5R1k2ptOBVUYwkH0t4TUQEMjfmq4rAFg45T1HysVY+plJ4w==" saltValue="CebHOV0kO4jwr2Ycg/4uJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -42832,7 +42998,7 @@
       <c r="K14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="miYoXhL85vetEP/GR/2AsKFTI4virjnDsxiEJJAW3f9Xc9aCuh5T51tFAKB3xQBf9Fs/UpocuDfZOOQRCJ/Y3A==" saltValue="YsCJJKHscQp2Y84ae32zIw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OZe0/xzsWNewZ/GfKZ0U9100y9gsUr3bfPaF9NnSjI/skPG/mJ3g6UCkAXIhPKfUoOko8IZkrjo3RVZmWopzNg==" saltValue="sbdbzWLS90cfvBxVsGvFEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43094,7 +43260,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="F6ljvdnlGAox8gJXCHxqY96bDwixsbQ1K+xo33dc/8eACken6lj8Ka1Q03X7FVlqxYGXBAvdzCNXM8Yx/jERZg==" saltValue="kx8U+qUT5zz5n0no9yOoMA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/nweEJy/jl37fsIpuSvyNtzu+QXKkgkrrVz7kvvRhmxf7Uhb59pLFe652jgz5qyMLS7eWMF5H6MqsLMEiY/HsQ==" saltValue="VimdUYqa7DCds+NB4+9jCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -43354,7 +43520,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="t0C0B1KolZM2T6TuA35aYP/PUMT2P6cOFv2sh7e45j3C+t0fuNiTNp9fcBvEq0Gj33wHq5k9mMCLzz2i/F8d7g==" saltValue="lwg+rVdOR3sjEAO9mCXnWA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lv0oJ3iZfhL1RMOjT9sd+5i/85hbjDrUyNFdU04PlAdTTrTpFzJzoMWYwd4DUqs450fKUEChnEQpKFMjkVUjkQ==" saltValue="gkT1ntWGVNlBdzjno+XVOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -43413,7 +43579,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Xjm0bXVTrMNsmAhJqsHHF6dYZtQRKE0WA3OD8e7mAh9VTL5BIDpItlEv/IyuPUAayNsj+YmKWbS3npcBRIxbvg==" saltValue="XQY/V+54ECXvIKVa/e/f/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6MtL4TqQeV8imfqSlvueIBB4vr3GGluF8yy6Mt24W0jct6amJ4FBqC4qj8hNU1u5UXoerixoXrnP7u8KefXMaA==" saltValue="KeIQE5UKfdIs3MH2Vnp3UA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/es/demo_region3_input.xlsx
+++ b/inputs/es/demo_region3_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr saveExternalLinkValues="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\es\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\es\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B17A955-6F76-4C21-8A33-A4A4322F58D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{119D5094-C7F4-4AE2-865E-B753F7B77785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas de población-año base" sheetId="1" r:id="rId1"/>
@@ -10865,6 +10865,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Baseline year population inputs"/>
       <sheetName val="Demographic projections"/>
@@ -11688,7 +11691,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nlCkvOYX1UbZROdF6iWUTBJsByfjz7oJ+y99dVjpvzU/kZi7JjyEe+Yy5hxxtIYGB5J7NAFTogPdJRaMe6kYtA==" saltValue="lG8c18XPgHIPj0C+wA8v7g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dcAkO0wm/Ogcc7kMob31Qk6vaYPjAPHvp2lKBU0TnlCJ9Z3/T6wTfdgGGkmxI3kSi3j6eGzglGKlD3BZVkwuMQ==" saltValue="ZJt0llHjdGvjzqNqqdesog==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -12612,7 +12615,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5n9N8JkQaF89hLNpI+MrcHHUk121soS9xbb7uMF5TJJNafyFEDYKF97c6XsEomXrviVyBzp1Tw/HlCD6E+5YrQ==" saltValue="WL+KNGNDZcPiKRr92YwbzA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="28okrP3RO5qVzFVGf1yA6sVvnzk0jHZx93YJh6Pl+mgyBHEADxYeQmMRmep0JqBLLjjgx0kH/yh22/TWua553g==" saltValue="0BmBu3zaysYWgoWf+g+hAg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D39">
     <sortCondition ref="A2:A39"/>
   </sortState>
@@ -12779,7 +12782,7 @@
       <c r="C20" s="67"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+YHescoDoZGNgqr2B/f4gF4J1pWtVhP5KbFPUP0mxPJdP4C7DleP4xQH/ZoXgt6/AaNt5HDp5ooM5u7lvQvqrA==" saltValue="3OptCr16nkugcXh390RtGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SLRGOgl2fhuYBlB/hYLkdPik4o+qSnGRikbwLhSCXB8m88rAvd4oxV/gC/xTic/qIaN0it1PN54cKYTvaol0aQ==" saltValue="JX/+2W3lI5CGVly+6QF+nA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -12874,7 +12877,7 @@
       <c r="A19" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lNHeh22ZyJwcpaC593oxZM/8brR2Udd0iTQC+imJQN8CrJd3/BVB5NdtQ/uAzG2zuJjAbrpKJWkcAj9tFmvuYQ==" saltValue="h8W664iv6+lb+uTqmH4m9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6lWqU3MCEwqEROMUiarN5WP/F93aEGTaX1Kewo5d6jPeVXrdTT0DQtWc9nSJPlh5yhurdFm16b1uZTxDT6I+wQ==" saltValue="g5UNxksbPZL15XV3RP2HBg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -12984,7 +12987,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="j58SAp1qVXp/yV7VtJMb9cnq7O+JYyKIGIpnw/ApvmIbHCNBl7UK9x5gwQIiQeruyW5exzpL7bGGYCwE964qlA==" saltValue="bdVCu6qn2yLb1Zihgf/T5w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4KHLF/tVBAH8eghgVYPjU8LfiazLAa5YHgnHcYQlx276KyWCraGB9WYjv8k76Qdli0tAquyW45bq6DlfZmj3pA==" saltValue="/tEchpLCcgyzi31/RfNhaA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -14742,7 +14745,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="HmuBaSF/Yi5XITt0V0ur7NhFIq/kHxNxTUT6eW1pfGUxizmq36CjLhyB3V3OqNceGQN1kxDdqKMphC3p5p3duQ==" saltValue="XooRESioeFWwN9LMTDzTLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="h3MIQXg7kkw4iFe1prGoI/7/kygJcFaoxvS9wO0OVZTep2fu8BqbxxvrdfE6cEeYGbClX608iAtaooQ2VOVfsQ==" saltValue="yPDk/V+N4t/ilLH+2pBD9A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:O22">
     <sortCondition ref="B15:B22"/>
   </sortState>
@@ -14777,7 +14780,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eTE6lSoeHDWCvkq5t4TFRNRTTpTpM4eaG3so4KeN5++wzJUprodNaC2zWn3YXfu5zZmHuH+3orqxQV/OeTeIFQ==" saltValue="RC58ld1YOuaDfHtlKeVbJg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wOL+I6jIbxYhmHWlRCPQCVfqJ83Zvl7QS1wjyxREpk+Kc2Hr/i3VA+HXQun5ZkZSjxAECzwQUCPtdvlGzXNN7w==" saltValue="KklZNtjhF/sswcgYmUe8CA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14977,7 +14980,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gQNu32f6V58z+BDcipJi0pwovAfsLzecf/svHOG4ozW5ThJkS5iORg9Nd0HUR7PArCDYb0h6CGtMz2MZn8/mlg==" saltValue="LGpPOHgbsm9iRn7HPIoQVw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WDy0RICXMg02+R1j0JSZ8eBQPDInWVh0p069e7/f7ZNookQKics0+68/e/XchUAskCEOiXKghpJWgj5AbZNRVQ==" saltValue="Wg6itI9X72QLkSAW7Pn68Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -16786,7 +16789,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1CrwyaUy4r1pnjazH9xEUxnqZeIBsGGYNS3MLaGwWArfQZ08cF4F9pY32TAZsFxPUNrY/cOxgm/QUVrxNOFLgA==" saltValue="S6N0ic7ss38i/SwHZdTc9Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uuhG87P9O1HIiFyTEv0eBkle5xNnccDBWQ+b1vDwlgfxi3FxN7h9Ry4Ht+K1tqh3OODmDJnw/6n1+yW+5BoDeg==" saltValue="b5CfDy8E3RMxLGgNMqH4tg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17597,7 +17600,7 @@
       <c r="L39" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="n4lIOP4sAh5bgOOlNRoUw+VUkoRNHH+bErmLfQix7B3KV7V31qplXMEgs8beWd4GPOXW1iTtQQTA/JlJiwLoQg==" saltValue="HXznFJiwb2+uFipvSsjlDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NVY7x0aVyFkx02GddTs2Eainp6qJBiJUeNPuVb7/AhuClQMtboCwg6LtCyQ/pqBg9lQmpvtVRbeH/QQb7Nwkqw==" saltValue="gwqGtR+N64RGdQynaLo5mg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17990,7 +17993,7 @@
       <c r="L14" s="100"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RfIi4GbExdNCJSshvGKVfpmffGOdGpa7tonHYk5K5rxpBeUQtlpA5a751hA+biL0mCMHJx5mwxosOmCvSTF5zw==" saltValue="br8k76gjyesQ2fJcfQsSlQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KJgocYCCrDA8qFTfYDt+NCZIkkY6zY/OyE1DVyPqdP3BDlqua3wk9c8NbRIO0X9+9Lgh402GoyyUuxKsp5HW9Q==" saltValue="kvlNl4W3PpXkXaR/xpVbGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19074,7 +19077,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PmyhSofeRoWsDWuKL90+u18VWaFQ2KLsAipT0keeWSGCwbJ9GM/SbUWB5GzJC/x8Cgx5Afyc/msjhWLxEIGKsg==" saltValue="ep2dqkEXf1+5gYMy10KXmA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fN1VXYaFlyxHcnZw80dK7hFyAK9GfCberwwHPAJzFSOfG4Mw8VscJsnFmbv4rVU+MocWqJr1srrL5/8+R5LOqg==" saltValue="FQszbFPnQlL0WsmpHNz99Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -22869,7 +22872,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tg/5A8V3CpE1EuOYw2/WmFS71hxU92ZHMkYQWsRTBA669RCFJUkZ1YCBLsnOEwnsqmRubhlrLEnKG/6Z7U0Lxw==" saltValue="LRYZzIU2j8CkmatRZkBybw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+6E6iOpoe5ClhLrtSUmR8jYjf+t3h1AicGauJGwrT30tc+LJT3RT91JUbD2ldVS17g0ManAGicOI2hzC0j6oFw==" saltValue="XE65mq6fBaaB5CLH/nuwSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B2:B4"/>
@@ -24130,7 +24133,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AdJlCpx0/Z43GIvaTB4vRRmtOfsai7oQpiMdLAEzZMYWIw/Sow21LTwsjUQ7XoAwsaZCK2bGMsDIobJaYZr+9A==" saltValue="P5riOOCaCl6tLFcZS/enEw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kfcfO15G0H3TBPQkUHhRT22O8iPmwVOEVZqVHjZxSkSWecz4tG8ShRiTXHP021SdGx3YejQktgkDcyp29iPwsA==" saltValue="ncMXcH5RMwUUlCZA+wE6AQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -32263,7 +32266,7 @@
       <c r="I328" s="92"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9f/64YhwssC4OqRZgAYhHAxPTB2w7juwvRYhbkcTQae00IiaZuMNQsCRS0hNq2Izc+Xn57o/kVFLukLQrp0fzg==" saltValue="Tjm8DvO+gEn2O/CgxUOuJA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B9ZxxrmGyvhHBVYWlK0NKHyUbi34Kd/Yb/0JNy4wqytOp2wiMmY/n/sjyUPMO39ZSL4EDtdZdNGzPX11htewBg==" saltValue="rICiq4DKOItfaiuSA5VIQA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33364,7 +33367,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JY0E76bjBj6ESxQHGLjTDrK1tqpT9wenNo1MwQMyRguLDG8GeUAiJiNcEOngV2m/MCtxdCDnxrLA9QX11UnvuQ==" saltValue="2jEeUamTqGVtsRIqvSs2tQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="01d66T5vLJ1lvw0NT2OoryepHMvLNKi06xfwP1vqUfLw9Zc4oAEY2cDC97GGNRlG8uaGqmBeLpD++A5SCVoxKA==" saltValue="0YNT1ii/YE8KbR6XfwkG9g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34305,7 +34308,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FqdFUx2pd/tW2+1kfgWFIWaoTRAnTA9hu5wSAndFiUeXt8U2umPTfWUQlPOg5Kr00o7xSBSN6oIMz1E5VBycug==" saltValue="p7bWhNKu12bQ4DdAi9xaew==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kOM+4Wg/EFJPvGYdSGDK9mNslzu09R5qPE9rnR948qqC3Wzy/S55zpPCilG8ifXUuYSPhxW4ZBUEqjp2K0QeBg==" saltValue="NIGkDkicP6dVb7jlzzJriA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37020,7 +37023,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3HCyt8pnL0JAi0SyZjkVbtE5MCO2OykaGuYu5xX2NYiFvJciSUYpJlba6/XweHcO4tkqj50bC8mRMlowL1JBMA==" saltValue="kOQhyxB3bYuwhLpOEEov9A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AoZGsEtLAiWyu7dPV8YPEpm2fiaQAaaV0+V4KfYze+0bdbvVQdEecST9DLekyz7CGde6FGEoWUV+KkPwi//aaw==" saltValue="sb9d+wUudJCQgTSvgxR1Iw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -37311,7 +37314,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="POLtJ9x/WtL7Mx66ZuPiBfNTNn3xbBfMf3VvmVrRTwIxP5hYxxXJ6CIUx0s+0WvtWi7yCuNu1+AnunxrcEbqPg==" saltValue="nPs/TLiB3eLAdqYuRBZZGA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ierCdiJfWrQ88aZCuvGdRX5IjdqUooVQkIzkHRvphykkaVTsERnogcuvcQ00vn0OjVlHB4UE9J7wfG16sK80MQ==" saltValue="uufORw0Q/5yLL0wcr65Eeg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -41171,7 +41174,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NQDraY2spfYYVqzQl8LZ0IRapA92gjwtELgJ5fK6J8OybvPWszF5yIEiRFd/q/28uvnkyHd/XnQGO8UFRz8trw==" saltValue="R9mKlxhzrk50HvWT01xhCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QxJ1OrNMM20N4xLdOAs6V6Sz5s0c0vX11q2Qkfsc83/gk0eeaSwGOkeL6K7KKZbUjDYbUHjUebjZbr8EMBuOAQ==" saltValue="egG39ICMnMhbMPZH9W9XJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -41812,7 +41815,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fSFUK4/veL4EaDNsOZQzTiVRQqDUFkgwYbfpkrXoffRtOGhO5P1hYAe18C1SoyYsFLLMeSb9j+A5uO0RX90bew==" saltValue="JsYs5PT74m4SVF0fzJpSvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4iijuxScj+ZRuVh0U6vSJg+J2uhhZpInPlYj0MkjigrqPGPNNzjempA7LstOZC+NZySTj5uoaPlwFEbAkhvqYw==" saltValue="xW3UL+JtwsO8zhQAGccM4w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -42245,7 +42248,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1Yu4H4DRz1UO8PL6PV+PNo5owm9GelHdFHHv2iu/4MFmk65SrIFfLBW1HKjo/H1VPd2UAjDhW8b+unJkeaJ9Ng==" saltValue="HFTbGshtnjb4DtzopHTp6Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6Emd86lnJk8jcOxRR8vsKfP7sdT/cacRbnQ451F0IHKjY3KYZdancEyzlN27xR4LokNK3lidTFjvgL1jYiHJkw==" saltValue="CPDBUxcOxejLvDiDAa+1gA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -42664,7 +42667,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="f3Il73s6TGtPmfwNHai934JBTN8TQTmPf9NJ5danll8elA9x0AZtD2OZaSPLkfsGlMc2O/Wq8uL9aE3ZE4qfpg==" saltValue="TkCytuo6mPYBnXRCHrEmBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="y6TAzW/u3wbBZLakn6wwa3oVZQyqeneeLZreXxDeRTaDYWcBc+XuldbKNgvEZxHBjlwiL418bYdV2vvmJ2kJ0g==" saltValue="21UBNU95jF7mIjNu0wkZng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <drawing r:id="rId1"/>
@@ -42796,7 +42799,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M/0c4dB0TZ0VaNxDXrNCGdYT4rsc0QnFuqBh5mT5R1k2ptOBVUYwkH0t4TUQEMjfmq4rAFg45T1HysVY+plJ4w==" saltValue="CebHOV0kO4jwr2Ycg/4uJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zwCqw9N0S2jyEu8bd+EGSb9QQxv0Ugwl4owz4FjCZM09X8+u/eMdYx33iHhZZ7Zc6wwZEiKJ0hwSulRW1C3jug==" saltValue="s3VqvpVqCi/f16XYljGVvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -42998,7 +43001,7 @@
       <c r="K14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OZe0/xzsWNewZ/GfKZ0U9100y9gsUr3bfPaF9NnSjI/skPG/mJ3g6UCkAXIhPKfUoOko8IZkrjo3RVZmWopzNg==" saltValue="sbdbzWLS90cfvBxVsGvFEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Uxhn1ywGGP0EIAgQ9eKLg+DYP9PGOtdVUx4aDOA+pMwISWaKSXYCGftNOHyzomzKNB/E2HDiKlY7dBVOn+GLjA==" saltValue="Qe1N2ojLh3Xwcnog1Vannw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43260,7 +43263,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/nweEJy/jl37fsIpuSvyNtzu+QXKkgkrrVz7kvvRhmxf7Uhb59pLFe652jgz5qyMLS7eWMF5H6MqsLMEiY/HsQ==" saltValue="VimdUYqa7DCds+NB4+9jCg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="k6Z9TW47ImH/d6tx9/8gSefBhm1AhpVQvshLkPgpY2gRaZTu6n8ckL3GgBogjblS3Ha7EfaJrVzaXWBKXE71JA==" saltValue="s1llVZAN7OJTkfWcIqW/xg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -43520,7 +43523,7 @@
       <c r="E21" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lv0oJ3iZfhL1RMOjT9sd+5i/85hbjDrUyNFdU04PlAdTTrTpFzJzoMWYwd4DUqs450fKUEChnEQpKFMjkVUjkQ==" saltValue="gkT1ntWGVNlBdzjno+XVOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HopFK0hEj75MXUrhZDp4XIMq14uRDeEmfM3JgSW6d1CiYxrYP97qPqWXkOfYe4RwDyc0prGKCcfQHxJohYZDSQ==" saltValue="2f+VWKujPdwPP9N4FWPyHw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -43579,7 +43582,7 @@
       <c r="D3" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6MtL4TqQeV8imfqSlvueIBB4vr3GGluF8yy6Mt24W0jct6amJ4FBqC4qj8hNU1u5UXoerixoXrnP7u8KefXMaA==" saltValue="KeIQE5UKfdIs3MH2Vnp3UA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+zQaq9DSDgk8tzNkYpv+6oXOZSMO4KYzvDAL7IX/nwkaCovKOw7AuHnoRfzPPTEPRFiNLBXAAOKczw1VuTM0Qg==" saltValue="P/kGgErgDcFE35+GYugdWA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>